--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Documents\main\NITW-Transportation-Division-main\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Downloads\mainnn\NITW-Transportation-Division-main\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="12150"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12150" firstSheet="10" activeTab="27"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -37,6 +37,9 @@
     <sheet name="2020" sheetId="23" r:id="rId23"/>
     <sheet name="2021" sheetId="24" r:id="rId24"/>
     <sheet name="2022" sheetId="25" r:id="rId25"/>
+    <sheet name="2023" sheetId="26" r:id="rId26"/>
+    <sheet name="2024" sheetId="27" r:id="rId27"/>
+    <sheet name="2025" sheetId="28" r:id="rId28"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -48,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="187">
   <si>
     <t>Year</t>
   </si>
@@ -62,29 +65,560 @@
     <t>Supervisor(s)</t>
   </si>
   <si>
-    <t xml:space="preserve">T.Venkata Ramayya </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traffic Simualtion- Highway Capacity </t>
-  </si>
-  <si>
-    <t>Prof.K.S. Pillai</t>
-  </si>
-  <si>
     <t>Name of the Scholar</t>
   </si>
   <si>
     <t>Photo</t>
   </si>
   <si>
-    <t>Picture1</t>
+    <t>T. Venkata Ramayya</t>
+  </si>
+  <si>
+    <t>Traffic Simulation – Highway Capacity</t>
+  </si>
+  <si>
+    <t>Prof. K.S. Pillai</t>
+  </si>
+  <si>
+    <t>B.K. Katti</t>
+  </si>
+  <si>
+    <t>Traffic Simulation – Intersection LOS</t>
+  </si>
+  <si>
+    <t>Prof. S. Raghavachari</t>
+  </si>
+  <si>
+    <t>B.N. Nagaraj</t>
+  </si>
+  <si>
+    <t>Regional Passenger Transportation Planning</t>
+  </si>
+  <si>
+    <t>B.P. Chandrasekhar</t>
+  </si>
+  <si>
+    <t>Regional Freight Transportation Planning</t>
+  </si>
+  <si>
+    <t>L.R. Kadiyali</t>
+  </si>
+  <si>
+    <t>Highway Economic Analysis</t>
+  </si>
+  <si>
+    <t>S.D. Gupta</t>
+  </si>
+  <si>
+    <t>Bus Network Evaluation</t>
+  </si>
+  <si>
+    <t>S.B. Sripathi Rao</t>
+  </si>
+  <si>
+    <t>Urban Mode Choice Analysis</t>
+  </si>
+  <si>
+    <t>N.V. Ramamoorthy</t>
+  </si>
+  <si>
+    <t>Mass Transit Planning</t>
+  </si>
+  <si>
+    <t>K.M. Badrinath</t>
+  </si>
+  <si>
+    <t>Mixed Traffic Simulation</t>
+  </si>
+  <si>
+    <t>S. Nagabhushana Rao</t>
+  </si>
+  <si>
+    <t>Bus Depot Location Planning</t>
+  </si>
+  <si>
+    <t>Francis Christopher</t>
+  </si>
+  <si>
+    <t>Land Use Transportation Planning</t>
+  </si>
+  <si>
+    <t>T.S. Reddy</t>
+  </si>
+  <si>
+    <t>Urban Freight Transportation</t>
+  </si>
+  <si>
+    <t>C.S.R.K. Prasad</t>
+  </si>
+  <si>
+    <t>Inter-city Mode Choice Analysis</t>
+  </si>
+  <si>
+    <t>R. Murugesan</t>
+  </si>
+  <si>
+    <t>Performance Appraisal of STUs</t>
+  </si>
+  <si>
+    <t>Prof. N.V. Ramamoorthy</t>
+  </si>
+  <si>
+    <t>N. Trivikrama Rao</t>
+  </si>
+  <si>
+    <t>Urban Mass Transit Patronage</t>
+  </si>
+  <si>
+    <t>Prof. B.P. Chandrasekhar</t>
+  </si>
+  <si>
+    <t>Syed Anisuddin</t>
+  </si>
+  <si>
+    <t>Mass Transit System Planning</t>
+  </si>
+  <si>
+    <t>V.R. Vinayak Rao</t>
+  </si>
+  <si>
+    <t>Traffic Forecasting – Time Series Analysis</t>
+  </si>
+  <si>
+    <t>Fareed Md Abdul Karim</t>
+  </si>
+  <si>
+    <t>Rail–Road Freight Mode Choice</t>
+  </si>
+  <si>
+    <t>G.V.R. Prasada Raju</t>
+  </si>
+  <si>
+    <t>Flexible Pavement Performance</t>
+  </si>
+  <si>
+    <t>Mohammed Ahmed Ali</t>
+  </si>
+  <si>
+    <t>Urban Transport Noise</t>
+  </si>
+  <si>
+    <t>C.N.V. Satyanarayana Reddy</t>
+  </si>
+  <si>
+    <t>Flexible Pavement Design</t>
+  </si>
+  <si>
+    <t>G. Bhaskar</t>
+  </si>
+  <si>
+    <t>Bus Transportation Efficiency and Effectiveness</t>
+  </si>
+  <si>
+    <t>B. Raghavendra</t>
+  </si>
+  <si>
+    <t>Combined Urban Transportation Models</t>
+  </si>
+  <si>
+    <t>N. Srinivasa Reddy</t>
+  </si>
+  <si>
+    <t>Modelling Urban Forms and Structures</t>
+  </si>
+  <si>
+    <t>K.V. Krishna Reddy</t>
+  </si>
+  <si>
+    <t>Accelerated Pavement Evaluation</t>
+  </si>
+  <si>
+    <t>M. Rajitha</t>
+  </si>
+  <si>
+    <t>Rigid Pavement Design</t>
+  </si>
+  <si>
+    <t>S. Shankar</t>
+  </si>
+  <si>
+    <t>Low Volume Roads</t>
+  </si>
+  <si>
+    <t>Prof. C.S.R.K. Prasad</t>
+  </si>
+  <si>
+    <t>https://nitw.irins.org/profile_images/156343.JPG</t>
+  </si>
+  <si>
+    <t>D. Abhigna</t>
+  </si>
+  <si>
+    <t>Uncontrolled Intersection Capacity Analysis</t>
+  </si>
+  <si>
+    <t>Dr. K.V.R. Ravi Shankar</t>
+  </si>
+  <si>
+    <t>S. Srikanth</t>
+  </si>
+  <si>
+    <t>Traffic Flow Modeling and Simulation</t>
+  </si>
+  <si>
+    <t>Dr. Arpan Mehar</t>
+  </si>
+  <si>
+    <t>V.M. Naidu</t>
+  </si>
+  <si>
+    <t>Trip Generation Models</t>
+  </si>
+  <si>
+    <t>Anil Modinpuroju</t>
+  </si>
+  <si>
+    <t>Rural Road Network Planning</t>
+  </si>
+  <si>
+    <t>P. Sharat Chandra</t>
+  </si>
+  <si>
+    <t>Public Transport</t>
+  </si>
+  <si>
+    <t>Poojari Yugendar</t>
+  </si>
+  <si>
+    <t>Crowd Behaviour Modeling</t>
+  </si>
+  <si>
+    <t>D. Harinder</t>
+  </si>
+  <si>
+    <t>Coir Geotextiles for Low Volume Roads</t>
+  </si>
+  <si>
+    <t>Dr. S. Shankar</t>
+  </si>
+  <si>
+    <t>S. Eswar</t>
+  </si>
+  <si>
+    <t>Pedestrian Behaviour in Railway Stations</t>
+  </si>
+  <si>
+    <t>Syed Mubashirhussain</t>
+  </si>
+  <si>
+    <t>Rheological Studies</t>
+  </si>
+  <si>
+    <t>Prof. Venkaiah Chowdary</t>
+  </si>
+  <si>
+    <t>Kamineni Aditya</t>
+  </si>
+  <si>
+    <t>Noise Modeling</t>
+  </si>
+  <si>
+    <t>J. Jayakrishna</t>
+  </si>
+  <si>
+    <t>Travel Time Prediction</t>
+  </si>
+  <si>
+    <t>Prashanth Shekar Lokku</t>
+  </si>
+  <si>
+    <t>Transit Oriented Development</t>
+  </si>
+  <si>
+    <t>Utsav Vishal</t>
+  </si>
+  <si>
+    <t>Moisture Damage Studies</t>
+  </si>
+  <si>
+    <t>Ramireddy Sushmitha</t>
+  </si>
+  <si>
+    <t>Signalized Intersection Capacity Analysis</t>
+  </si>
+  <si>
+    <t>Pallavi Gulivindala</t>
+  </si>
+  <si>
+    <t>Capacity Analysis of Urban Roads</t>
+  </si>
+  <si>
+    <t>Kurre Sai Sahithya</t>
+  </si>
+  <si>
+    <t>Urban Road Network Modeling</t>
+  </si>
+  <si>
+    <t>Kamatalam Mahaboob Peera</t>
+  </si>
+  <si>
+    <t>Accident Prediction Models</t>
+  </si>
+  <si>
+    <t>Sarella Chakravarthi</t>
+  </si>
+  <si>
+    <t>Performance Evaluation of Treated Bases</t>
+  </si>
+  <si>
+    <t>Kakara Sreekanth</t>
+  </si>
+  <si>
+    <t>Fatigue and Rutting Studies</t>
+  </si>
+  <si>
+    <t>Thesis title</t>
+  </si>
+  <si>
+    <t>Simulation Studies on Traffic Capacity of Road Systems for Indian Conditions</t>
+  </si>
+  <si>
+    <t>Simulation Analysis of Traffic Quality at Priority Intersection Under Mixed Traffic Conditions</t>
+  </si>
+  <si>
+    <t>Conjectural Origin-Destination Matrix of Bus Passengers Through Cordon Counts in A Region</t>
+  </si>
+  <si>
+    <t>Development of Highway Freight Transportation Demand Model for A region With Application to Hyderabad Area</t>
+  </si>
+  <si>
+    <t>Quantification of Road User Benefits and Their Application to Highway Economic Analysis and Highway Planning in India</t>
+  </si>
+  <si>
+    <t>T. Arjun Kumar</t>
+  </si>
+  <si>
+    <t>G. Shravan Kumar</t>
+  </si>
+  <si>
+    <t>Lalam Govinda</t>
+  </si>
+  <si>
+    <t>Influence of chemical warm mix additive on the performance of bituminous binders and bituminous mixtures containing waste plastic coated coarse aggregate.</t>
+  </si>
+  <si>
+    <t>Pavement Materials- Lime Fly ash and RCA</t>
+  </si>
+  <si>
+    <t>Pedestrian-Vehicle interactions at uncontrolled intersections under mixed traffic conditions</t>
+  </si>
+  <si>
+    <t>Modelling of Operating speed of vehicles for evaluating geometric design consistency on two lane Rural highways in India</t>
+  </si>
+  <si>
+    <t>Examining the effect of Curb-Side bus stop on traffic stream characteristics on Indian Urban roads</t>
+  </si>
+  <si>
+    <t>Assessment of Rail transport noise perceived by trackside dwellers</t>
+  </si>
+  <si>
+    <t>Bus Rapid Transit system and Lad Land-use relationship with mode choice</t>
+  </si>
+  <si>
+    <t>Effect of traffic volume on Ambient air quality on multilane divided urban roads and signalized intersections</t>
+  </si>
+  <si>
+    <t>Estimation of capacity and performance evaluation of uncontrolled intersections</t>
+  </si>
+  <si>
+    <t>Bio-Medical Waste in Pavement Applications</t>
+  </si>
+  <si>
+    <t>Kiran Kumar Tottadi</t>
+  </si>
+  <si>
+    <t>Pallela Sruthi Sekhar</t>
+  </si>
+  <si>
+    <t>Boddu Sudhir Kumar</t>
+  </si>
+  <si>
+    <t>Khalil Ahmad Kakar</t>
+  </si>
+  <si>
+    <t>Rama Kanth Angatha</t>
+  </si>
+  <si>
+    <t>Ramesh K</t>
+  </si>
+  <si>
+    <t>G. Ramulu</t>
+  </si>
+  <si>
+    <t>Gummadi Chiranjeevi</t>
+  </si>
+  <si>
+    <t>G Dharma Teja</t>
+  </si>
+  <si>
+    <t>G.S. Diwakar</t>
+  </si>
+  <si>
+    <t>Influence of aggregate gradation on Permeability, Clogging and Performance of porous Asphalt Mixtures</t>
+  </si>
+  <si>
+    <t>Safety Evaluation of Horizontal Curves on Two Lane Rural Highways in India</t>
+  </si>
+  <si>
+    <t>Surrogate Safety Analysis and Risk Modelling of Entry-Circulating Vehicle Conflicts at Roundabouts under Mixed Traffic Conditions</t>
+  </si>
+  <si>
+    <t>Analysis of queuing behavior on signalized intersections</t>
+  </si>
+  <si>
+    <t>Capacity Analysis of Signalized Intersections in Mixed Traffic Conditions</t>
+  </si>
+  <si>
+    <t>Capacity Analysis of Multilane Divided Urban Roads Under the Influence of Side Friction in Heterogenous Traffic Conditions</t>
+  </si>
+  <si>
+    <t>Evaluation and Modelling of Urban Road Network Structure Using Geographic Information System (GIS)</t>
+  </si>
+  <si>
+    <t>Development of Land Use Based Accident Prediction Models</t>
+  </si>
+  <si>
+    <t>Performance Evaluation of Cement and Emulsified Asphalt Treated Bases</t>
+  </si>
+  <si>
+    <t>Influence of Roughness Induced Dynamic Loads on Fatigue and Rutting Damages in Flexible Pavement</t>
+  </si>
+  <si>
+    <t>Jithender J</t>
+  </si>
+  <si>
+    <t>Travel Time Prediction and Signal coordination in Mixed Traffic Conditions</t>
+  </si>
+  <si>
+    <t>A Framework for Implementation of Transit-Oriented Development</t>
+  </si>
+  <si>
+    <t>Influence of Moisture Damage and Hydrated Lime on the Fatigue Life of Hot Mix Asphalt and Warm Mix Asphalt</t>
+  </si>
+  <si>
+    <t>Pedestrian Behavior Modeling on Level Changing Facilities Inside Railway Stations</t>
+  </si>
+  <si>
+    <t>Rheological Studies on Identification of New Rutting Parameters for Unmodified Bitumen</t>
+  </si>
+  <si>
+    <t>Assessment of the Effects of Vehicular Speeds on Noise Levels Generated from Vehicles as Perceived by Commuters and Road users</t>
+  </si>
+  <si>
+    <t>Traffic flow modeling and simulation of traffic behavior under mixed traffic conditions</t>
+  </si>
+  <si>
+    <t>Modeling Trip Generation Rates for Indian Cities</t>
+  </si>
+  <si>
+    <t>Facility-Based Rural Road Network Planning Using Spatial Techniques</t>
+  </si>
+  <si>
+    <t>Desirable Public Transport Shares for Indian Cities</t>
+  </si>
+  <si>
+    <t>Micro and Macroscopic Analysis of Crowd Behavior and Evacuation Planning.</t>
+  </si>
+  <si>
+    <t>Rutting Potential of Coir Geotextiles as Interface over Poor Subgrade for Low Volume Roads</t>
+  </si>
+  <si>
+    <t>Capacity Analysis of Uncontrolled Intersections and Roundabouts in Mixed Traffic Conditions</t>
+  </si>
+  <si>
+    <t>Pavement Deterioration Models for Low Volume Roads</t>
+  </si>
+  <si>
+    <t>Development of performance-based design and appraisal of steel fiber placed in critical regions of rigid pavement</t>
+  </si>
+  <si>
+    <t>Performance Evaluation of flexible pavements on stabilized subgrade with modified surface course using accelerated pavement testing</t>
+  </si>
+  <si>
+    <t>Strategic appraisal of human resource functions of state transport undertakings for profitability using artificial neural network</t>
+  </si>
+  <si>
+    <t>SBC-Based Design and Performance Aspects of Reinforced Flexible Pavements with Anchored Geotextiles Over Expansive Soil Subgrades</t>
+  </si>
+  <si>
+    <t>Development of volume-based trip generation models and combined distribution and assignment model with a feedback mechanism for simplified urban transportation planning</t>
+  </si>
+  <si>
+    <t>Modeling urban form and structure using transportation planning techniques for small and medium cities</t>
+  </si>
+  <si>
+    <t>Evaluation of Flexible Pavement Performance with Reinforcement and Chemical Stabilization of Expensive Soil Subgrade</t>
+  </si>
+  <si>
+    <t>Urban Transport Noise: Magnitude, Perceptions and Modelling</t>
+  </si>
+  <si>
+    <t>Behavioral Mode Choice Models for Rail Road Non-Bulk Commodity Transport</t>
+  </si>
+  <si>
+    <t>Traffic Growth, Modelling on Primary Road System Through Modified ARMA And Multiple Time Series Analysis Using Data From PTCS</t>
+  </si>
+  <si>
+    <t>Strategic Appraisal and Performance Optimization of State Transport Undertaking with User-Operator Perceptions</t>
+  </si>
+  <si>
+    <t>Urban Mass Transit Patronage Through Link Volume Counts with Route and Mode Choice Behavior</t>
+  </si>
+  <si>
+    <t>Mass Transit System Planning and Scheduling for An Identified Corridor Incorporating Time Congestion Effects Through Optimization Techniques</t>
+  </si>
+  <si>
+    <t>Urban Goods Flow Characteristics and Demand Estimation</t>
+  </si>
+  <si>
+    <t>Behavioral Mode Choice Models for Intercity Rail-Road Passenger Travel</t>
+  </si>
+  <si>
+    <t>Urban Traffic System Model for Managing Traffic</t>
+  </si>
+  <si>
+    <t>Location and Sizing of Bus depot In Relation to Rural Travel in A Region</t>
+  </si>
+  <si>
+    <t>Demand Oriented Route Network Generation and Appraisal Form Integrated Urban Mass Transit System</t>
+  </si>
+  <si>
+    <t>Development of Methodology for Optimal Selection of Civil Engineering Parameters in Railway Projects</t>
+  </si>
+  <si>
+    <t>B.U. Rama Rao</t>
+  </si>
+  <si>
+    <t>Community Response to Components of Urban Transport for Work Journeys Through Mode Choice Models</t>
+  </si>
+  <si>
+    <t>Planning and Evaluation of Urban Bus Route Networks Based on Origin-Destination Information in A Multimode Environment</t>
+  </si>
+  <si>
+    <t>2008/81201</t>
+  </si>
+  <si>
+    <t>https://media.licdn.com/dms/image/v2/C5103AQEdsBhjnc233g/profile-displayphoto-shrink_200_200/profile-displayphoto-shrink_200_200/0/1560254960329?e=2147483647&amp;v=beta&amp;t=NH0m6tvpm5uWPHOUe91O7fF8Cjl4-S4VuzNHp8vL8VQ</t>
+  </si>
+  <si>
+    <t>S2025/GummadiChiranjeevi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +640,21 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -124,15 +673,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -411,46 +968,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="42.28515625" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="3" max="4" width="42.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1980</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1980</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -460,10 +1020,10 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,31 +1034,32 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1996</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="E3" s="2"/>
+      <c r="B2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -507,13 +1068,13 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -524,44 +1085,50 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1997</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="150" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>1997</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
+      <c r="B3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -571,10 +1138,10 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -585,61 +1152,64 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="240" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1998</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="225" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>1998</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="B3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="315" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>1998</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
+      <c r="B4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -649,10 +1219,10 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -663,27 +1233,30 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="285" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1999</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
+      <c r="B2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -693,10 +1266,10 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -706,28 +1279,31 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="180" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>2000</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
+      <c r="B2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -737,10 +1313,10 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -751,45 +1327,50 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="270" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>2001</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>2001</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -798,10 +1379,10 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -812,45 +1393,50 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="315" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>2003</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="225" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>2003</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -859,10 +1445,10 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -873,45 +1459,50 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="375" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>2004</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="210" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>2004</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -920,10 +1511,10 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -934,31 +1525,35 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="300" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>2005</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="E3" s="2"/>
+      <c r="B2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -967,10 +1562,10 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -981,28 +1576,32 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="240" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>2006</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1011,10 +1610,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="4" width="22.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1025,27 +1627,30 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1982</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1055,10 +1660,13 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="45.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1069,27 +1677,33 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>2012</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
+      <c r="B2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1099,10 +1713,10 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1113,27 +1727,33 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="195" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>2018</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
+      <c r="B2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -1143,10 +1763,10 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1156,114 +1776,123 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="195" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>2019</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>2019</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="B3" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" ht="150" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>2019</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="B4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>2019</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="B5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" ht="165" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>2019</v>
       </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="B6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" ht="180" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>2019</v>
       </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1272,10 +1901,10 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1286,62 +1915,68 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="165" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>2020</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="195" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>2020</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="B3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" ht="285" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>2020</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1350,10 +1985,10 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1363,63 +1998,69 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="165" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>2021</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="150" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>2021</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="B3" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" ht="240" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>2021</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1428,15 +2069,15 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.42578125" customWidth="1"/>
-    <col min="3" max="3" width="41.5703125" customWidth="1"/>
-    <col min="4" max="4" width="23.42578125" customWidth="1"/>
+    <col min="3" max="4" width="41.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1446,126 +2087,146 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
         <v>2022</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B2" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>2022</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="B3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>2022</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="B4" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>2022</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="B5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>2022</v>
       </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="B6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>2022</v>
       </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B7" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1575,28 +2236,47 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1983</v>
+        <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2023</v>
+      </c>
+      <c r="B3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2023</v>
+      </c>
+      <c r="B4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1604,12 +2284,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1619,28 +2299,91 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1984</v>
+        <v>2024</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2024</v>
+      </c>
+      <c r="B3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2024</v>
+      </c>
+      <c r="B4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2024</v>
+      </c>
+      <c r="B5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2024</v>
+      </c>
+      <c r="B6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2024</v>
+      </c>
+      <c r="B7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2024</v>
+      </c>
+      <c r="B8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1648,12 +2391,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1663,28 +2406,50 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1985</v>
+        <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
+        <v>137</v>
+      </c>
+      <c r="F2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -1692,12 +2457,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1708,27 +2473,30 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1986</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
+    </row>
+    <row r="2" spans="1:6" ht="195" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1983</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1736,12 +2504,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1752,27 +2520,30 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1988</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
+    </row>
+    <row r="2" spans="1:6" ht="225" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1984</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1780,16 +2551,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="21.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1800,27 +2567,30 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1989</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
+    </row>
+    <row r="2" spans="1:6" ht="255" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1985</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1828,15 +2598,171 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="270" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1986</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="225" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1988</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1989</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1989</v>
+      </c>
+      <c r="B3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1847,44 +2773,47 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1992</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>1992</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
+      <c r="B3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12150" firstSheet="10" activeTab="27"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12150" firstSheet="21" activeTab="26"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="206">
   <si>
     <t>Year</t>
   </si>
@@ -611,7 +611,64 @@
     <t>https://media.licdn.com/dms/image/v2/C5103AQEdsBhjnc233g/profile-displayphoto-shrink_200_200/profile-displayphoto-shrink_200_200/0/1560254960329?e=2147483647&amp;v=beta&amp;t=NH0m6tvpm5uWPHOUe91O7fF8Cjl4-S4VuzNHp8vL8VQ</t>
   </si>
   <si>
-    <t>S2025/GummadiChiranjeevi</t>
+    <t xml:space="preserve">Urban Planning </t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2025/GummadiChiranjeevi</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2022/J.Jithender</t>
+  </si>
+  <si>
+    <t>Safety Analysis of Horizontal Curved</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2025/719017</t>
+  </si>
+  <si>
+    <t>K.V.R. Ravi Shankar</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2025/22CER1Q01</t>
+  </si>
+  <si>
+    <t>S.Shankar</t>
+  </si>
+  <si>
+    <t>Safety Analysis of Roundabout Intersection</t>
+  </si>
+  <si>
+    <t>Arpan Mehar</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2024/719030</t>
+  </si>
+  <si>
+    <t>Traffic Engineering</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2024/Pallela Sruthi</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2024/718106</t>
+  </si>
+  <si>
+    <t>Transportation Engineering (Rail transport Acoustics)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venkaiah Chowdary </t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2024/Khalil Ahmad Kakar</t>
+  </si>
+  <si>
+    <t>C.S.R.K Prasad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavement Materials </t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2024/721005</t>
   </si>
 </sst>
 </file>
@@ -2104,8 +2161,17 @@
       <c r="B2" s="6" t="s">
         <v>147</v>
       </c>
+      <c r="C2" s="6" t="s">
+        <v>186</v>
+      </c>
       <c r="D2" s="3" t="s">
         <v>140</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2316,8 +2382,17 @@
       <c r="B2" t="s">
         <v>127</v>
       </c>
+      <c r="C2" t="s">
+        <v>197</v>
+      </c>
       <c r="D2" t="s">
         <v>120</v>
+      </c>
+      <c r="E2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2330,6 +2405,12 @@
       <c r="D3" t="s">
         <v>121</v>
       </c>
+      <c r="E3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F3" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -2338,8 +2419,17 @@
       <c r="B4" t="s">
         <v>129</v>
       </c>
+      <c r="C4" t="s">
+        <v>200</v>
+      </c>
       <c r="D4" t="s">
         <v>122</v>
+      </c>
+      <c r="E4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2352,6 +2442,12 @@
       <c r="D5" t="s">
         <v>123</v>
       </c>
+      <c r="E5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F5" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -2363,6 +2459,9 @@
       <c r="D6" t="s">
         <v>124</v>
       </c>
+      <c r="E6" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -2374,6 +2473,9 @@
       <c r="D7" t="s">
         <v>125</v>
       </c>
+      <c r="E7" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -2382,8 +2484,17 @@
       <c r="B8" t="s">
         <v>133</v>
       </c>
+      <c r="C8" t="s">
+        <v>204</v>
+      </c>
       <c r="D8" t="s">
         <v>126</v>
+      </c>
+      <c r="E8" t="s">
+        <v>193</v>
+      </c>
+      <c r="F8" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -2395,6 +2506,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="75" customWidth="1"/>
+    <col min="5" max="5" width="66.140625" customWidth="1"/>
+    <col min="6" max="6" width="32.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -2426,8 +2542,11 @@
       <c r="D2" t="s">
         <v>137</v>
       </c>
+      <c r="E2" t="s">
+        <v>193</v>
+      </c>
       <c r="F2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2437,8 +2556,17 @@
       <c r="B3" t="s">
         <v>135</v>
       </c>
+      <c r="C3" t="s">
+        <v>189</v>
+      </c>
       <c r="D3" t="s">
         <v>138</v>
+      </c>
+      <c r="E3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F3" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2448,8 +2576,17 @@
       <c r="B4" t="s">
         <v>136</v>
       </c>
+      <c r="C4" t="s">
+        <v>194</v>
+      </c>
       <c r="D4" t="s">
         <v>139</v>
+      </c>
+      <c r="E4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F4" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Downloads\mainnn\NITW-Transportation-Division-main\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD6FA6E-CC69-4706-992D-8F02365F32E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12150" firstSheet="21" activeTab="26"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -51,14 +52,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="205">
   <si>
     <t>Year</t>
   </si>
   <si>
-    <t xml:space="preserve">Name of the Scholar </t>
-  </si>
-  <si>
     <t>Area of Research</t>
   </si>
   <si>
@@ -674,7 +672,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -734,7 +732,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -743,7 +741,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1024,7 +1021,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1038,19 +1035,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1058,16 +1055,16 @@
         <v>1980</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1073,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1085,19 +1082,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -1105,14 +1102,14 @@
         <v>1996</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -1124,7 +1121,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1136,19 +1133,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="135" x14ac:dyDescent="0.25">
@@ -1156,16 +1153,16 @@
         <v>1997</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="150" x14ac:dyDescent="0.25">
@@ -1173,19 +1170,19 @@
         <v>1997</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -1194,7 +1191,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1203,19 +1200,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="240" x14ac:dyDescent="0.25">
@@ -1223,16 +1220,16 @@
         <v>1998</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="225" x14ac:dyDescent="0.25">
@@ -1240,16 +1237,16 @@
         <v>1998</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="315" x14ac:dyDescent="0.25">
@@ -1257,16 +1254,16 @@
         <v>1998</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1275,7 +1272,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1284,19 +1281,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="285" x14ac:dyDescent="0.25">
@@ -1304,16 +1301,16 @@
         <v>1999</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1322,7 +1319,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1331,19 +1328,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="180" x14ac:dyDescent="0.25">
@@ -1351,16 +1348,16 @@
         <v>2000</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1369,7 +1366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1378,19 +1375,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="270" x14ac:dyDescent="0.25">
@@ -1398,16 +1395,16 @@
         <v>2001</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -1416,16 +1413,16 @@
         <v>2001</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -1435,7 +1432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1444,19 +1441,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="315" x14ac:dyDescent="0.25">
@@ -1464,16 +1461,16 @@
         <v>2003</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -1482,16 +1479,16 @@
         <v>2003</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -1501,7 +1498,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1510,19 +1507,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="375" x14ac:dyDescent="0.25">
@@ -1530,16 +1527,16 @@
         <v>2004</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -1548,16 +1545,16 @@
         <v>2004</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -1567,7 +1564,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1576,19 +1573,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="300" x14ac:dyDescent="0.25">
@@ -1596,16 +1593,16 @@
         <v>2005</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -1618,7 +1615,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1627,19 +1624,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="240" x14ac:dyDescent="0.25">
@@ -1647,16 +1644,16 @@
         <v>2006</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -1666,7 +1663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1678,19 +1675,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="75" x14ac:dyDescent="0.25">
@@ -1698,16 +1695,16 @@
         <v>1982</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1716,7 +1713,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1728,19 +1725,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="120" x14ac:dyDescent="0.25">
@@ -1748,19 +1745,19 @@
         <v>2012</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" t="s">
         <v>64</v>
-      </c>
-      <c r="F2" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1769,7 +1766,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1778,19 +1775,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="195" x14ac:dyDescent="0.25">
@@ -1798,19 +1795,19 @@
         <v>2018</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1819,7 +1816,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1828,19 +1825,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="195" x14ac:dyDescent="0.25">
@@ -1848,16 +1845,16 @@
         <v>2019</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -1866,16 +1863,16 @@
         <v>2019</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -1884,16 +1881,16 @@
         <v>2019</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -1902,16 +1899,16 @@
         <v>2019</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -1920,16 +1917,16 @@
         <v>2019</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F6" s="2"/>
     </row>
@@ -1938,16 +1935,16 @@
         <v>2019</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -1957,7 +1954,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1966,19 +1963,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="165" x14ac:dyDescent="0.25">
@@ -1986,16 +1983,16 @@
         <v>2020</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -2004,16 +2001,16 @@
         <v>2020</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -2022,16 +2019,16 @@
         <v>2020</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -2041,7 +2038,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2050,19 +2047,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="165" x14ac:dyDescent="0.25">
@@ -2070,16 +2067,16 @@
         <v>2021</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -2088,16 +2085,16 @@
         <v>2021</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -2106,16 +2103,16 @@
         <v>2021</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -2125,7 +2122,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2139,39 +2136,39 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+      <c r="A2">
         <v>2022</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>186</v>
+      <c r="B2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" t="s">
+        <v>185</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>188</v>
+        <v>70</v>
+      </c>
+      <c r="F2" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2179,16 +2176,16 @@
         <v>2022</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -2197,16 +2194,16 @@
         <v>2022</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -2215,16 +2212,16 @@
         <v>2022</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -2233,16 +2230,16 @@
         <v>2022</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F6" s="2"/>
     </row>
@@ -2251,16 +2248,16 @@
         <v>2022</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -2269,16 +2266,16 @@
         <v>2022</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -2288,7 +2285,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2297,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2317,10 +2314,10 @@
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2328,10 +2325,10 @@
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2339,10 +2336,10 @@
         <v>2023</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2351,7 +2348,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2360,19 +2357,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2380,19 +2377,19 @@
         <v>2024</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2" t="s">
         <v>195</v>
-      </c>
-      <c r="F2" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2400,16 +2397,16 @@
         <v>2024</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2417,19 +2414,19 @@
         <v>2024</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" t="s">
         <v>200</v>
       </c>
-      <c r="D4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E4" t="s">
-        <v>201</v>
-      </c>
       <c r="F4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2437,16 +2434,16 @@
         <v>2024</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2454,13 +2451,13 @@
         <v>2024</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2468,13 +2465,13 @@
         <v>2024</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2482,19 +2479,19 @@
         <v>2024</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8" t="s">
         <v>204</v>
-      </c>
-      <c r="D8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" t="s">
-        <v>193</v>
-      </c>
-      <c r="F8" t="s">
-        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -2503,7 +2500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2517,19 +2514,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2537,16 +2534,16 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2554,19 +2551,19 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F3" t="s">
         <v>189</v>
-      </c>
-      <c r="D3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F3" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2574,19 +2571,19 @@
         <v>2025</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F4" t="s">
         <v>191</v>
-      </c>
-      <c r="F4" t="s">
-        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2595,7 +2592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2604,19 +2601,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="195" x14ac:dyDescent="0.25">
@@ -2624,16 +2621,16 @@
         <v>1983</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2642,7 +2639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2651,19 +2648,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="225" x14ac:dyDescent="0.25">
@@ -2671,16 +2668,16 @@
         <v>1984</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2689,7 +2686,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2698,19 +2695,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="255" x14ac:dyDescent="0.25">
@@ -2718,16 +2715,16 @@
         <v>1985</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2736,7 +2733,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2745,19 +2742,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="270" x14ac:dyDescent="0.25">
@@ -2765,16 +2762,16 @@
         <v>1986</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2783,7 +2780,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2792,19 +2789,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="225" x14ac:dyDescent="0.25">
@@ -2812,16 +2809,16 @@
         <v>1988</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2830,7 +2827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2843,19 +2840,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="90" x14ac:dyDescent="0.25">
@@ -2863,16 +2860,16 @@
         <v>1989</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2880,10 +2877,10 @@
         <v>1989</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2892,7 +2889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2904,19 +2901,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="105" x14ac:dyDescent="0.25">
@@ -2924,16 +2921,16 @@
         <v>1992</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="135" x14ac:dyDescent="0.25">
@@ -2941,16 +2938,16 @@
         <v>1992</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD6FA6E-CC69-4706-992D-8F02365F32E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6727814F-8043-495F-886D-CF731AB889E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="204">
   <si>
     <t>Year</t>
   </si>
@@ -601,9 +601,6 @@
   </si>
   <si>
     <t>Planning and Evaluation of Urban Bus Route Networks Based on Origin-Destination Information in A Multimode Environment</t>
-  </si>
-  <si>
-    <t>2008/81201</t>
   </si>
   <si>
     <t>https://media.licdn.com/dms/image/v2/C5103AQEdsBhjnc233g/profile-displayphoto-shrink_200_200/profile-displayphoto-shrink_200_200/0/1560254960329?e=2147483647&amp;v=beta&amp;t=NH0m6tvpm5uWPHOUe91O7fF8Cjl4-S4VuzNHp8vL8VQ</t>
@@ -1182,7 +1179,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1806,9 +1803,7 @@
       <c r="E2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>183</v>
-      </c>
+      <c r="F2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2129,6 +2124,7 @@
     <col min="2" max="2" width="23.42578125" customWidth="1"/>
     <col min="3" max="4" width="41.5703125" customWidth="1"/>
     <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2159,7 +2155,7 @@
         <v>146</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>139</v>
@@ -2168,7 +2164,7 @@
         <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2380,16 +2376,16 @@
         <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D2" t="s">
         <v>119</v>
       </c>
       <c r="E2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F2" t="s">
         <v>194</v>
-      </c>
-      <c r="F2" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2403,10 +2399,10 @@
         <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2417,16 +2413,16 @@
         <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D4" t="s">
         <v>121</v>
       </c>
       <c r="E4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2440,10 +2436,10 @@
         <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2457,7 +2453,7 @@
         <v>123</v>
       </c>
       <c r="E6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2471,7 +2467,7 @@
         <v>124</v>
       </c>
       <c r="E7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2482,16 +2478,16 @@
         <v>132</v>
       </c>
       <c r="C8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D8" t="s">
         <v>125</v>
       </c>
       <c r="E8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2540,10 +2536,10 @@
         <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2554,16 +2550,16 @@
         <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D3" t="s">
         <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2574,16 +2570,16 @@
         <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D4" t="s">
         <v>138</v>
       </c>
       <c r="E4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F4" t="s">
         <v>190</v>
-      </c>
-      <c r="F4" t="s">
-        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6727814F-8043-495F-886D-CF731AB889E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D1DD15-2FFF-43A8-956C-55E9A1685F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -52,11 +52,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="230">
   <si>
     <t>Year</t>
   </si>
   <si>
+    <t xml:space="preserve">Name of the Scholar </t>
+  </si>
+  <si>
     <t>Area of Research</t>
   </si>
   <si>
@@ -369,15 +372,9 @@
     <t>Performance Evaluation of Treated Bases</t>
   </si>
   <si>
-    <t>Kakara Sreekanth</t>
-  </si>
-  <si>
     <t>Fatigue and Rutting Studies</t>
   </si>
   <si>
-    <t>Thesis title</t>
-  </si>
-  <si>
     <t>Simulation Studies on Traffic Capacity of Road Systems for Indian Conditions</t>
   </si>
   <si>
@@ -603,6 +600,9 @@
     <t>Planning and Evaluation of Urban Bus Route Networks Based on Origin-Destination Information in A Multimode Environment</t>
   </si>
   <si>
+    <t>2008/81201</t>
+  </si>
+  <si>
     <t>https://media.licdn.com/dms/image/v2/C5103AQEdsBhjnc233g/profile-displayphoto-shrink_200_200/profile-displayphoto-shrink_200_200/0/1560254960329?e=2147483647&amp;v=beta&amp;t=NH0m6tvpm5uWPHOUe91O7fF8Cjl4-S4VuzNHp8vL8VQ</t>
   </si>
   <si>
@@ -664,13 +664,96 @@
   </si>
   <si>
     <t>Phd_Alumini/S2024/721005</t>
+  </si>
+  <si>
+    <t>Pavement Materials</t>
+  </si>
+  <si>
+    <t>K.V.R Ravi Shankar</t>
+  </si>
+  <si>
+    <t>Kakara Srikanth</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2022/Ramireddy Sushmitha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phd_Alumini/S2022/Kurre Sai Sahithya </t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2022/Kakara Srikanth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phd_Alumini/S2022/Kamatalam Mahaboob Peera </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phd_Alumini/S2022/Sarella Chakravarthi </t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2023/G.Shravan Kumar</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2021/J.Jaya Shankar</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2021/Prashanth Shekar Lokku</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2021/Utsav Vishal</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/2019/Poojari Yugendar</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2020/Syed Mubashir Hussain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phd_Alumini/S2020/Kamineni Aditya </t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2019/S. Srikanth</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2019/vmnaidu</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2019/Anil Modinpuroju</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Position </t>
+  </si>
+  <si>
+    <t>Current Position</t>
+  </si>
+  <si>
+    <t>Current Posoition</t>
+  </si>
+  <si>
+    <t>Thesis Title</t>
+  </si>
+  <si>
+    <t>Thesis Abstract</t>
+  </si>
+  <si>
+    <t>reight Transportation is an important infrastructural facility that contributes to the national economy by linking the industrial and agricultural production with consumption. Highways and Railways are the most important modes for the freight movement at regional level. Accurate estimation of the transportation demand for freight movement is a prerequisite for developing efficient transportation systems. While the planning of Railway system is institutionalized, the Highway sector, being a monopoly of private undertakings and individuals, is least organized and unplanned. In controlled economies such as India, the share between these two major modes is more or less predetermined on the basis of other policy vectors.
+While developing the Highway transportation system it is observed that there are no established procedures to either quantify the travel demands or develop a network that satisfies the present or expected desires. The review of literature around the world has revealed that the Highway sector, though neglected, has an important role to play for the movement of expensive consumer goods, packed products, perishable commodities etc., while the Railways has exclusive advantages for bulk commodity movement over longer distances. It is also observed that little literature is available for scientific estimation of the highway goods movement which is a vital input for system development.
+An attempt is, therefore, made in this study to develop the highway freight transportation demand models at regional level by considering the basic mechanism of freight movement. The excess production, excess consumption and spatial separation of the regions are found to be the most important controlling factors for the regional freight transfers. In this context delineation of regions plays an important role for estimating the inter-regional and intra-regional freight movement. In this study a hypothesis has been presented to delineate the transportation regions for India together with a detailed discussion on the division of study area into micro regions. Hyderabad Region with 10 districts in its hinterland has been chosen for detailed study in this work.
+A pilot study was organised for quantifying the economic, social, demographic and transportation characteristics and a Factor Analytic study has been undertaken to isolate the basic causal factors affecting the Highway travel. On the basis of the findings a hypothesis is proposed to model the Highway freight movement as a function of the causal variables embedded in the mechanism of freight movement.                                       Detailed surveys have been organised in the region for measuring the actual Highway freight transportation that is explained subsequently through the calibration of freight transportation models on the basis of the proposed hypothesis. These models were examined for their validity in respect of statistical goodness of fit as well as predictive ability in the region. They form basic tools for forecasting the future flows for four different horizon years and three anticipated growth options of the region.
+Having ascertained the capacity of the proposed hypothesis for estimating the highway freight movement, their application to the development of Highway network has been demonstrated. Its potential use in the terminal planning for the trucks near Metropolitan Area has been illustrated. The study, therefore, presents a procedure for the estimation of goods movement on 'Highway Systems' under the controlled economies and, therefore, serves as a valuable tool in 'Highway System' Planning.
+The limitations that still exist in the proposed methodology are then presented and scope for further research is identified.</t>
+  </si>
+  <si>
+    <t>sfdsdf</t>
+  </si>
+  <si>
+    <t>gchbcgc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -707,6 +790,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -729,7 +832,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -738,6 +841,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1019,49 +1128,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="4" width="42.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="3" max="5" width="42.28515625" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1980</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>7</v>
+        <v>228</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -1071,46 +1194,53 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1996</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F3" s="2"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1119,66 +1249,74 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1997</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="150" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1997</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>183</v>
       </c>
     </row>
@@ -1189,78 +1327,87 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="240" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="240" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1998</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="225" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="225" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1998</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="315" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="315" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1998</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>35</v>
+        <v>172</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1270,44 +1417,51 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="285" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="285" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1999</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>38</v>
+        <v>169</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1317,44 +1471,51 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="180" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="180" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2000</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>38</v>
+        <v>168</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1364,64 +1525,72 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="270" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="270" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2001</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1430,64 +1599,72 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="315" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2003</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="225" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="225" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2003</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1496,64 +1673,72 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="375" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="375" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2004</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="210" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2004</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1562,49 +1747,56 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="300" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="300" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2005</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F3" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1613,46 +1805,53 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="240" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="240" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2006</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1661,47 +1860,54 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="4" width="22.140625" customWidth="1"/>
+    <col min="3" max="5" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1982</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>108</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1711,50 +1917,57 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="45.5703125" customWidth="1"/>
+    <col min="7" max="7" width="45.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2012</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>64</v>
+      </c>
+      <c r="G2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1764,46 +1977,55 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="195" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="195" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2018</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F2" s="3"/>
+        <v>158</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>182</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1812,136 +2034,160 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="40.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="195" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="195" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2019</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2019</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" ht="150" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2019</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2019</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" ht="165" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2019</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" ht="180" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="180" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2019</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F7" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1950,82 +2196,109 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="165" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="G1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+    </row>
+    <row r="2" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
         <v>2020</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>2020</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="195" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="E3" s="8"/>
+      <c r="F3" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+    </row>
+    <row r="4" spans="1:10" ht="270" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
         <v>2020</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B4" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" ht="285" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>2020</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="E4" s="8"/>
+      <c r="F4" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2034,82 +2307,100 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="165" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="G1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
         <v>2021</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>2021</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="150" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="E3" s="8"/>
+      <c r="F3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" ht="240" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
         <v>2021</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B4" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" ht="240" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>2021</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="2"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H4" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2118,162 +2409,184 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.42578125" customWidth="1"/>
-    <col min="3" max="4" width="41.5703125" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="41.5703125" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2022</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
         <v>184</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2022</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2022</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2022</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2022</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2022</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>2022</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>106</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" t="s">
+        <v>209</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2282,60 +2595,82 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="32.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>113</v>
+      </c>
+      <c r="C3" t="s">
+        <v>204</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="F3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2023</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="F4" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -2345,148 +2680,154 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
         <v>195</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" t="s">
         <v>193</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2024</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" t="s">
         <v>193</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2024</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" t="s">
         <v>198</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" t="s">
         <v>199</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2024</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" t="s">
         <v>201</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2024</v>
       </c>
       <c r="B6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2024</v>
       </c>
       <c r="B7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2024</v>
       </c>
       <c r="B8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
         <v>202</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" t="s">
         <v>191</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>203</v>
       </c>
     </row>
@@ -2497,88 +2838,95 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="75" customWidth="1"/>
-    <col min="5" max="5" width="66.140625" customWidth="1"/>
-    <col min="6" max="6" width="32.28515625" customWidth="1"/>
+    <col min="4" max="5" width="75" customWidth="1"/>
+    <col min="6" max="6" width="66.140625" customWidth="1"/>
+    <col min="7" max="7" width="43" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2" t="s">
         <v>191</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
         <v>187</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F3" t="s">
         <v>189</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2025</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" t="s">
         <v>192</v>
       </c>
       <c r="D4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F4" t="s">
         <v>189</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>190</v>
       </c>
     </row>
@@ -2589,44 +2937,51 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="195" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="195" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1983</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2636,44 +2991,57 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="225" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1984</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>227</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2683,44 +3051,51 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="255" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="255" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1985</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>111</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2730,44 +3105,51 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="270" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="270" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1986</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>181</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2777,44 +3159,51 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="225" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="225" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1988</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>180</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2824,59 +3213,66 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+    <col min="3" max="5" width="21.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1989</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1989</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2886,64 +3282,72 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1992</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1992</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>10</v>
+        <v>176</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Downloads\mainnn\NITW-Transportation-Division-main\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D1DD15-2FFF-43A8-956C-55E9A1685F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12150" firstSheet="12" activeTab="20"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -52,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="282">
   <si>
     <t>Year</t>
   </si>
@@ -345,9 +344,6 @@
     <t>Ramireddy Sushmitha</t>
   </si>
   <si>
-    <t>Signalized Intersection Capacity Analysis</t>
-  </si>
-  <si>
     <t>Pallavi Gulivindala</t>
   </si>
   <si>
@@ -549,9 +545,6 @@
     <t>Development of volume-based trip generation models and combined distribution and assignment model with a feedback mechanism for simplified urban transportation planning</t>
   </si>
   <si>
-    <t>Modeling urban form and structure using transportation planning techniques for small and medium cities</t>
-  </si>
-  <si>
     <t>Evaluation of Flexible Pavement Performance with Reinforcement and Chemical Stabilization of Expensive Soil Subgrade</t>
   </si>
   <si>
@@ -576,9 +569,6 @@
     <t>Urban Goods Flow Characteristics and Demand Estimation</t>
   </si>
   <si>
-    <t>Behavioral Mode Choice Models for Intercity Rail-Road Passenger Travel</t>
-  </si>
-  <si>
     <t>Urban Traffic System Model for Managing Traffic</t>
   </si>
   <si>
@@ -591,9 +581,6 @@
     <t>Development of Methodology for Optimal Selection of Civil Engineering Parameters in Railway Projects</t>
   </si>
   <si>
-    <t>B.U. Rama Rao</t>
-  </si>
-  <si>
     <t>Community Response to Components of Urban Transport for Work Journeys Through Mode Choice Models</t>
   </si>
   <si>
@@ -666,9 +653,6 @@
     <t>Phd_Alumini/S2024/721005</t>
   </si>
   <si>
-    <t>Pavement Materials</t>
-  </si>
-  <si>
     <t>K.V.R Ravi Shankar</t>
   </si>
   <si>
@@ -735,7 +719,431 @@
     <t>Thesis Abstract</t>
   </si>
   <si>
-    <t>reight Transportation is an important infrastructural facility that contributes to the national economy by linking the industrial and agricultural production with consumption. Highways and Railways are the most important modes for the freight movement at regional level. Accurate estimation of the transportation demand for freight movement is a prerequisite for developing efficient transportation systems. While the planning of Railway system is institutionalized, the Highway sector, being a monopoly of private undertakings and individuals, is least organized and unplanned. In controlled economies such as India, the share between these two major modes is more or less predetermined on the basis of other policy vectors.
+    <t>In this modern world where everything is becoming smart, there is a great need for the trip forecasting to catch up with the transportation planning. Cities across the world are growing in terms of their urban area and in number. Every city has its travel demand based on its socio-economic and land use characteristics. Number of trips generated in a day per person in a city is considered as Trip Rate. In this work, trip generation rate, Per Capita Trip Rate are synonymous with the word Trip Rate.
+Present transportation planning models are prepared for estimation of cross-sectional data, hence are referred to as cross-sectional demand models. These works have demonstrated the theoretical and practical significance of developing travel demand models based on panel data (Kitamura 1988; Kitamura 1990; Meurs 1990; Goodwin et al. 1987; Michael et al. 2002 and 2006). Residential trip rates are underreported by the residents, especially trips that are not made with consistency. Retail trips are probably underreported than trips for work purpose (Reid 1982; Kumar et al. 1993). Modelling of small urban regions using single internal trip purpose was carried out by Anderson (2001).
+Yam et al. (2000) formulated a multi linear regression model to assess traffic generation to high density, large scale, multi-story public residential accommodation estates in Hong Kong. The cross-classification analysis is more universally adopted (McNally 2000) with applications in passenger travel (Guevara et al. 2007) and also freight (Bastida et al. 2009). Even though, there were various attempts in the field of trip generation, quick estimates of trip generation rates for developing countries has become a field of rare focus. Keeping this in view, trip generation rate estimation process is studied for a developing country like India. Trip generation studies include Cross-classification, Linear Regression, count data and neural network techniques. However, there is requirement for advancement in this matter. Instant estimation of trip generation rates for developing countries is required. Hence, this research work is taken up.
+Parameters related to socio-economic status and land use were considered in the study. It is found that trip rate varies with power function, trip length varies linearly with respect to population of the city. Both these parameters vary exponentially with population density. For combined data, City Population and Industrial Area (%) are found to be having a logical sign,and population parameter is found to be most significant in the trip rate model. Cities were categorized based on population and area. Cities are categorized based on the population as CP1 (Population &lt;10 Lakhs), CP2 (Population: 10-40 Lakhs) and CP3 (Population &gt;40 Lakhs). Cities are categorized based on the Area as CA1 (Area &lt;300 sq.km), CA2 (Area: 300-1000 sq.km) and CA3 (Area &gt;1000 sq.km). Regression models were developed for these categories. Regression models were developed for combined cities and categorized cities data. As multiple parameters are available, the Principal Component Analysis (PCA) is used to reduce the dimensionality. Combined data (Socio-economic and Land-Use) is processed to get principal components. Better regression models were developed for the data of all the cities with principal components.
+Data was processed through Artificial Neural Network (ANN) for trip rate prediction. For accurate prediction of trip rate, ANN has been applied. The Artificial neural network analysis with same data (Socio-economic and Land-Use) was employed. Performance of these models using ANN is found to be better than the performance of corresponding regression models. Various sets of Nomograms were developed to assess the trip rate using different input variables for all the city categories considered. PyNomo, sub-module of Python program was used for developing Nomograms. For all categories of cities, various Nomograms were developed with single and two input variables.
+Trip rate increase with population size and this increase is steep up to a population of 40 lakhs. There is an abrupt change around 40 lakhs and increase in trip rate is found to be nominal, beyond 40 lakh population. The trip length of the city increases with the increase in population size. Regression analysis revealed that city population is found to be the significant variable in explaining Trip Rate. The training function TRAINLM has performed perfectly using the Feed Forward Back Propagation algorithm producing a predicted trip rate value. Principal Components with Artificial Neural Network arrangement models yielded superior correlation coefficient.</t>
+  </si>
+  <si>
+    <t>The mixed traffic behavior on multilane highways remains scarcely explored. Most of the studies on multilane traffic flow pertain to homogeneous traffic scenarios. These studies have very limited applications to mixed traffic conditions due to their incapability in satisfactorily explaining the complexities of mixed traffic behaviour. Also, the available literature on mixed traffic mainly deals with the single and two-lane roads and there is no comprehensive study for understanding traffic flow behavior on multilane highways. IRC: 64-1990 also provides detailed guidelines for capacity of single-lane, intermediate lane and two lane rural roads; leaving multi-lane highways almost unattended. Due to lack of standard codes for multilane highways in India, it is difficult for traffic engineers, policymakers and planners to take accurate decisions with respect to planning, design, and operations of these highways. The present research work aims at investigating the mixed traffic flow behaviour on highways for varying conditions of traffic volume. To understand the traffic flow behavior on four-lane divided highways under mixed traffic conditions, the arrival patterns of vehicles, time headway characteristics, speed characteristics, lateral placement of vehicles and overtaking behavior were analyzed.
+The aim of the present study is to develop more appropriate models for estimating the passenger car units of different vehicle types on multilane highways, considering the limitations of available methods. Present study describes a modified methodology for estimation of PCU value of subject vehicles that includes the time headway as influencing parameter. The approach used in the present study is inspired from the method of dynamic PCU estimation where a PCU is expressed as the ratio of speed ratio and area ratio of standard cars to the subject vehicle type. Unlike dynamic PCU method, this method includes time headway factor for PCU estimation. The method was found to be more realistic and logical as it provides relatively higher values of PCUs than those obtained from dynamic PCU method.
+Multiple non-linear regression (MNLR) method is proposed for estimation of equivalency units for vehicle types by developing speed models based on multiple non-linear regression approaches. The equivalency units estimated by using models are found to be realistic and logical under heterogeneous traffic flow conditions. The PCU values estimated by the multiple non-linear regression method are compared with and found to be relatively higher values than the values obtained by the dynamic PCU method. The accuracy of the models is checked by comparing the observed values of speed with estimated speeds. The multiple non-linear regression approach is also used for estimating the equivalency units on six-lane divided highways.
+The primary limitations of field data arises due to practical difficulties in conducting extensive field experiments under wide variations of traffic flow parameters, non-availability of required field conditions, difficulty in experimenting with individual components in isolation, etc. As a solution to these practical problems, computer simulation has been proved to be a powerful tool in replicating complex traffic systems which allows experimentation to the basic traffic flow system. For the simulation VISSIM microscopic simulation tool is used and data analysis is performed by considering individual parameters and performance measures like speed, volume and random seed number. Statistical tests have been performed to check the sensitivity of the different simulation parameters and calibration is done using trial and error method and optimization is performed using solver function. The maximum simulated flow rate was found with default values as 4599 veh/hr, and with calibrated values is 5147 veh/hr which is close to the target capacity 4958 veh/hr as obtained using field composition. Calibrated values of CCO and CC1 and CC2 parameters are found as most optimised values to achieve target capacity. Finally, validation of calibrated parameter values was also performed on other section of a multilane highway which have shown satisfactory results.
+Lane changing is a very complex maneuver which can be studied through microscopic and macroscopic measures. Calibrated VISSIM model was used for generating traffic flow data to obtain the essential parameters. Lane change behaviour is analysed with homogeneous vehicle type traffic on four-lane, six-lane and eight-lane divided highway sections through VISSIM simulation model. The study finds the number of lane changes depends on traffic volume as well as on number of lanes provided for a direction of travel. Lane change data was correlated with traffic volume and third degree polynomial trend was found to be fitted on each type of simulated highway sections. Maximum number of lane changes and lane change at capacity level of volume are also quantified on simulated sections of four-lane, six-lane and eight-lane divided highways. It is found that no more number of lane changes is observed in all simulated sections when traffic volume reaches to maximum capacity. The relationship between capacity per lane and number of lane changes is established which shows capacity decreases with addition of number of lanes.
+Level of service concept is applied in the present study to estimate the passenger car unit (PCU) value of each vehicle type at different level of service and different percentage share. Calibrated VISSIM model was used to simulate traffic conditions for the development of PCU models. The PCU value of each vehicle type at different level of service and different percentage share was found for the development of the models. The accuracy of the models is checked by comparing the obtained PCU values with PCU values estimated by dynamic PCU method. PCUs of different vehicle types at six lane and eight lane divided highways are also estimated. The effect of number of lanes on PCUs was studied, and it was observed PCU of each vehicle type decreases with increase in the number of lanes and at different level of service. Artificial neural networks (ANN) and Artificial neuro fuzzy interface system (ANFIS) models are also developed for estimating PCU values of subject vehicle types with respect to passenger cars. The PCU estimated from different approaches are compared statistically in order to justify the best approach with the same set of input variables.</t>
+  </si>
+  <si>
+    <t>In the process of developing Level Of Service standards on urban roads under varying road widths and mixed traffic conditions, the concept of Group is introduced. A simulation model entitled "Urban Traffic System Model (UTSM)" is constructed by integrating various processes that depict the complex vehicle behaviour.
+The traffic on urban roads carry variety of fast and slow moving vehicles. Amongst the fast moving vehicles there are four wheelers consisting of cars and busses, two/three wheelers consisting of scooters, auto rickshaws and other two/three wheeler slow moving vehicles consisting of cycles and cycle rickshaws. All these vehicles share the same right of way. The operational characteristics of these vehicles differ from each other quite considerably resulting in unique dynamic relationship among themselves.
+Homogeneous traffic moves in file formation on lanes and this discipline is achieved by the size of the vehicle and other related characteristics. The research works carried out on mixed traffic followed the same lane concept to develop various relationships governing the flow of traffic. However, it is observed that on most of the urban streets in India, non-standard undemarcated lane widths exist resulting in complex vehicle movements. As a result, the standard approaches to quantify concentration, speeds etc. do not appear to describe the detailed situation.
+IRC draft standard addresses this problem on lines of Highway capacity manual of USA wherein Equivalent Passenger Car Units are suggested to convert the mix of vehicles into a uniform Car units. Conceptually, this approach is valid in homogeneous situations, where only Trucks, Buses and other recreational fast moving vehicles are present in smaller proportion in relation to Cars. Utilisation of the same concept under mixed traffic conditions may have limited usage. This warrants for an indepth study of the behaviour of the urban traffic under mixed mode situation and to suggest a more suitable parameter to describe the traffic flow.
+Since this complex system is difficult to be modelled analytically digital simulation is resorted to. Field studies have been conducted using manual, photographic and videographic techniques to capture traffic data in the city of Hyderabad. Analysis of the data has enabled to describe headway, lateral positioning, speeds, vehicle compositions etc. and to formulate and develop several component models. Generation of mixed traffic stream, positioning of the mix of vehicles across the road, decision making based on information processing criteria, polynomial acceleration, deceleration models are some of the component models developed. All of them are logically integrated to form an operational system to represent urban traffic stream  termed as "Urban Traffic System Model" (UTSM). UTSM has been coded in FORTRAN 8X language for processing.
+UTSM is designed to address road widths varying from 3.5 meters to 6.5 meters at 1 meter increments, and for traffic volumes varying 200 vph to 2000 vph. UTSM receives the input data from field study and simulates the situation for any of the above said configurations. The model has been field validated by comparing the output from the program with corresponding field data. The data is related to micro and macro aspects of traffic. There is general agreement in field and simulated results. This strengthens a feeling that the model is capable of replicating mixed mode behaviour on urban roads.
+The model has been used extensively for experimentation. The composition of four wheelers is varied to study the traffic behaviour for varying volumes and road widths. The composition of mix is also varied to contain four wheeled traffic from 10-50% of the total flow.
+The results obtained are tabulated and used as a basis for developing standards for urban traffic. In the process of developing standards the concept of lane behaviour is proposed to be replaced by road width criteria and positioning of vehicles by risk criteria. Vehicles in terms of mixed volumes are considered instead of passenger car units. Information processing is employed for decision making in tracing vehicle manoeuvers. A new parameter  called 'Group' is introduced to suggest the Level of Service enjoyed by the mixed traffic on a given stretch of road.
+It is hoped that the approach presented in this research, for generating the mixed traffic flow by Convolution Theory, rationalising the categorisation of vehicles based on their behaviour, application of Information Theory for decision making, refinement in acceleration/deceleration modelling, replacement of the lanes by road width and finally the introduction of Group as parameter to describe LOS instead of speeds of vehicles, will present a better insight in managing the urban traffic.</t>
+  </si>
+  <si>
+    <t>Bus Transportation plays a vital role in providing mobility to urban commuters. With scarce resources at hand the transport operations find it difficult to provide adequate services to these commuters during rush hours. There is a need to utilize the existing fleet of buses to derive full benefits and efficiency of performance. The efficiency of bus transportation depends upon the network of routes chosen and frequency of operation on these routes. At present planning of routes and scheduling of buses is being attempted based on experience and intuition. With the rapid expansion of city new routes are added, mostly as extensions, and buses are distributed based on perceived demands. Alternative networks and scheduling on the routes are not evaluated. Thus a need is felt to have a rational planning methodology for bus route network design in an urban area.
+Literature survey has revealed that although rational approaches are available on planning single routes, no such methods exist for network planning and they are mostly based on experience. Some efforts are being made in the maximization of net user benefits subjected to certain constraints but generally it has been observed that the O-D matrix is not considered and the planning is done without recognizing the changes brought with the changes in the level of services offered by its own mode as well as competing modes. These factors are to be incorporated in planning.
+In order to improve existing procedures for bus route network planning a methodology is proposed consisting of four submodels as mentioned below:                                                                                                                                                                                                                     Trial Network Generating Model (TNETGEM)
+Mode Split Probability Model (MOSPROM)
+Bus Travel Demand Estimation Model (BUSTDEM)
+Trial Network Performance Evaluation Model (TNETPEM)
+In Trial Network Generating Model (TNETGEM) traffic zones are to be classified as activity nodes, transition nodes and residential nodes based on employment, population, trip production and trip attraction characteristics. Routes are generated in accordance with the details presented and a trial network is prepared. It is then consolidated in the light of the desire line diagram and the existing route network experiences. Few such trial networks can be generated. In Mode Split Probability Model (MOSPROM) population is divided into four groups namely car owners, scooter owners, cycle owners and no vehicle group. Mode split probability coefficients for these vehicle owning groups are found Using Multinomial Logit Model (ULOGIT). In Bus Travel Demand Estimation Model (BUSTDEM) the initial fleet size requirement is calculated based on the passenger kilometre requirement of the network and the buses are distributed on various routes proportional to the trips. Random allocation is also possible. Care is taken to see that equal headways are maintained in the main corridors. Bus patronage is then estimated using ULOGIT coefficients on the trial networks generated in TNETGEM. In Trial Network Performance Evaluation Model (TNETPEM), the performance of the network is evaluated both in the view of operator as well as the public. If the performance is not in accordance with the objectives, then the policy is changed either in terms of network or frequency of buses or both till satisfactory results are obtained. Detailed flow charts depicting the sequence of operations in each submodel and for the entire methodology have been presented.                                                                                                                                                                                         Relevant computer programmes are presented in FORTRAN language to make the methodology operational. They include, O-D Matrix Estimate Programme, ULOGIT Programme, TNET-55 Program., TNET-60 Programme and Main Package interconnecting the four submodels.
+In order to show that the methodology is operational data was collected for Warangal City from 2107 houses through home interview survey. The data collected for an individual trip maker are the trip details, socio-economic condition and location information, Time, cost, and distance matrix from zone to zone along with peak hour fraction is also collected. Data is also prepared for disaggregate mode split model calibration. The proposed methodology was calibrated and operated upon using this data.
+First of all the Warangal city traffic zones are categorised into activity, transition and residential zones. The individual routes are then categorized as corridor routes, activity routes and residential routes. Four trial bus route networks are then developed for Warangal city. Mode split Model has been calibrated and co-efficients thus obtained for various vehicle owning groups have been utilized for bus patronage estimation and performance evaluation. Four route networks with twenty two alternative frequency of operations have been tried and the best network and the best frequency of operation has been identified for implementation based on performance indicators. The sensitivity analysis for Mode Split co-efficients has also been carried out. On the basis of this exercise several conclusions have been drawn and limitations and scope for future work have been presented.</t>
+  </si>
+  <si>
+    <t>B.V. Rama Rao</t>
+  </si>
+  <si>
+    <t>B Someswara Rao</t>
+  </si>
+  <si>
+    <t>Traffic safety evaluation at uncontrolled intersections</t>
+  </si>
+  <si>
+    <t>https://www.nitw.ac.in/CIVDeptAssets/images/phd25.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The traffic stream in India as in other developing countries consists of two distinct categories of vehicles namely, fast moving vehicles such as cars, buses, trucks, autos, motor cycles and slow moving vehicles like cycles, cycle rickshaws and bullock-carts. The static and dynamic characteristics of these two types of vehicles vary very widely. Most of the times the same right of way (road width) is used for the movement of both types of vehicles.
+Current literature on analysis of traffic stream conditions, though comprehensive in itself, does not deal with specific problem of determining the carrying ability of the road under mixed traffic operating conditions. In this study the term mixed traffic is used to denote a stream which consists of both slow and fast moving vehicles while this term in the context of developed countries is used to denote the percentage of truck traffic in the passenger car stream.
+The Highway Capacity Manual, U.S.A., an authoritative document on the subject is silent on these aspects of mixed traffic. The effect of two-wheelers like scooters and motorcycles and presence of other slow moving vehicles in the stream are not considered in the Manual, and therefore, its application under mixed traffic conditions experienced by developing countries is very limited, if not altogether misleading.                                                                                                                                        The fact that very little literature is available in this regard suggests the need for an indepth study of highway capacity under mixed traffic conditions. The aim of this research work is, therefore, to establish the procedure to obtain the capacity of a road system under mixed traffic operating conditions.
+The behaviour of the traffic being very intricate, neither a mathematical model nor a physical model is amenable for carrying out experimental studies. But digital simulation models are better suited for studying traffic systems as they are more efficient, economic and flexible. Therefore, the obvious choice of the model under the more complex interactions of a number of classes of vehicles in the mixed traffic stream, is the digital simulation approach. Thus this research addresses itself to "Simulation studies of traffic capacity of Road system for Indian conditions."
+The research work is broadly divided into four phases.
+Development of component models
+Integration of the components into an operational system
+Validation of the performance of the model
+Application of the model to study mixed traffic operations.
+In order to make the model a realistic one, under mixed stream conditions, field studies have been conducted at Hyderabad and Warangal to determine the field behaviour of the stream. From the data obtained on the field a number of mathematical and  logical algorithms has been developed as component models for the simulation.
+Adoptability of lateral clearance for overtaking manoeuvres, continuity of action in following the lead vehicle, probability of overtaking a bunch of vehicles, safe minimum distance adopted by drivers and the random behaviour of drivers, are some of the component models developed.
+After development, the component models are integrated to form an operational system which has been coded in FORTRAN IV language for dynamic processing on an IRIS-55 high speed computer. Three different models, MORTAB I, MORTAB II and MORTAB III, for the three highway systems, namely, single-lane one-way, two-lane one-way and two-lane two-way, respectively are developed. The computer program consists of one driver program and twenty sub-routines. The models are capable of incorporating eight different types of units simultaneously in the logic. The models have been structured as general purpose ones capable of utilising any input data arising from mixed operations on highway sections of the above three types. The performance of the models has been validated both at micro and macro levels by comparing the output information from the model with the corresponding field data. The results have indicated that the models are capable of replicating the mixed traffic behaviour in a satisfactory manner. About 20 hours of IRIS-55 high speed computer time was utilised for development and validation of the three simulation models.                                                                                                                                                                                                             After the formulation of the models, they are extensively used to develop traffic stream models, and to obtain the operating conditions of different units in the stream, at various volume levels and percentage combinations of slow and fast moving vehicles. Experimentation with the models encompass, at one extreme only passenger cars in the stream and hundred per cent slow moving vehicles at the other end, and, in between, many intermediate permutations and combinations of the two groups are used.
+The analysis of the results from the experiments, are made use of to provide the necessary theoretical inputs for developing capacity standards as well as the level of service concept under mixed stream operations. The value of such an exercise is specially evident in the fixation of capacity standards and service volumes in terms of mixed vehicles per hour rather than in terms of passenger car units followed by contemporary research in the field of highway capacity. A new concept of design vehicle unit is brought in to take care the dissimilarities in operation prevalent in India and other developing countries. Thus for any vehicle, the equivalent design vehicle unit is found to be a varying standard for the specified level of service under different percentage slow moving vehicles in the stream.
+This thesis advances the hypothesis that the simulation approach, is appropriate, to study complex mixed traffic operations existing on Indian road system.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority type intersections are quite numerous in our urban network. The guidelines regarding the design and operation of such intersections are not established to this date due to lack of relevant literature and prevailing mixed traffic conditions. This prompted the author to study in-depth the mixed traffic behaviour at the priority approaches as well as the intersection proper in order to evolve design and operational criteria.
+As the conventional approaches have lot of limitations in the treatment of the complexities of the mixed traffic behaviour, digital simulation techniques has been adopted in this research. This technique is ideally suited to study the behaviour of mixed traffic consisting of fast and slow moving traffic, with wide variation in static and dynamic characteristics while sharing the same right of way.
+Some of the field studies are conducted in the cities of Hyderabad and Surat for the priority intersections in order to build the component models for headways, speeds, gap acceptance and passing and overtaking manoeuvres which form the vital input for the simulator MITISS (Mixed Traffic Intersection Speed Simulation) and SIMPRI (Simulation of Priority Intersections).
+Digital simulation technique adopted in this work has been programmed in FORTRAN-IV language keeping in view of its wide acceptability. In order to save the computer time and to have microlevel processing of the individual vehicles, the event scanning for SIMPRI and unit time scanning for MITISS have been adopted.
+MITISS is developed to study the mixed traffic behaviour at priority approaches. With the help of this simulator, flow-speed-density relationships are developed. It also provides the mixed speed models as input to SIMPRI which is meant for studying the traffic performance to establish the level of traffic quality at the intersection proper. Simulation models have been validated by some field studies and also data through relevant literature.
+Some of the important contributions to the study of priority intersection under mixed traffic conditions of this thesis are:
+i. The establishment of limits for the random process for the traffic condition existing.
+ii. Investigation of suitability of various statistical distributions for headways, speeds and gap acceptance.
+iii. Desirability of the use of Von-Karber's technique for the estimation of gap acceptance parameters.                                                                                                                                                                                                     iv. The choice of car following models for the mixed traffic under low volume conditions.
+Based on the study the following models and the concepts have been developed which will be of immense help for evaluating traffic quality at the priority intersections.
+i. Speed models for the mixed traffic.
+ii. Speed-flow-density relationship for traffic flow at priority approach.
+iii. The concept of "Approach Density Index" and its values for mixed traffic flow.
+iv. Mode-wise delay models.
+v. Service volumes for the priority intersection for various levels of service.
+vi. Equivalent passenger car units for the priority intersections.                                                                   </t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S1982/B.K. Katti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professor at Sardar Vallabhbhai National Institute of Technology Surat </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Origin - Destination Matrices are necessary for successful model building and analysis in the field of Transportation Planning at Urban and Regional levels. The standard procedures for obtaining these Matrices through Home Interviews, Roadside Interviews etc., are prohibitively costly techniques and considerable difficulties are experienced in their execution even at the scale of urban levels. When these are extended to the regional travel quantification, the job becomes much more complicated and sometime unmanageable. Researchers in the field of Transportation Planning have, therefore, turned their attention to obtain the O-D Matrices indirectly through inexpensive field information such as traffic volume counts on the links. The above approach is a typical reversal of the traditional travel demand estimation procedures.
+Gravity Formulation, Network Equilibrium, Information Minimization and Entropy Maximization are some of the techniques that are suggested to achieve this objective. Although considerable progress has been made on the theoretical aspects, predictive probability or confidence level of the results have not been established. In this thesis, it is proposed to develop an approach to estimate O-D Matrices at regional level, through link volume counts and demonstrate their capability by actual comparison with the O-D Matrix obtained through the conduct of traditional surveys. It is proposed to restrict the study to regional bus transportation, being the predominant mode of passenger travel, at the regional level.
+(The sequence of the model development is presented in nutshell through a flow chart.)
+The current research in the use of minimum information or maximum entropy is mostly confined to updating an old survey matrix to the present by the use of the current traffic volume counts. Apparently, this problem does not have any immediate significance to problems in Urban or Regional situations prevailing in developing countries. Except for some of the metropolitan cities traffic and transportation studies have not been initiated in many of the countries and hence the question of the existence of previous O-D estimates is completely ruled out. In such situation, in order to apply the concepts of minimum information or maximum entropy, realistic seed matrices have to be generated based on simple techniques to model the travel characteristics. The literature in the field so far accumulated is totally silent on this aspect. Even the suggestions for generating seed matrices based on random flow or uniform distributions for such conditions are purely of theoretical interest. Hence a methodology has been proposed in this thesis, which to a large extent alleviates the necessity to have a previous matrix for building up the current estimate. It is based on replicating the real travel through seed matrices, generated by models, which calibrate the link volumes. This method has several advantages over the earlier approaches by incorporation of socio-economic characteristics of the region into the model structure. By this technique purely empirical models of the current research are converted from their descriptive nature to predictive type.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        Since any O-D Matrix obtained through a synthesis of link volumes is only a conjecture, the proposed models that generate the seed matrices should replicate the travel patterns as close to the reality as possible. For this purpose two models namely FREXIV-U and FREXIV-C based on Gravity Formulation are proposed. A growth factor model named FRAFUT is developed based on existing O-D Matrix through traditional procedure with a view to provide future link volumes by actual assignment. UPDATE is a Programme based on information theory that UPDATES the existing O-D Matrix to the future, by means of a few selected link volumes generated through FRAFUT. These models are then applied to the city of Warangal for which the full scale O-D Matrix was available. The above models are loaded on the Warangal network to yield future link volumes. From the comparison of these volumes, it emerged that FREXIV-C Model is able to forecast trips comparable to those provided by FRAFUT. Further it is established that UPDATE Programme could be used to advantage only when appropriate links are selected and realistic seed matrices are supplied as input.
+Having established the capabilities of the models at Urban level, it is proposed to extend this to the regional scale. Two problems crop up which are less likely in urban situation. The first one is the   possibility of sparse O-D Matrix, while the second relates to the size of traffic zones creating distortions due to the assumptions in the concentration of trip productions and attractions at the centroids. A hierarchical travel decision was proposed to explain the sparse matrices. The concept of nodes in zones was introduced to reduce the likely distortions due to the assumption of trip interchanges between zone centroids to zone centroids.
+While the trips can be produced at several nodes within zones there is a possibility of trips being attracted to only a few selected centres in the zones. In order to account for this, two more hypotheses were, therefore, proposed. The first assumes that interzonal attraction trips from various nodes of other zones are routed through zonal centroids. While in the second the nodes in a zone are independent in attracting the trips.
+Based on these two hypotheses, two groups of models namely ZIPTAC/ZODIAC and NIPTAC/NODIAC are developed for estimation of O-D Matrix from link volume counts. ZIPTAC and NIPTAC are for link volume forecasting under gravity formulation while ZODIAC and NODIAC are for estimating O-D matrices based on information theory which use the parameters of calibration of ZIPTAC and NIPTAC respectively. A subroutine CHECK  specially designed to monitor the hierarchical trip interchanges in a regional travel is the key in these model developments.
+In order to apply these packages transportation planning regions had to be defined in the framework of national transport policy. While the concern of the nation are of providing mobility, connectivity and accessibility, appropriate planning regions to handle these functions are to be identified. As transportation is a spatial flow interaction, the regions delineated for transportation planning must be functional and not homogenity based. Using the concept of CITY REGION and quantification of spatial flow interactions, 8 Macro-Regions and 24 Meso-Regions are identified for India. One such meso-region demarcated for this study is the region around Hyderabad.
+The process of delineation of zones (Micro-Regions) within a meso-region is problem specific. These zones define the Origins and Destinations between which the trips are to be estimated for planning the connectivity. Based on Factor Analysis of causal variables, locational aspects of urban centres and bus depots etc., 26 zones are delineated in the Hyderabad Region for estimating the interzonal passenger travel by bus.                                                                                                                                                                                                                                                                                                                                      For validating the packages, detailed traffic surveys are conducted at 14 bus depot locations and 64 Cordon Count Stations (Zonal interfaces on the Network) spread over the study region thereby obtaining actual O-D Matrix for 8 zones and sufficient traffic volume counts for model calibration and validation.
+A detailed study of the travel characteristics revealed that there exists a relationship between the influence distance of the nodes and the service facilities existing in them quantified in the form of Rank Scores. The above distance is termed REACH. This relationship is one of the inputs to the packages.
+ZIPTAC/ZODIAC and NIPTAC/NODIAC packages are then calibrated with the link count data collected from traffic survey and a detailed statistical validation is performed to compare the conjectural matrices generated with the actual O-D Matrix. For this purpose a computer programme called CODIAC is specially developed.
+On the basis of comparison through CODIAC and with Direct Demand Model calibration it is established that ZIPTAC/ZODIAC package can give matrices which are close to the actual bus passenger O-D Matrix at the regional level, thus considerably reducing the conjectural estimates to a manageable number. It is felt that in practical situations the final selection
+of the best O-D Matrix among ZIPTAC/ZODIAC estimates could be effectively tackled by a rough judgement on the part of the user agency.
+Based on the findings of this research a summary pro-
+cedure for the ready application of ZIPTAC/ZODIAC models is presented and its application to route rationalization, fleet estimation, terminal planning by the State Road Transport Organisations are recommended. Some research alternatives for future work in this field are suggested in the light of the limitations of the study.                                                                                                                                                                           </t>
+  </si>
+  <si>
+    <t>ROAD User benefits under prevailing traffic and road conditions in India are quantified and their application to highway project appraisals through an algorithm is presented in this Thesis.
+FOR a developing country like India, transport is an important infra-structure which affects economic growth. Road transport, as one of the principal modes, is poised for a rapid development in the coming years. Roads play an important role in transporting passengers and goods, bringing the country's numerous villages within easy access and achieving agricultural, industrial and social growth. The country's road system has not  been developed adequately and suffers from many serious deficiencies. In the future years, large amounts are likely to be invested on constructing new roads and improving the existing ones. At present the highway engineer in India relies on ad-hoc and tentative norms while recommending schemes for improvement and bases his judgement on the initial cost of construction. In this process, other important components such as main-tenance cost and cost borne by the road user are dis-regarded, thus very often leading to wrong choice of schemes.
+NON-RECOGNITION of the total cost concept in highway planning has resulted in wastage of resources of the
+country. Fuel is one of them. A rational method of selecting the improvement strategy through economic
+analysis is urgently needed.
+THOUGH the subject of economic analysis has developed to a higher level of sophistication abroad, the models of those countries cannot be applied directly to  India. This is because of the heterogeneity of the traffic on Indian roads, lower standard of roads due to scarcity of resources, and stage construction practices. This establishes the need to quantify road user benefits and develop an appropriate methodology for economic appraisal of highway schemes by incorporating the peculiar conditions prevailing in India so that the available resources are utilised most efficiently.
+THE present investigation addresses itself to the quantification of road user benefits and development of a methodology for economic analysis of highway schemes in India. A large number of models, tables, graphs and equations are developed and presented for use in highway project appraisals. The data from the Road User Cost Study has been utilised wherever necessary for the development of models for predicting road user benefits, which form an important input into the economic analysis procedure.
+WARRANTS are developed for road improvement policies for which there are only ad-hoc norms at present. These improvement policies include selection of pavement surfacing types, pavement widths, maintenance strategies, widening two-lane roads to three-lanes, construction of bypasses and gradients for rural roads. The application of the results of the present work in highway planning is thereby illustrated.
+ROAD transport operators in the country at present determine their passenger fare and freight rate structure based on their previous experience. This is often unrelated to the roadway conditions. The vehicle operating cost models that have been developed have been used to determine accurately the economic fare and freight rate structure applicable under the varied road conditions in the country.
+THE economic analysis methodology developed and the vehicle operating cost models formulated have been tested by applying them in case studies of certain selected National Highway Schemes. This has demonstrated the potentialities of the methodology developed in highway project appraisal.
+THE study presented here is a useful tool to examine the economic viability of highway projects and to rank them in the order of their attractiveness. The investigations have yielded tables, graphs and equations to predict road user benefits with ease.
+THESE findings are, however, applicable to rural areas and need further extension to urban environment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urbanisation, poor spatial planning and easy availability of automobiles have resulted in flooding of urban streets with individual modes of transport of different sizes and speeds. Consequently the urban areas are facing traffic congestion, hazardous situations, environmental pollution and above all increased fuel consumption draining the scarce foreign exchange resources. A way to mitigate these problems is to plan the public transport systems based on the desires of the community of the urban travellers, that induce higher patronage to Public Transport, enabling to reduce the number of vehicles on the streets. To effectively translate this objective into practice, the identification of the desired levels of service at various stages or segments of travel by Public transport is necessary for efficient planning of the system.                                                                                                                                                           The transport components that discourage the use of public transport are walking, waiting, travelling in a crowd and slow speeds. Nevertheless travel by an individual mode also has certain deterrent factors such as higher journey costs, driving through congested roads and exposing to danger of accidents. Thus a trade off can exist between the transport components of public and individual modes. The process of comparing the components of all alternative and competing modes form the mode choice process of the Urban Transportation Planning Process. A review of related works carried out in the country indicate that the transport components considered are only total journey time and cost, and have several draw backs. Considering the deficiencies, an approach that maps the community desires and wants for quantifying the responses to the public transport usage has been proposed. Travelling public of urban areas have been grouped to, 'public transport captive', 'public transport choice', 'own mode captive' for identification of choice of transport. Establishing the importance of work journeys, transport components for the journeys have been identified and defined through quantifiable terms. Observing that the basic property of Multinomial Logit Model gets violated under mixed mode conditions prevailing in urban areas of the country and realising that a sequential decision making process is involved, Sequential Binary Mode choice models have been suggested. The formulated models have been calibrated using the travel data of Greater Bombay, which has an environment for exercising mode choice options. The calibrated models are found to be logically valid, statistically sound, and the disaggregation policy has generated desired responses.
+The hypothesis is so formulated that the calibrated models operate within the frame work of Urban Transportation Planning Process, thus enabling to demonstrate the usefulness of the models in the planning exercises. The calibrated models have been applied to New Bombay area for the activities planned for 2001 A.D. The needed input variables for the operation of the models have been estimated by adopting policies on vehicle ownership, road network performance, public transport connectivity and frequency of services.                                                                                                                                                                                                                                                                                                                                                                                                                          The Operation of SBM models has demonstrated that the models are usefull in estimating travel demand that is sensitive to policies on transport and transportation. The operation has shown that the Road network performance has an influence on modal shares of traffic having longer trip lengths. Public transport level of service either in terms of Route frequency or Route connectivity has shown to have an influence on modal shares. These level of services together have shown to have greater influence on modal shares.                                                                                                                                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bus transport is the predominant and captive mode in all the places either as an independent mode or as a feeder system to the rail based service. In the initial enthusiasm of expanding the public bus transport sector, little thought was given to the long-term financial viability of public sector organisations and for political and social reasons, various uneconomic operations were assigned to public sector. This converted what was essentially a profitable business under private sector into a loss making industry in the public sector. The growth of public bus transport sector with the twin objectives of providing adequate and efficient service and achieving economic viability has raised the problems of evaluation of performance which takes into account both the objectives.                                                                                                                                                                                                                                                                                                                                                         
+In the recent past, the financial loss has become a common feature among various State Transport Undertakings (STUs) in India. Several reasons can be attributed to the continuing losses of these STUs. But the government's present general policy is towards privatisation and dilution of loss making public sector undertakings and the government is trying to distance itself from any commitment to STUs. As per the guidelines of the Planning Commission, the entry of private sector in road transport is to be encouraged and the STUs should consolidate their operations in the existing operational area. This may pose certain problems to STUs. In the long run private operators may corner all the profitable routes, while uneconomic routes may be left unattended or left with the STUs.
+STUs were earlier treated as vehicles of macro-economic development but now their commercial profits and losses only are considered. Thus there is a major shift in the government policies. So, the change in this public policy brings in an urgent need for every STU to examine their external and internal strengths and weaknesses. The most widely used argument for privatisation of STU services would be nullified if STUs start showing profits for which they are capable of to certain extent. Hence it has become necessary for STUs to improve their financial performance and operational efficiency for their development. A comprehensive strategic appraisal and optimisation of STU performance from user and operator perception is very much essential. The existing approaches fail to provide a handy tool in this direction.
+The purpose of this research is to propose methodologies for appraisal and improvement of performance at STU level from user and operator perceptions, including the strategy for impact assessment of service changes on ridership and Total Quality Management in STUs. The proposed framework comprises of five main submodels.
+The Factor Analysis model is proposed for obtaining the composite performance index from the initial set of operator perception parameters. The key parameters are selected as the most salient performance indicators against the larger data structures. To make the key parameters comparable, they are normalised and these normalised values are combined to form a composite performance index. This composite index is used for inter-STU comparison.
+The composite level of public transport service from the user perception parameters have been determined by the Crisp Value Approach and Fuzzy Set Approach. Since the conventional crisp value approach with the single number representation for linguistic grades is too abstract, a better approach which accounts for uncertainty associated with the quantification of linguistic grades, like fuzzy set approach is also proposed. The deficiency level of various attributes are also obtained through crisp value approach.
+The Goal Programming Model is proposed for the attainment of optimal values for the objectives and also for the attainment of the values of objectives with degree of goal attainment for different input combinations under multi objective user-operator environment. The Service Changes Model evaluates various service improvement options and helps us in the selection of best alternative to improve ridership and revenue.
+The main feature of the study is that, it envisages performance appraisal to diagnose and correct the problems which limit an STU's efficiency and quality of service with a view to increasing the ridership so that the financial and operational performance of STUs is enhanced. All these models are subjected to a set of tests with the actual data obtained from the STUs of Tamil Nadu. The typical set up of STUs prevailing in the state has provided an ideal setting for performance ranking, through factor analysis model. The remaining models are applied to Jeeva Transport Corporation (Tamil Nadu State Transport Corporation - Erode) to examine the operational difficulties and it is observed that the proposed approach is workable and will be of great help to managers to improve the performance of STUs.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The growing concern of rapid increase in urban population and vehicular growth culminates into emerging of many Megalopolises. In such areas, spatial distribution of activities warrant, the necessity for travel by appropriate arrangement of sub-systems in tune with the form of urban structure and routes serving it. Mass transportation in Megalopolises is facing problems mainly during peak hours due to the concentration of commuters on certain routes. However, as the urban area is growing, so-called peak hours are extended to peak periods thus extending the duration of congestion as well. Increase in the travel demand and usage of mass transportation systems indicates that considerable additional capacity is required for mobility in various forms. To solve the most pressing hardships of the users in realising their desires the introduction of a medium capacity track-guided system is established along the identified high dense corridors. The LRT under operation in more than 330 countries appears to be a reasonably good solution which is not only capable of catering to 5000 to 20,000 pphpd, but also can integrate and co-exist in a multi-modal environment.
+The main issues that confront in the introduction of LRT is the lack of a systematic, mathematical approach in the identification of the routes with the cost effective demand estimation techniques and patronage determination incorporating congestion. The existing approaches when reviewed, revealed several limitations to provide a handy tool in this direction.
+The purpose of this research is to propose mathematical modeling techniques relying upon Operations Research. The research undertaken proposes a theoretical basis for the identification of transit corridors using Network Compression and Label Correction techniques. It also presents a methodology for the quantification of demand resorting to deterministic and stochastic approaches for estimating the base year as well as the future demand employing the Linear and Non-Linear Programming approaches. Based on the Optimisation and Entropy Maximization techniques the demand between two-station pairs has been computed for transit and other modes. By calibrating the Logit model by DLOGIT and making use of HIS, the disutility coefficients, cross elasticities and mode choice probabilities for modes like Private, IPT, Bus and LRT, varying the cost of LRT in terms of bus have been obtained. Also, the micro-responsiveness of passengers along the corridor specifying the commuter shift in favour of LRT and its patronage at two policy options has been presented.
+In the present work, the On-line congestion has been introduced by way of Link Performance Functions by formulating a Combined Mode Split and Assignment model, for computing the transit and non-transit patronage under user equilibrium condition, in which the users can choose the modes and routes simultaneously satisfying Wardrop's principles modeled by a Frank Wolfe technique. Finally the research presents a methodology for the management of transit operations by estimating the optimum fleet requirement and a combined schedule of transit services satisfying the pivotal demand utilizing the Optimisation technique.
+All the models developed fit into the overall urban transportation planning and thus present a simplified tool in association with standard network coding procedures and data collection methods. Relevant Computer Programs are developed to facilitate them to work on personal computers, hence they could be easily adaptable by the transport organizations. The models include NETCOM and OR models for Corridor Identification, TROPT, CSR &amp; ENTMAX models for estimation of demand, COMSEA model for patronage determination introducing On-line congestion and OPTCOST model for quantifying optimum fleet requirement and generating a combined schedule of transit services.
+The main feature of the study is that, it envisages an overall planning and management of mass transit systems through a systematic procedure through optimization techniques, ensuring healthy interaction between the LRT and other transit systems. All the models that have been developed are subjected to a set of tests with the actual data collected in the city of Hyderabad. The typical travel scenario and transport problems existing in the study area has provided an ideal setting for the case study. Even though this exercise has been carried out for a corridor between Kukatpally-L.B. Nagar in Hyderabad, the suggested methodology can be applied for other Indian Cities for mass transport planning and scheduling, thus helping the planners in improvising the efficiency of mass transit services.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In this study, a procedure is presented, for estimating the patronage of urban mass transit systems through link volume counts incorporating the trip maker's choice behaviour in the selection of route and mode. The growing population and vehicles are straining the urban traffic infrastructure to the limits. The introduction of the mass transit systems will facilitate the moving of a large number of commuters. The estimation of the likely demand for these systems forms a pre-requisite for the successful planning, design and operation. The Origin-Destination matrices manifest the aggregated travel desires forming the basis for plan preparation. However, the traditional methods of obtaining them are becoming harder due to the limitation of the resources. The need of the hour is the evolution of a procedure that can estimate the mass transit demand with cost-effective methods.
+A review of the contemporary research revealed that there is no unique procedure for the travel demand estimation. Though updating of the O-D matrices through link volume counts is an effective tool that is being favoured by the researchers of the later day, its application to the urban level has not been exploited unto the desired levels. Some of the key issues in travel demand estimation at urban levels are the expression of the travel patterns in Passenger Car Units, adopting all-or-nothing procedures for route assignment and consequently, the mode split. Considering the flow in terms of Passenger Car Units in a heterogeneous urban environment hitherto is more or less a rule than an exception. The reported segmented estimation of the O-D matrices in terms of actual number of vehicles is apparently limited. The assignment of these O-D matrices has been through all-or-nothing procedure in a majority of cases. Assignment methods that include the behaviour of the individual trip maker who considers the non-minimum paths as well, have not found wider applications. Efforts in the direction of incorporating the choice of the trip makers in selecting a new mode while weighing the choice options of all the competing modes have not come into limelight. Even with the available modal shifts, the final estimation methods have differed by a large extent. The critical review of literature has helped in identifying the deficiencies in the existing approaches and formulating the methodology for the present study.
+A procedure is suggested for the estimation of mass transit demand in urban environment overcoming the identified shortcomings. Based on the experiences, it is proposed to group the trip makers into slow moving, bus and fast moving categories. Most likely mode-wise trip matrices are proposed to be estimated by making use of computer programs MINTRAP and MODUA. The O-D matrices so obtained are assigned on to the network in accordance with the behaviour of the trip makers. Nature's laws of conservation of energy and the previous experiences have revealed the preferences of the trip makers by slow moving vehicles towards the shortest paths. Hence, they are being assigned to the minimum path routes. The trip makers by buses are captive to the designated routes and are being assigned accordingly. The choice behaviour of the users by fast moving vehicles valuing the travel time more than the travel distance, is proposed to be incorporated by considering all the links between an O-D pair having a likelihood of being chosen. Multipath assignment is proposed to be adopted by introducing a path diversion parameter. For the realistic assessment of the link travel time, speed-flow relationships need to be developed by classifying the links in terms of the link characteristics such as the lane width, composition of slow moving traffic and the link-side interference. The introduction of a mass transit system draws its patronage from amongst these flows. The patronage is proposed to be estimated through DOGIT formulation for the competing modes for the attributes of travel time and travel cost. The time and cost options of the competing modes are taken in terms of bus travel time and bus fare structure. Obtaining the shifts from various modes, the boarding and alighting for the mass transit systems is computed at zonal level irrespective of the actual location of stations along the alignment.
+Appropriate models for various stages beginning from the updating of O-D matrices to the modal shifts have been developed. Appreciable land-use changes have taken place since an earlier study HATS (Hyderabad Area Transportation Study), necessitating a fresh look into the zoning scheme. Accordingly, the study area is classified into 125 traffic zones as against 99 zones delineated previously. Road inventory study has preceded the field surveys on 200 links where the link information is collected. The field surveys are mainly conducted on those corridors that are likely to have an influence on the mass transit patronage. The secondary data is computed through concerned agencies like Municipal Corporation of Hyderabad, Hyderabad Urban concerned agencies like Municipal Corporation of Hyderabad, Hyderabad Urban Development Authority, Traffic Police, Planning Department etc. Models have been developed, calibrated and validated with the help of the data so obtained.
+The usefulness of the suggested methodology is demonstrated for a case study of Hyderabad and salient features and findings of the study are explained. A comparison of the results obtained is made with those of earlier studies. The modifications and improvements suggested in the hypothesis - updating of the mode-wise urban O-D matrices through link counts, incorporation of route choice behaviour of the trip makers and selection of a mode through a formulation that considers the choice options of all the competing modes - proved to be in order.
+The exercise has resulted in a systematic cost-effective method of travel demand estimation together with the choice behaviour of the trip maker with expected reliability. The limitation of the study and the scope for further work are also touched upon.
+Although the techniques developed have been demonstrated for their application for the case study of Hyderabad, it is hoped that, the suggested procedure be adopted for similar exercise in other urban areas as an effective tool for the planners.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highway transportation is the most adoptable means of transport under different topographical conditions. Top priority is given by the Government to improve the highway transportation facilities through allocation of huge funds. The flexible pavement construction should ensure reasonable performance throughout its design life. The key to effective performance of flexible pavements is to understand the causes of distress.
+In recent years, Highways have experienced an increase in the severity and extent of permanent deformation (rutting) in hot mix asphalt pavements built especially on poor subgrades. The increased rutting has been attributed to increase in axle loads, traffic volumes and additional overlays as maintenance. Pavement structural design has historically focused on protecting the subgrade, shear resistance of the hot mix asphalt layer is left to appropriate material selection. In this context, a simultaneous approach considering the subgrade, which acts as the foundation and the top layer, which receives the wheel load, is required to ensure high performance.
+In the present study, an attempt is made to evaluate the life benefit of the flexible pavements in terms of rutting potential by treating the poor subgrade and the surface course simultaneously by improving the strength of the subgrade and the stiffness of the top layer sufficiently to sustain the high stress states. The study includes evaluation of optimal quantities of additives in both subgrade and surface courses and development of a Medium Scale Accelerated Pavement Rut Tester (MAPRT). This facilitates field-testing of flexible pavement performance in terms of rut formation.
+The equipment is fabricated locally. It constitutes a 3HP-3 phase motor connected to a gear box constituting a reduction gear arrangement through a set of three gears, the other end has a bevel pinion mounted on to the bevel gear arrangement which facilitates conversion of the rotations about horizontal axis to that about vertical axis. The shaft connected to the bevel gear carries an adjustable arm with a wheel assembly. It is equipped to vary the contact pressure and frequency of load application. The entire system rotates in a circular path producing a circular test track facility. The methodology evaluated suggests use of 25% pond ash + 5% lime by weight of the soil for subgrade stabilisation, to ensure a minimum CBR of 15. High performance of surface course can be ensured by using 12% of crumb rubber by weight of bitumen as a modifier.
+Field tests have been conducted on the test track built for the purpose to evaluate the life benefit due to subgrade and surface modification in various combinations. The life benefit of the pavement in terms of rutting at two different frequencies of wheel load repetitions was also evaluated. The results of the work indicated that the 15% increase in life could be achieved by improving the subgrade alone. In case of surface modification, there is an increase in life by about 35%. Improvement at both top and bottom layers increased the life by about 50% when compared to the conventional pavement section. It was also observed that the rutting in case of low speeds developed faster than that in case of high speeds.
+Analysis for stresses and strains under the test track sections has been done using FPAVE program to support the findings in the field. The Analysis and Design of the full-scale pavements was also carried out under various combinations considered in the field-testing to highlight the decrease in the pavement thickness required and the cost reduction thereof.
+The present work demonstrates the life increment (life benefit) by improving the subgrade and surface courses independently and in combination. The equipment developed (MAPRT) can become an important tool in pavement management as it aids in determining the performance of innovative materials for use in design and also help in stage wise construction of pavements.
+</t>
+  </si>
+  <si>
+    <t>Modelling urban form and structure using transportation planning techniques for small and medium cities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industrialization and migration of the people are the major factors influencing growth of urban areas. The total urban population in India is 28% of total country's population, amounting to 30 crores. Indian census classified these urban areas into six groups of cities, out of which the class-I are the most prominent and account for 65% of India's urban population. There are 425 such small and medium with population one lakh ten lakhs and 26 cities with population more than ten lakhs.
+Out of the three important components of an urban area i.e. Housing, Activity and Transportation, transportation is treated as the top most priority. As the cities are growing, traffic and transportation problems are increasing manifold. To solve the transportation problems of the small and medium cities, urban modelling exercise is carried by many researchers. Review of literature reveals that current urban transportation modelling approaches have been piecemeal and desultory. Further the current experience of urban transportation planning shows that while preparing master plans, economic activity in urban development is treated as static concept. So in today's context of urban transportation modelling in India, economic activity in urban areas must be seen as a dynamic, adaptive, iterative and continuous process.
+Trips generated in urban areas are mainly of three types namely work, educational and other trips. Among these, work trips constitute about 70 percent. Educational and other trips are evenly distributed over total geographical area of the city. Work trips are originated from the place of residence and destination to the place of employment. In urban areas mostly the jobs are located in central business district (CBD). The formation and development of CBD usually takes place along the major arterial roads of the urban areas. Hence, these arterial roads form as major corridors in cities. Future development of the city generally takes place along the arterial roads as ribbon development. Spatial separation of residence to work place increases with the ribbon development affecting the mean trip length and there by the mode choice. Thus the shape of the urban area is determined by the growth taking place in the corridor along with the location and size of the CBD.
+The urban development in most of the Indian cities is the result of laissez-faire development with ribbon extension along the major arterials emerging out of the city core. Existing four stage conventional urban transportation planning process has failed to consider the parameters such as urban form, shape and structure in to urban transportation modelling. Hence in the present research work it is proposed to study the effect of urban form, size, shape and structure on transportation activity. While doing so the dynamic behavior of urban area is taken into consideration for modelling. Spatial development and directional growth of the urban areas along the major arterial roads from city core to the periphery is taken as the basis for evaluation of urban areas.
+The total work has been divided in to three broad stages.
+In the first stage, theoretical city concept is introduced with various forms and structures and the corresponding transportation activity and accessibility criteria are evolved. The out come of the first stage is performance evaluation of city for urban form, structure and shape. Urban Travel Activity Index (U.T.A.I) is developed to classify any city for its group using optimization technique.
+In the second stage, using the conventional trip distribution model the effect of different shapes on distance deterrence parameter is studied. To find the suitability of mode of transport for different urban shapes and forms, Gamma distribution is fitted to the cumulative frequency trip length data. Critical trip lengths for different modes of transport are derived by equating the rate of change of slope of gamma distribution curve to zero. The derived critical trip length for different modes, among different urban forms and shapes helps in characterization of distribution of CBD’s and residential zones in urban areas.
+In the third stage variation of spatial development along the arterial roads from city core to periphery is studied to establish directional growth of the urban areas using exponential density models. Urban Composite index is developed for the evaluation of urban areas using principal component and factor analysis. From the principal component and factor analysis, key factors contributing to the urban development are established.
+To fulfill the objectives of the proposed three stage methodology, a theoretical city is designed using building block exercise. The building blocks are juxtaposed in increasing number to represent the cities of bigger size. Interactive software program is written in C++ with control statements to generate urban areas with different forms, shapes and structures. Performance evaluation of the urban areas for their form and shape is carried out by taking transportation activity and accessibility criteria. Urban Travel Activity Index is developed using optimization technique to represent the dynamic behavior of changing urban form and also to classify the urban areas for their form and structure. To validate the proposed methodology six cities with two to thirteen lakhs are taken as case study areas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">During the past few decades there has been tremendous growth of urban centers all over the world. In India, slow but steady rise in urban population has been noticed since 1901 when the urban population constituted 11% of the total. As per the census of India, about 28% of India's population is living in towns in 2001, while this figure was only 20% in 1971 and 24% in 1981 and 26% in 1991. It has also been reported that the number of Class-I cities which were 152 in 1971, rose to 216 in 1981, 302 in 1991 and then to 423 in 2001. Consequent to these changes in demographic as well as socio-economic characteristics and in the pattern of growth rate, the necessity for transportation facilities for intra as well as inter urban-center travels, is being felt badly. Such stage has now reached that in order to have an effective and economic solution of this problem, comprehensive transportation planning has to be adopted instead of trying to solve a few isolated transportation problems to pacify public demand.
+Determination of future traffic volume and pattern is one of the objectives of any transportation planning process of a study area. Estimation of trips from and attracted to a traffic zone is essential in a conventional four stage Urban Transportation Planning System (UTPS). The conventional planning process comprises of four general steps with a view to determine the future travel pattern and its volume.
+Through the entire process of transportation planning, from determination of objectives, and data collection, model calibration and forecasting, evaluation of alternatives to implementation stages, procedures have increased greatly in complexity and variety having sole reliance on complicated computer based models and systems. For calibration of these models, data requirement is enormous and the process of collecting the data requires long time as well as great amount of money. It is true that these complexities have brought some benefits but have caused a growing frustration amongst the planners because in most of cases complexity of techniques, requirement of long time and large sums of money obscures the benefits accrued. Moreover, the fact that the conventional methods require large amounts of data the collection of which takes lot of time makes them not suitable for short range planning.
+In the above context, the need for simplification and streamlining of the techniques of transportation planning processes is being felt badly for some time past. These simplified procedures should be so developed that they will require less data, less computer time, less money and less manpower without sacrificing the effectiveness and utility. Research workers and experts in the profession have been trying since last few years to evolve simplified methods of forecasting travel patterns and volume of traffic. The developed method should be able to make use of available resources like manpower and past records and consume less time and cost to forecast the traffic conditions. On the other hand, the different stages in the conventional planning process are independent of each other. Trip Generation is the first of the four stages and the most important one since the real travel demand is estimated in this stage. Distribution and Assignment are dependent on each other and there should be a feedback effect in the model structure to account for change in the choice of distribution based on the assignment on the road network. Mode Split should give an estimate of public/private transport demand on the links of the network, which is not biased by any mode.
+To fulfil the above requirements, a simplified process is developed in this research work involving three different stages, namely Trip Generation, Combined Trip Distribution-Assignment and Mode Split. For the trip generation stage, two models have been proposed, one by the development of Trip Rates and the other using Artificial Neural Network technique. Important links in the road network are identified and traffic volume count surveys are conducted on those links. Cordon line survey is carried out and external traffic volume is determined and deducted from the total volume observed from surveys to yield internal traffic volume. The study area is divided into zones and data on socio-economic variables are collected from various surveys and secondary sources. The socio-economic variables are distributed among all the zones and matrices are computed and assigned on to the network as if they are trips. The assigned socio-economic variable volumes and internal traffic volumes are regressed to yield trip rates. Based on the output from VBTR model, the variables influencing trip production and attraction for the Trip Generation using Artificial Neural Networks (TGANN) Model are determined. Resilient back propagation algorithm is used in the TGANN model to estimate the trip production and trip attraction values. Data for training and testing the neural network are prepared and software is developed for the analysis. Once the model is observed to be yielding good results, the weights are saved and using the same weights, the values of trip production and attraction are estimated. These values along with travel time for the links in the network are used in the second stage of iterative Combined rip Distribution and Assignment model. The proposed CDA model incorporates feedback effect from assignment stage to the distribution stage. In the last stage, a mode split model has been developed which uses data collected initially on vehicle cost and time through road side interviews and O-D matrix developed in the second stage. The output from the last stage of mode split gives link volume of mass transport trips on the network.
+Outputs from the developed models are compared with those from conventional models and results have suggested that these models are accurate. Important advantages of the models are that since they are based on real traffic volume counts, the accuracy is assured. Outputs from models in preceding stages are utilised as inputs in those of succeeding stages and this highlights their ability to be integrated and formed a comprehensive modelling system. The complete package is applied to Hyderabad city to examine the operational difficulties and it is observed that the proposed approach is workable and will be of great help to planners.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development of transport systems has produced both the economic and social benefits to the mankind, however, it has polluted the environment too. Road transportation is next only to industries in causing irreversible damage to the environment. Effects of noise can be cumulative and its influences may cover several aspects of every day life. Road traffic noise has been reported to be a cause of annoyance in many countries of the world.
+Traffic noise prediction models have been developed in many industrialized countries, these models cannot, however, be applied in their original form in other countries, especially in the developing countries as the characteristics of the traffic and reference mean emission levels of the vehicles are different. Very little work has been reported on the traffic noise in the non-industrialized nations. Another marked area where there has been very limited work is urban bus transit noise. The growing demand for energy, congestion and associated environmental degradation in urban areas demand immediate remedial measures. An oftenly cited solution by the transport professionals is the mode shift from private auto to the Public Transit. In most cities of the non-industrialized countries, urban bus transit remains the best form of public transit because of high costs involved with underground or other forms of rail based rapid transit. High noise levels are one of the problem areas in the urban bus systems of the developing countries. Further, there appears to be little awareness in the public about the ill effects of continuous exposure to high noise levels. In the light of this, the current study aims at investigating the road traffic noise, the bus transit noise and the noise perceptions in urban areas.
+The study is divided into two parts: Urban bus transit noise studies and Road traffic noise studies. Three types of data requirements are identified for the research study: Noise levels, Perception of noise and its annoyance and Traffic flow characteristics. Kuwait, Hyderabad and Warangal are identified as the case study areas.
+Experiments are carried out using systematic random sampling in the selected bus routes, bus stations and roadway sites. State of the art Sound Level analyzers from Bruel &amp; Kjaer, Denmark, and PEEK and Nu-Metrics (USA) traffic flow measurement equipment are employed for the data collection. SAS® and SPSS® programs are utilized to analyze the data. Descriptive, Frequency, Correlation, Cross-classification, Factor and Regression analyses are performed on the data. Prediction models and perception models are developed. Urban transport noise mitigation policies and recommendations are also included in the thesis.
+It is hoped that the results of this study will be used to come out with action plans for urban planning in general and urban transportation planning in particular for the benefit of community at large.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Efficient road transportation plays a vital role in the economy of any Nation. Road transport in India plays a significant role in the overall transportation system of the country due to its advantages like easy availability, flexibility in operation, door to door service facility. Reliability and its tracking ability is an another advantage. India has the second largest network of roads in the world, next to USA. The total road length in the country is over 3.3 million km, a spatial road density of about 1 km/km² of area. Of the total network, the Low volume rural road constitutes 80% which indicates their importance. These roads are generally granular pavements with or without a bituminous surfacing layer and the design of which is usually done by an empirical method considering subgrade CBR as the main contributing factor towards its design. In India, over the last two decades’ huge investments are being pumped in for the construction of low volume rural roads. Pavement maintenance decisions are generally based on the skimpy rules and rules of thumb of engineers without evaluating the actual pavement performance criteria.
+The rate of pavement deterioration depends on the timing of the maintenance intervention, choice of the type of maintenance treatment, and the quality of the construction. It is in this context, Pavement deterioration prediction models and the evaluation of performance of in-service pavements are essential. A few studies were carried out in India in the past on the performance of low volume roads. To study the performance of low volume roads, this study is taken up with few selected test sections in three districts of Andhra Pradesh, India (Guntur, Kurnool and Warangal) under varying subgrade and traffic conditions. Deterioration models are developed for low volume roads using the data collected on key distresses parameters. The subgrade characteristics are used from the samples collected and tested in the laboratory. Given the conditions (physical, traffic and climatic), these models can be applied anywhere to understand the deterioration levels of a pavement during its design life. This research is to investigate the significant factors that affect the pavement deterioration in low volume roads at the project and also at a broader level. To achieve this, a relation between observations of the distress parameters (independent parameters) and the pavement age and traffic applications is developed. The developed relations are in turn used to compute the fatigue traffic and the age that the pavement can withstand before failure. The use of an iterative linear and nonlinear regression analysis is adopted while determining the model coefficients.
+After predicting the deterioration levels of pavements the remaining service life of pavements (RSL) is estimated. Remaining Service Life is defined as the projected number of years until rehabilitation is required. This is done using the present pavement condition and the latest rehabilitation action performed on that particular pavement. Remaining service life models for low volume rural roads as described above are predicted by traffic and time approaches. Individual RSL models for distresses such as rutting, skid resistance, cracking, roughness and deflection by the said two approaches are established. From the individual models, a comprehensive RSL model for state level is developed based on the minimum RSL value and weighted average method. The developed RSL models are helpful in facilitating the decision making regarding maintenance and rehabilitation. Different maintenance interventions are recommended on the selected stretches for different pavement conditions
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freight Transportation becomes imminent because the production and consumption centers are spatially separated. This movement is one of the contributing factors for the national economy. At present it is found that highways and railways are catering for the domestic freight in any country with marginal share by other modes. Since the transport sector is one of the main energy consuming sectors, any saving in this direction through optimal use of the systems go a long way in the conservation of energy and savings in the foreign exchange. Therefore, for any policy decision for system development the optimal modal shares need to be assessed with a clear understanding of the competition among different modes of transport.
+Attitudinal variables such as reliability, safety, location of firm, avoidance of loss or theft etc. affect the mode choice in addition to the basic distance, travel time, or cost of transportation. However earlier studies have not explicitly or in detail considered them because of the difficulty in quantification and forecasting. In the present study an attempt is made to incorporate these variables by quantifying them using psychometric scaling technique (method of successive category analysis) in addition to transit time, transit cost and distance as considered in several other studies.
+Having gone through the literature a disaggregate Logit model is adopted because of its simplicity for freight mode split modeling and evaluation of policy options. 
+Hyderabad city is considered as the study area. It has been found that bulk commodities like coal, cement, fertilizer, food grains etc. are captive in choice, by both the modes. Railways provide special routes and siding for giant industries and corporations. Whereas in road sector these bulk commodities are transported by specified transport companies on yearly contract. Therefore, these bulk commodities are not considered in this study. Non-bulk commodities are not captive, and the individual shipper has a choice to select any particular mode based on mode and commodity characteristics, and hence only the non-bulk commodities are considered in this study.
+A 10% sample of non-bulk commodities shipped on a normal working day in Hyderabad city is collected for the study. A preliminary analysis of the data revealed that road sector is dominant for short distance (&lt; 600 km), while competition exists between the two modes for medium distances (600-1200 km), and for long distances (&gt; 1200 km) the rail mode is the dominant one. The data is divided into eight commodity groups. A set of mode split models for total commodities as well as selected commodity groupings for short, medium and long distances have been developed with necessary statistical tests, reproducibility and then validated. Geographical transferability of the calibrated models is tested by examining another city much smaller in size (Warangal). In general, it is observed that the models are geographically transferable based on their predictive ability with marginal percentage error. Probability surfaces of choosing the road are constructed for several combinations of significant explanatory variables by varying them within a specified range.
+The present work suggests that disaggregate Logit modeling approach offers better explanation of freight mode choice behaviour. The limitations that still exist in the proposed methodology are then presented and scope for further research is identified.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currently, there is a hub of huge rush to highways and roads in any where of the world. Transport has become essential key element in functioning and socio-economic development of any nation. The demand for transport is derived demand in the wake of rapid population explode, industrialization and urbanization. Due to globalization of trade and commerce and liberalization of economic policies world wide, the transport services occupied significant position, to cater freight and passenger conveyance under top priority. The road transport is commonly adoptable mode of transport, as it readily suites to any topography and climatic conditions. Transport infrastructure provides accessibility and interconnectivity to different places and regions all over the world. India has the second largest road network in the world after USA. India has embarked upon a new era of highway constructions namely, Golden Quadrilateral, National Highway Development project (NHDP) and Prime Minister Gram Sadak Yojana (PMGSY) programme for development of rural roads.
+There is a growing interest in the construction of concrete pavements in India, due to their high strength, durability, better serviceability and overall economy on long run. There is no rational method of design available for the rigid pavements. Most methods of designs are either empirical or semi-empirical in nature. In flexible pavements the performance based design procedure is already in practice. The performance-based design is a promising practice, which reflects on stability and improvement of design, construction quality and maintenance in a broad sense. In wake of this the performance based design procedure practice also can be incorporated in the conventional rigid pavement design procedure. It is necessary for a systematic procedure to define the causes and remedies of various distresses be evolved to provide a satisfactory pavement performance.
+The pavement deterioration, visible at the surface is broadly referred to as pavement distress. The defects of concrete pavements may be of structural defects, surface defects and miscellaneous type. The deterioration of concrete pavement is majorly due to crack formation. The event of crack is due to separation of the cement concrete pavement into one or more parts, with or without a space between them. There are several possible causes of cracking in concrete pavements. This necessitates to study the present pavement condition.
+The principal component of pavement performance is evaluation of pavement condition. Evaluation is one of the best tools available to know the condition of the pavements at a given time and to anticipate the probable changes of that condition. In the pavement evaluation system the survey for the pavement condition is key component parameter. This system is capable of effective collection, processing and evaluation of in-service pavements data pertaining to physical and structural evaluation aspects. To improve the design, construction quality and maintenance needs of concrete pavements, accordingly this system has invariable significance. This consists of three major components i.e., data collection, retrieval and evaluation of pavements for both visual and structural conditions. By conducting distress study on in-service pavements, Pavement Condition Index (PCI) of those pavements has been calculated. For this a software program PCI SLAB has given in appendix-B to find the PCI value by giving type of distress and its severity present. By conducting non-destructive testing on these pavements the strength characteristics can be determined and stress ratio can be found. Stress ratio is the ratio of stress due to load to the flexural strength of concrete. For these selected in-service pavements, traffic volume studies have been conducted to find the traffic. Knowing the PCI values, traffic and stress ratio of these pavements a performance based rigid pavement design equation has been developed by using regression analysis techniques. This performance based design equation is incorporated in the present design of rigid pavement as per IRC 58-2002 procedure as an additional performance check for high design precision and to obtain optimum design thickness. A software program WR_PAVE has been developed to obtain the performance based design for rigid pavements. To improve the performance a number of new concrete materials for specific constructions are being developed and among them fibre reinforced concrete is one of the fast emerging innovative promising material.
+Fibre reinforced concrete can be referred as concrete containing hydraulic cement, water, fine or fine &amp; coarse aggregates and discontinuous discrete fibres. Fibres used in concrete can be either natural fibres like jute, bamboo etc., or artificial fibres like steel, glass, polypropylene etc., Steel fibres are generally considered to be effective and economic. The steel fibres possess high modulus of elasticity and plastic behavior as compared to other types of fibres. Addition of these fibres in concrete increases its resistance to tensile stresses, impact, fatigue, and modifies its brittle behavior. If the steel fibres are discrete and are randomly oriented, then the concerned concrete is referred to be steel fibre reinforced concrete (SFRC). The SFRC brings better control of cracking and improves mechanical properties. The addition of these fibres to concrete makes it more homogenous and isotropic can improve the tensile properties particularly ductility.
+The significance of SFRC is now well-recognized and gained worldwide acceptance due to its low cost and improved performance of thinner sections. A conventional numerical parameter describing the geometry of a fibre is its aspect ratio, defined as the ratio of fibre length divided by an equivalent diameter. Both aspect ratio and fibre volume will affect the ability of steel fibre in improving the properties of concrete. This has been investigated by laboratory experimentation for finding optimum values of aspect ratio and fibre volume.
+The recent research in this new millennium is concentrating on the construction of thinner pavement section of better quality, which could bare heavy traffic loads of modern vehicles. These thinner pavement sections are possible with steel fibre reinforced concrete. The traditional methods of designs do not account for the finite size pavement slabs. The only rational approach to such type of problem is finite element method. The 3D FEM can handle greater deals, complex characteristics, and construction materials than any other analysis. Using Finite Element Method the pavement of size 3.5m × 4.5m is analyzed by using ANSYS 5.4 Direct solver. The PCC pavement Slab is analyzed for determination of the effect of stresses, strains and deflections in the Y-direction (i.e, in the direction along 4.5m long side) and found that the effect of stress in Y-direction is with in 1m. Therefore the slab dimensions of the pavement for model testing are chosen as 3.5m × 1.0m with the thickness determined from performance based design equation.
+The pavements are designed by performance design procedure for an optimum thickness. The model pavement test tracks are constructed in 3.50 m × 1.00 m size with the optimum thickness derived from performance based design. Though SFRC pavement required thinner slab sections, to have a comparative assessment between the SFRC and PCC pavements the same thickness of slab are being laid. As the critical stresses are normally observable in the edge and corner regions of the pavement slabs, in SFRC pavements all around 150mm has been constructed with SFRC leaving the interior portion with PCC. The optimum fibre content with an optimum aspect ratio is taken for construction of steel fibre reinforced concrete pavement slab. The model test tracks are cured for 28 days and tested for static loads at edges and corner load positions.
+The deflections, stresses and strains are calculated for the corner and edge loading positions in PCC and SFRC pavements, for different loads. The comparison is made between PCC and SFRC pavements. It has been observed that the PCC pavement failed at 5000 Kg and where as SFRC pavement has failed at 9278 Kg. This shows the increased load carrying capacity of SFRC pavement. The analysis and correlations studies are made between PCC and SFRC pavements, with observed values, FEM results and with the theoretical methods like IRC and Westergaard methods. The conclusions are made from the above analysis.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intersections are the critical zones where vehicles perform different maneuvers in an attempt to share the same space at the same time. As the vehicle reaches the intersection, the driver of the subject vehicle has to take a quick decision by taking into account the intersection geometry, speed and type of the vehicles approaching the intersection from the other legs. At uncontrolled intersections there are no external signs or signals to control the movement of vehicles and the traffic operates based on the priority of traffic movements. In mixed traffic conditions priority rules are often violated by the road users. Vehicular interactions at uncontrolled intersections under mixed traffic conditions are very complex. At higher traffic volumes, the minor road vehicles tend to wait for longer time to cross the intersection that increases the probability of the vehicles to accept the shorter gaps. Hence, the general behavior of different vehicle types and the gap required for each vehicle type approaching from the minor and the major road taking right turn need to be carefully analyzed. Gap acceptance method is used for mixed traffic condition because it is based on the critical gap and followup time, which in turn depends on the type of vehicles and traffic conditions. Also, gap acceptance procedure is more suitable for mixed traffic conditions because it can be used for different composition of vehicles. 
+For this study, data was collected from three three-legged and three four-legged intersections located in various cities in India. The following parameters were extracted from the videographic data at each intersection and for each vehicle type: total volume, gap accepted, gap rejected, follow-up time, stopped delay, and total delay. This study tries to analyze the effect of vehicle type on gap acceptance behaviour of each of the right turning vehicles from the minor and the major road. Also, this study analyzes the major stream vehicle combinations on the gap-acceptance behavior of the minor stream and the major stream vehicles. It is observed that the size of the vehicles and traffic volumes has a significant influence on the critical gap. Depending on the major road vehicle combinations, the critical gap for each right turning subject vehicle varied from 1.4 s to 8.7 s. 
+Mixed traffic is composed of different vehicle types with varying geometric and acceleration characteristics. The performance of an intersection very much depends on the vehicular composition. This may be due to varying lengths and widths of different vehicle types which influences the intersection capacity. Different vehicle compositions are simulated using VISSIM for different vehicle types with an increment of 10% starting from 0% to 100%. The proportion of each vehicle type for the selected composition is considered in such a way that these proportions matches with the observed field proportion. Thereby, the effect of traffic composition on delay and volume at urban uncontrolled intersections is studied for all the vehicle types. Also, the total delay and the service delay is calculated for all the vehicles at all the intersections considered in this study. It is observed that there is an increase in delay as the size of the vehicle increases. Finally, the field delay data is compared with the simulated delay data and the error observed is less than 10% for all the vehicle types.
+Capacity estimation is necessary for designing the intersection facilities and for upgradation of the control facilities to avoid unnecessary delay. Capacity at uncontrolled intersection is measured either by gap acceptance method, empirical regression approach, or conflict technique. Performance of uncontrolled intersection is influenced by the delay caused by lowpriority movements on minor roads. In this study, capacity at uncontrolled intersections is estimated by considering the gap acceptance models including Tanner’s model, Drew's model, modified Sieogloch's model, and Luttenin's model. Further, the capacity is also estimated using the HCM (2010) and Indo-HCM methods. Based on the MAPE, Tanner's model is observed to be the best among the selected models for determining the capacity at urban uncontrolled intersections. Also, the performance of each of the six intersections is evaluated using the LOS criteria. HCM (2010) failed to differentiate between the performance of the six intersections. However, the LOS evaluated using the volume-capacity ratio resulted in significant variation in performance of the six intersections.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The theme of this research is to develop a desirable public transport (PT) share model for Indian cities. If cities are “engines of growth”, then the PT system is the fuel through which these engines derive its energy, and therefore, the extent of the PT system is one of the factors that influence the urban development. It is the critical stakeholder in urban 3Es (Economy, Environment and Equality) dynamism. Good public transportation increases the economic growth of a city (Economy), reduce energy consumption, emissions level (Environment) and increase accessibility to all levels of income groups’ (Equality).
+In the absence of an adequate and efficient PT, many private and para-transit modes have entered into the market to meet the travel demand. The decline in PT shares is a severe concern regarding health, urban environment and city’s sustainable mobility. Due to the absence of clear guidelines to implement the PT system and level of desirable PT share to be achieved, cities are inconveniently moving towards alternative transport system. Out of 468 Indian class- I cities, less than 20% of cities are having organised PT system. Cities with a population of over 1 lakh (0.1 million) shall target for a minimum 30% PT share (MoUD 1987). However, even after 30 years of such policy in existence, only limited cities have reached this minimum. The need of the hour is to introspect these policy recommendations, revise the benchmarks if needed, incorporating the characteristics of the city.
+PT is a function of various urban factors. Statistical evidence reveals that PT shares are influenced by urban variables such as population, urban form, density, average trip length, vehicle ownership, per capita trip rate, fare, public transport network density, fleet size, etc.
+The research methodology is outlined in four phases. Phase-I discusses the review of the preliminary literature and research objectives. In phase-II, a comprehensive literature review was conducted and compiled the inferences from all the relevant works and methodological approaches related to the research. The secondary data collection process, data analysis and models development have been discussed in phase-III. The desirable PT share model approach, model development, study conclusions and recommendations have been addressed in phase- IV.
+36 Indian cities and 11 International cities (restricted to the Asian continent) are analysed as part of the study. The cities are shortlisted based on the availability of data and its uniformity across different cities. The research study is significantly developed from secondary data. The determinants are then filtered by discarding correlated variables. The relevant variables of the existing PT model have been substituted with desirable variables to develop the desirable PT modal share model.
+The research analysis revealed that city average trip length and population density are essential factors in PT share. The developed desirable PT model will help to propose the sustainable PT shares for Indian cities and support in the formulation of city transport policies.
+</t>
+  </si>
+  <si>
+    <t>Provision of good rural roads to meet the public facilities changes the characteristics of rural transport. Efficient rural transportation depends largely on a well-knit road network to provide accessibility and mobility in rural areas. Rural roads are primary infrastructure which provide essential access to rural population to various social facilities such as education, health, transportation and market facilities. Transportation planning in rural areas is highly complicated because of the multiple activities having non-specific interaction between any two places. Various models for planning of rural road network were developed by different research organizations, educational institutions, and consultants but in actual practice, they have not been of much help to implementing agencies (shrestha 2013). There is a need for the consolidation of the existing rural road network for maintenance and connectivity to the local community and enable economical transportation of goods and services to provide better livelihood opportunities as part of poverty reduction strategy.
+One of the primary constraints in the development of rural infrastructure is the lack of sufficient funds in developing countries. Apart from the limited resources to build rural infrastructures (roads, water supply, electricity, telecommunication network) and public facilities, the lack of proper planning methodologies for development, improvement, and management of rural infrastructure is also a significant problem. Optimal use of available funds is a necessity and may help to develop and improve the present situation. Populations covered by a road link (Kumar and Kumar, 1999) can be taken as significant indicator to be considered to take into account the socio-economic benefits from the rural road links. The two other factors can be costs (construction costs and travel costs). However, these factors cannot be assessed precisely for rural areas. Hence, costs can be considered indirectly taking distances (construction cost) and the person-km (travel costs) (Kumar and Tilloston, 1985; Makarchi and Tilloston, 1991; Singh, 2010).
+This study envisages consolidation of the existing Rural Road Network to improve its overall efficiency as a provider of transportation services for people, goods and services. The proposed methodology in this study, enables to determine rural hubs in the rural areas based on the facility index of the settlements. The Village Facility Index (VFI) is calculated by considering the desirable coverage distance. Spatial analysis is carried out in the study area to identify the Desirable Coverage Distance of the Facility (DCDF). VFI is the summation of all facility indices such as Educational Facility Index (EFI), Medical Facility Index (MFI), Transportation and Communication Facility Index (T&amp;CFI) and Economic Activity Facility Index (EAFI).
+The rural road network is generated by connecting the rural hubs by minimum travel time path in Geographical Information System (GIS). In the present study, travel time was measured from the field by travelling along the road using design vehicle. In a place where the terrain is not flat and the level difference between the two origin-destination points is very high, travel time was considered in both directions. In this study, since the terrain is plain and traffic volumes in both directions are more or less equal, the travel time in both direction is assumed to be same. The Minimum Spanning Tree (MST) of network is generated from the existing rural road network. MST represents the minimum connection level necessary for the rural accessibility of a specified coverage distance. In this study, MST of network is considered as the optimal road network of the study area.
+Fund available for rural road construction/upgrade is usually a constraint in developing countries. Hence, the available resources should be effectively used. For this, a prioritisation method is necessary. Based on a realistic and practical criterion, the rural road links in the network are to be prioritised. The study explored the different rural road network models for prioritization of links for new construction and upgradation works. In this study, planning for prioritization of links is achieved by considering two parameters i.e. population and vulnerability of link. The model allows investigating the public resource allocation to attain minimum total cost with an investment budget constraint, intended to design the infrastructure by keeping total transportation costs to a minimum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low Volume Roads (LVRs) constitute an integral component of the road system in all countries. Their importance extends to all aspects of the social and economic development of rural communities. India has a total road network of over 5.3 million kilometers in length, making it the second-largest road network in the world. This is about 80 percent of all types of roads in India. Given this, they often form the most crucial link in terms of providing access to educational, medical, recreational and commercial activities in local and regional areas.
+The use of geosynthetics for engineering applications is not a new concept. The concept of reinforcing weak soils to enhance their load carrying capacity has been developing until present times, and the first textiles were used in road construction in the United States in 1926. After that, it has been practiced for centuries in various infrastructure projects and road construction. Geosynthetic materials include geotextiles Geonets, Geogrids, Geocells, and Geocomposites. Most of these materials become a permanent part of the road. The use of Geosynthetic materials has grown significantly in road construction for the past 40 years and trial construction over the past 15 years. In the pavement, they perform four essential functions, namely reinforcement; separation; drainage; and filtration. Today a variety of geosynthetic materials can be used in many engineering projects such as roads, railroads, dams, retaining walls, tunnels, landfills, recreation areas, etc. The construction of LVRs on weak subgrade soil within the sinking budget is a challenging task. Most of these roads are lower order roads and subjected to low traffic. Under such circumstances whenever the poor native subgrade soil found, it is mandated to adopt the soil stabilization techniques or ground improvement methods.
+Coastal and river portion of India is predominantly blessed with clays and expansive soils. Coastal and river portion of India is predominantly blessed with clays and expansive soils. These soils behave very typically due to the presence of montmorillonite minerals. Further, they pose several problems in terms of swelling and shrinkage and contribute cause for various distresses. To address these issues one of the common and innovative techniques are promoting the usage of geotextiles. So, the utilisation of geotextiles has gained universal promises to enhance the weak subgrade soil and geotechnical engineering aspects.
+A review of existing literature revealed that most of the experimental studies were conducted on polymeric geosynthetic to reinforce the weak subgrade soil; limited research is available on coir Geotextile applications for LVRs. The LVRs are usually the lower order roads in the world, where the traffic ranges from 100 vehicles per day to 5000 vehicles per day.
+The coir geotextile is naturally available eco-friendly and abundant material. It is available in huge quantity in the coastal area and also Malaysia, Indonesia, Srilanka, etc. The coir geotextile has higher tensile strength, more extended durability high performance among the other natural geotextile material, the utilisation of coir geotextile mats in pavement and geotechnical applications having high demand. It also creates an opportunity for rural employment, saving of natural material such as aggregate, morrum soil in the pavement application. With this background, in the present study four types of the coir geotextile mats such as Non-Woven Coir Mat (NWCM), Woven Coir Mats (WCM), Coir Composite (CC) and Geogrid with Non-Woven Coir Mat (GG+NWCM) combinations were considered with a aim to evaluate their effectiveness and potential benefits in laboratory using the Wheel Tracking Test (WTT) setup and in-situ by constructing a test tracks in the field under Accelerated Pavement Testing (APT). The primary conclusion from the laboratory study is that the maximum and minimum rut depth was 37.0 mm and 13.0 mm was found at sub-base-I and sub-base-II with 200mm thickness of the fabricated mould. The placement of the coir geotextile mats with morrum soil showed more significant performance in terms of rut depth and No. of passes than the gravel soil sub-base. It is also concluded that the inclusion of coir-geotextile mats improved the No. of passes (1200 passes) in sub-base-II with 100mm layer thickness with 300 mm assemble of mould during reduction thickness of the sub-base material. The rut depth at sub-base-I and sub-base-III position are noticed with reinforcement and without reinforcement as 3.0 mm, 4.0 mm and 11.0 mm, 24.0 mm respectively. In addition, the gravel sub-base soil is more effective when providing the decreased thickness of the sub-base as per the design standard charts (225 mm). In the case of the reinforcement function, the composite material provided better reinforcement than the woven and non woven coir mats. From the test track study, it was noticed that the reduction (55mm to 40mm) of the sub-base layer thickness is more in case of gravel soil with different types of coir geotextile. The deformation in the gravel sub-base soil is less than the morrum sub-base soil. To summarize finally, it is noticed that test track studies are more reliable to quantify the performance of these materials than laboratory evaluation. The coir composites material are shown the better function (reinforcement and separation) than the woven coir geotextile, the thickness of pavement can be reduced up to 55 mm with provisions of coir geotextile mats.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedestrians are one of the vulnerable road users and their safety is utmost important. The pedestrian risk taking behaviour and driver yielding behaviour varies from person to person. There is a possibility of accidents between pedestrians and vehicles at pedestrian crossing locations due to the misunderstanding between pedestrians and drivers. Improvements in the pedestrian facilities and safety-related issues will help to reduce the number and severity of pedestrian-vehicle (P-V) accidents and improve the pedestrian safety. This can be possible only with better understanding of pedestrian road crossing behaviour and their interactions with vehicular traffic. The present study is intended to analyse and model the P-V interactions at uncontrolled intersections to know the various factors affecting the severity of P-V interactions. Also, intended to estimate and model the pedestrian dilemma zone (PDZ) at uncontrolled intersections to improve the gap acceptance behaviour of pedestrians.
+Four 3-legged and four 4-legged uncontrolled intersections were selected from Warangal and Visakhapatnam cities in India. Video was recorded continuously for two hours in the morning (7:30AM to 9:30AM) and evening (4:30PM to 6:30PM) periods from each study location on a week day. Geometric details of all study locations were directly measured from the field. Required pedestrian, vehicle, and geometric parameters were extracted from the videos using MPC-HC media player, Kinovea and DataFromSky softwares. Risk indicator (RI) was defined using post encroachment time (PET) and approaching speeds of vehicles for each pedestrian-vehicle interaction.
+The threshold limits of PET and RI were defined using support vector machine (SVM) technique in Python interface to define the severity levels of P-V interactions at uncontrolled intersections. The results showed that the severity of P-V interactions was inversely correlated with threshold limits of PET and threshold limits of RI directly correlated with RI. The severity level was higher at lower values of PET and higher values of RI. The threshold limits PET at three-legged intersections were found to be lower than that of four-legged intersections and threshold limits of RI at four-legged intersections were found to be lower than three-legged intersections.
+An ordinal logistic regression models were developed at uncontrolled intersections to know the various parameters affecting the severity levels of P-V interactions. The model results showed that the probabilities of P-V interaction severity levels increase with the presence of male pedestrians, crossing with luggage, usage of mobile phones while crossing, pedestrians crossing with lower crossing speeds, and pedestrians crossing at entry point of intersection. The probabilities of severity levels also increase with the increase in speed of the vehicle, left turning vehicles, and presence of young pedestrians. The probability of severity levels at threelegged intersections were found to be higher than that of four-legged intersections. The developed models were validated using various validation techniques.
+The pedestrian dilemma zone (PDZ) at uncontrolled intersections was estimated using gap cumulative distribution (GCD) and support vector machine (SVM) methods and developed a binary logistic regression (BLR) model to estimate the PDZ boundary limits. The estimated lower and upper boundary limits of PDZ at three-legged intersections were 7.5 m and 24.0 m respectively using SVM method and 6.0 m and 18.5 m respectively at four-legged intersections. The boundary limits at three-legged intersections were found to be higher than that of fourlegged intersections. The BLR model results showed that the PDZ boundary limits lies close to the intersection in case of male and young pedestrians. They shift away from the intersection when the pedestrians crossing at the entry point of intersection, increase in size and speed of vehicles. The developed models were validated using classification table, model fitting criteria, and likelihood ratio test. 
+The study results can be used for better understanding of P-V interactions at uncontrolled intersections under mixed traffic conditions. The proposed threshold limits of can be used to define the P-V interaction severity levels using pedestrian and vehicle characteristics at uncontrolled intersections. The proposed PDZ boundary limits can be used for the practical applications in the field to eliminate the dilemma behaviour of pedestrians while crossing the road at uncontrolled intersections.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The key aims of this study are to examine models for describing the possibilities of Bus Rapid Transit system (BRT) system and the association among land-use and transport modal choice. Kabul and Jalalabad were considered as study areas. These cities are the most significant metropolitan areas in Afghanistan in terms of traffic and urban form. In the analysis and modeling of Kabul's urbanization and transportation systems, the geographic unit used is the municipal area of Kabul, which spans 1,025 km² and comprises 22 districts. In order to achieve accurate results, the city was divided into 213 traffic zones. Hence, traffic zone is the unit for analysis. For Jalalabad city, disaggregate Stated Preference (SP) data were collected through a survey along the PT routes to analyze the mode shift from the current modes to the proposed BRT system. 
+A preliminary survey revealed a lack of sufficient and efficient high-capacity public transport (BRT) systems in both cities. Additionally, segregation between land-use and the transportation system in Kabul city has created problems such as congestion, a high level of accidents, and air pollution. To evaluate the possibilities for an efficient BRT system, key concepts such as travel demand, modal shift, and affiliation among land-use and trip behaviours must be analysed. Various factors can affect these concepts, including household characteristics, travel features, and characteristics of the built environment. 
+Urban Travel Demand Modelling (UTDM) study for Kabul utilized various tools to understand the city's travel behaviours. Through multiple linear regression, key factors such as population, job availability, car ownership, and urban density were recognized as major influences on trip- making. The majority of journeys appeared to start from the suburban areas and move towards the Central Business District (CBD). Using the Gravity Model, trips between 213 traffic zones were analysed, highlighting the main travel paths in the city. The study also looked into Kabul's transportation choices and noticed a preference for smaller vehicles. With the help of the Logit curve function, these travel preferences became more apparent. The rise in small vehicles poses a challenge for the city's transportation network. To address this, there's a suggestion to introduce an advanced BRT system to reduce the reliance on these smaller vehicles. As a part of this research, possible BRT routes were assessed to match travel needs. Among them, the All-or-Nothing model identified route 23 as the best candidate for a BRT, connecting Kabul airport to the city core. 
+Modal shift is a fundamental concern when introducing a competent BRT system. Therefore, it V was necessary to develop a modal shift model to understand the influential variables. The research identified crucial elements associated with the viability of the BRT system. The suggested BRT system is anticipated to attract a considerable number of passengers form cars, share taxis, and personal transport means. The transition to BRT is profoundly shaped by factors such as journey and wait durations, distance to stations, the presence of air conditioning, the motives of the commuters, and gender considerations might catalyse a notable shift of users from low-capacity vehicles (LCVs) to the BRT. It has spotlighted pivotal elements driving the transition from LCVs to the advocated BRT system. The data gathered in this research demonstrates that many low-capacity vehicle users, including those using cars in Jalalabad city, are dissatisfaction with the current state and would likely consider this new transit alternative. The last part of study investigates into the relationship between urban compactness and transportation preferences in Kabul's 213 traffic zones using the mode choice model. Evaluating urban compactness, the research considers land use diversity and demographic densities. Using metrics. it identifies districts with high, low, or sprawling compactness levels. Results highlight a clear trend: densely populated areas like Bibi Mahroh and Khair Khana witness a greater inclination towards walking and public transport. In contrast, sprawling regions such as Paimonar and Reshkhor see a preference for private vehicles. The study confirms that urban layout significantly influences transportation trends, with sprawling areas showing a reduced tendency to utilize public transport or walking. The thesis aims to explore the impact of Bus Rapid Transit (BRT) systems on urban mobility, specifically examining how BRT influences the mode choice among urban residents. It contributes to the body of knowledge by providing empirical evidence on the efficacy of BRT systems in encouraging a modal shift from private vehicles to public transport, and examines the relationship between the built environment and mode choice.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The majority of Indian roads are constructed with bituminous pavements for the surface course using Hot Mix Asphalt (HMA) technology. This technology involves the production of bituminous mixture at relatively higher mixing and compaction temperature. At these temperatures, inordinate oxidation and degradation of the bituminous binders occur due to aging. Furthermore, these higher temperatures requires higher energy consumption and emits harmful greenhouse gases which causes environment pollution and endangers the people who are involved in the various construction activities. Recently, various scientists and government agencies focused on reducing the working temperature of bituminous mixture which in turn consume less energy and less emission of greenhouse gases. In this direction, Warm Mix Asphalt (WMA) additives have been developed and practiced around the world to produce bituminous mixtures at reduced temperatures. Many researchers reported that the use of WMA additive reduces the stiffness of binders during short-term and long-term aging. However, very few researchers have reported the possible reason for stiffness reduction by analysing the formation of oxidation compounds during aging. The performance of the bituminous mixture will also depend on the rheological properties of the binder and the type of additives. Therefore, the present study investigates the influence of WMA additive on the changes in chemical and rheological characteristics of binders occurring during the aging process. Reduction in production temperatures results in bituminous mixtures that are more susceptible to rutting, whereas higher production temperatures results in mixtures that are susceptible to cracking and moisture damage. Inorder to overcome these issues, waste plastic has been incorporated in HMA and WMA mixtures using a dry process. However, the major disadvantage of the dry process is that the shredded waste plastic is added to whole fractions of preheated aggregate in the pug mill. Fused plastic tends to agglomerate with fine aggregate particles, and result in the formation of small lumps which may lead to underperformance of bituminous mixtures. Hence, the present study used an enhanced process, in which shredded waste plastic is initially introduced with preheated coarse aggregate, followed by the addition of fine aggregates and binder.
+Therefore, the first phase of the present study was focused on evaluating the influence of WMA additive on functional chemical group characteristics, and rheological performance of bituminous binders. Two unmodified binders (VG20, VG40), two modified binders (PMB40, CRMB60), and a chemical warm mix additive (Evotherm) were selected for this study. To assess the chemical and rheological characterstics of all binders, a comprehensive laboratory testing was carried out using Fourier transform infrared (FTIR) spectrometer, and dynamic shear rheometer at various aging conditions. FTIR spectrometer was used to quantify various aging indices such as carbonyl index and sulfoxide index whereas dynamic shear rheometer was used to evaluate the rheological performance of bituminous binders in terms of Superpave rutting parameter, fatigue parameter, Shenoy’s parameter, non-recoverable creep compliance, zero shear viscosity, low shear viscosity, fatigue life, Glover-Rowe parameter, cracking initiation and the significant cracking threshold at various aging conditions using amplitude sweep, frequency sweep, multi-stress creep and recovery tests.
+The second phase of the present study was focused on evaluating moisture-induced damage and rutting performance of HMA and WMA mixtures containing waste-plastic-coated coarse aggregates. Bituminous mixtures were prepared in the laboratory using Bituminous Concrete grading 2. The waste plastic consists of only shredded Low Density Polyethylene (LDPE) milk packets. The short-term aged mixtures were compacted to prepare specimens with a target air voids of 4% and 7% whereas the specimens for long-term aging were compacted to 4% air voids. The performance of bituminous mixtures towards moisture-induced damage was evaluated by carrying out dry as well as wet indirect tensile strength tests at 25oC for all aging conditions. Rutting performance was evaluated by performing a dry wheel tracking test on all mixtures at 60oC temperature for all aging conditions. The entire data obtained through tests on bituminous binders and bituminous mixtures was critically analysed to quantify aging indices and rheological parameters for bituminous binders, and moisture-induced damage and progression of rut depth for bituminous mixtures.
+From the test results, it was observed that the addition of Evotherm additive in the base binder reduces the carbonyl index, and sulfoxide index. It indicates that the addition of an Evotherm additive in the base binder undergoes less aging. It was also observed that the addition of Evotherm additive in the control binder increases all rutting parameters except for nonrecoverable creep compliance where reverse trend was observed. It indicates that addition of Evotherm in control binders increases the rutting potential. Furthermore, it was observed that the addition of Evotherm in the control binder increases the fatigue parameters which indicates a beneficial effect and resistance toward fatigue cracking. From the bituminous mixture test results, it was observed that the addition of LDPE-coated coarse aggregate (LCA) in HMA mixtures through the enhanced process improved the resistance against moisture-induced damage and permanent deformation. In the case of WMA mixture test results, it was observed that the addition of LCA has very less effect on moisture-induced damage performance whereas  resistance toward permanent deformation has been increased. Among all rutting parameters, the low shear viscosity has a better correlation with the rut depth of HMA and WMA mixtures.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavements are usually composed of large amounts of aggregate for different layers. Therefore, pavement construction consumes huge aggregate quantities obtained from natural sources. The increased demand for quality natural aggregate (NA) and scarcity of NA have paved the way for alternative materials to NA in pavement construction. Recycled concrete aggregate (RCA) is one of the alternative materials, which is a by-product of demolition waste; it can be stabilized and used as pavement base or subbase material. The present work investigates the performance of recycled concrete aggregate (RCA) stabilized with a combination of lime fly ash (LFA) as a sustainable pavement material for low-volume rural roads (LVRRs). RCA was stabilized with 10,15, and 20% LFA content, with a lime-to-fly ash ratio of 1:2. Cement is a commonly used stabilizer for RCA stabilization. Therefore, the present study also considered RCA stabilization with 5 and 7% of cement (CRCA); and NA stabilized with LFA (LFNA).
+The comparison was made between LFRCA and CRCA, LFRCA with LFNA. Several laboratory tests, including modified Proctor compaction, Unconfined Compressive Strength (UCS), Indirect Diametrical Tensile Strength (IDTS), durability, repeated load indirect diametrical tensile stiffness and fatigue, were conducted to evaluate the performance of stabilized mixes. Further, microstructural analysis was carried out using Scanning Electron Microscopy (SEM), Energy Dispersive Spectroscopy (EDS) and X-ray diffraction to understand the stabilization process for RCA. The results of UCS comply with the requirements of stabilized base for low-volume roads in India. The mechanical properties are influenced by curing age. The fatigue life increases with a decrease in stress ratio. Two-parameter Weibull distribution function was used to analyze the fatigue test data. It is concluded that fatigue and mechanical characterization of LFRCA indicated that NA could be completely replaced with RCA, and LFA can be an alternative to cement. The test results demonstrated that adding 10 to15% LFA content is sufficient to meet the strength and durability requirements of 3MPa for stabilizing RCA. Finally, the pavement design was carried out using RCA stabilized with 15%LFA, and RCA stabilized with 5% cement as a complete replacement for the gravel base of low-volume roads, and the critical strains were determined using IITPAVE software. The design and analysis indicated that the pavement with 145 to 185mm LFRCA and 150 to 200mm thickness of CRCA could be used as a complete replacement for gravel base for different traffic and subgrade conditions. It has been noticed that the pavement thickness with LFRCA is comparable to that of pavement thickness with CRCA. This study provides an approach to the sustainable use of RCA and FA for pavement applications.
+</t>
+  </si>
+  <si>
+    <t>EXPERIMENTAL STUDIES ON THE PERFORMANCE OF LIME FLY ASH AND CEMENT STABILIZED RECYCLED CONCRETE AGGREGATE FOR THE BASE COURSE OF LOW VOLUME ROADS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permanent deformation in bituminous pavements is considered to be the most critical distress phenomena and is generally associated with high temperatures. Bituminous mixture performance tests are mostly conducted at the Performance Grade (PG) temperatures or at 60 °C. However, rutting also occur at temperatures lower than the PG pass/fail temperature. This rutting performance of bituminous mixtures is highly dependent upon the response characteristics of a bitumen binder subjected to shear. Therefore, it is important to measure viscosity of bitumen at different temperatures. Bitumen can exhibit non-Newtonian behaviour at pavement temperatures lower than the PG pass/fail temperature. This non-Newtonian behaviour can become prominent with aging of bitumen. Zero Shear Viscosity (ZSV) is a property of bitumen corresponding to the Newtonian plateau observed at shear rates approaching zero. However, there are issues with the measurement of ZSV, wherein, ZSV measured from different methods and models is different. Moreover, the creep test to measure ZSV is time consuming. Thus, the main research aim is to characterise the non-Newtonian response of bitumen at typical pavement temperatures. This non-Newtonian response of the bitumen binders is studied by adopting a Linear Shear Rate Sweep (LSRS) test protocol and a Step-wise Steady Shear Rate Sweep (SWSSRS) test protocol. The LSRS test protocol is a linear sweep protocol wherein the rate of change of shear rate is constant. On the other hand, SWSSRS test is a step-wise steady shear test conducted at very low shear rates. Further, wheel tracking tests are widely used to measure the rutting resistance of bituminous mixtures in the laboratory where a loaded solid rubber wheel moves at a particular speed over a specimen prepared with bituminous mixtures and rut depth is measured at a particular temperature. As the loaded rubber wheel moves over the specimen, deformation is measured and rut depth is computed. The accumulated permanent deformation with repeated application of wheel passes is termed as rutting in bituminous mixtures.
+The main aim of the LSRS test was to capture the classical response of viscosity as a function of the shear rate. However, it was observed that the resultant response of the binder was quite different. For most cases, both Newtonian as well as a non-Newtonian response was observed. At very low shear rates, an initial plateau region was observed which was followed by a shear thickening region. This shear thickening region was subsequently followed by two shear thinning regions for most cases. The initial plateau was able to give a direct measure of ZSV denoted as η0(L). Moreover, from the shear thickening region the peak transient viscosity (ηTV) is selected and is proposed as a non-Newtonian rutting parameter, respectively. The non- Newtonian response in the SWSSRS test was characterized by the appearance of a stress overshoot. A steady state was observed after this stress overshoot at time, ‘ts’. It was observed that the bitumen response was independent of shear rate, time and shear history. Since, the adopted shear rates in the SWSSRS test were very low and is within the region where ZSV is typically measured, the viscosity at ‘ts’ in the first forward sweep was considered as an alternate ZSV and is denoted as η0(S). η0(S) is also proposed as a rutting parameter. |G * |/sinδ, |G * |/(1-(1/tanδsinδ)) and Jnr were also measured by following the standard test procedures. 
+From the wheel tracking tests it was observed that there is considerable scatter in the rut data measured along the loaded wheel traverse. A probabilistic approach was chosen to analyse the scatter in the rut data. It was observed that the Weibull and lognormal distributions were able to represent the scatter in the rut data comparatively better than the normal distribution. Using the Weibull and lognormal forms, probability curves were determined at 50, 80, 90, and 99% reliability levels. However, it was further observed that the lognormal distribution tend to over-estimate the probabilistic rut data. With an increase in reliability, there was an increase in rut depths. Comparative analysis of the probabilistic rut data showed that the Dense graded Bituminous Macadam (DBM) mixture was comparatively better at resisting permanent deformation than the Bituminous Concrete (BC) mixtures. Effect of bitumen aging was observed wherein, the long-term aged mixtures had greater resistance towards rutting than the short-term aged mixtures. Moreover, three rutting rates were determined.
+In order to determine the efficacy of the proposed bitumen parameters to be used as alternative to the existing rutting parameters, correlation of the bitumen parameters with the mixture rut depth and mixture rut rate were identified. It was observed that all the six binder parameters determined in this research showed a strong correlation with mixture performance. This strong correlation was observed with both the rut depth as well as the rut rate. These correlations were observed to be indpedent of wheel passes and percentage reliability. However, from the overall correlations a clear hierarchy was observed, wherein, η0(S) had the better coefficient of correlation followed by Jnr. Thus, the non-Newtonian characterisation of the unmodified bitumen binders helped to identify two bitumen parameters, a Newtonian parameter, η0(S) and a non-Newtonian parameter, η0(L) which were corraborated through the wheel tracking tests.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With globalization, the exponential rise of vehicle number in different classes has made the nature of heterogeneous traffic into more complex phenomena. Accordingly, with the presence of different vehicle sizes, different engine characteristics, and maneuvering abilities, road traffic movements result in a wide spectrum of speeds and noise levels. Thus, with road speed being the prime fluctuating agent, researchers determined road traffic noise from vehicle fleet as a combination of aerodynamic noise, propulsion noise and tire-pavement interaction noise. Aerodynamic noise is the source emitted along the geometrical structure of the vehicle in motion, and its effect is very low compared to other noise sources on the road. This is due to the fact that, it is experienced only by the person sitting in the vehicle and the major aerodynamic drag at the tire-pavement interface is considered within the tire-pavement noise itself. Moreover, dependence of aerodynamic noise on vehicle speed is a complex phenomenon as it varies with temporal changes in the field. Tire-pavement interaction noise is defined as the noise generated due to tire-pavement interaction caused by the movement of vehicle tires over the pavement surface. As the vehicle moves at a high speed, high tirepavement interaction can occur. Thus, tire-pavement interaction outstrips other noise sources at higher vehicle speeds exceeding 40 kmph. On the contrary, propulsion noise is a dominant noise source at vehicle speeds falling below 40 kmph, as it is noise generated from the engine, gear transmission and the exhaust system.
+At lower vehicle speeds in mixed traffic conditions, one more major noise source known as honking (number of honks in the time interval) defines noise levels. This is due to the fact that, accelerating vehicles generate more noise than vehicles travelling at constant speed, where the driving pattern of a vehicle is likely to change frequently at intersections and rotaries or roundabouts. Even though the primary objective of improving traffic flow by reducing conflict points from safety point of view is achieved with rotaries or roundabouts, the noise level due to honking will severely affect people residing nearby. Thus, apart from high speed midblock sections of a highway passing through urban area, there is a need to initiate the study on evaluating traffic noise pollution near urban units such as intersections, rotaries or roundabouts, where traffic volumes are high, and vehicle speeds are comparatively low. Thus, prior to the individual source level noise quantification, the current study focused on identifying major parameters responsible for overall traffic noise on both midblock sections and rotaries. Standardized Control Pass-By (CPB) method was used for measuring the far field noise experienced by the roaduser on both highways and rotaries. The noise levels measured for all selected highways showed that, both LAeq (dB) and LA10 (dB) exceed noise limits prescribed by Central Pollution Control Board (2000). Overall, two and three wheelers are dominating the volume proportion in most of the highways selected, showing the need for improved public transportation facilities. The results also revealed that, a combination of volume proportion and vehicle speeds would play a significant role in highway noise level generation. Similar approach of far field measurement at the rotaries revealed that, heavy vehicles and their corresponding honking were majorly affecting the LAeq (dB) compared to other vehicular proportion. It was observed that, an equivalent noise level [LAeq (dB)] rise of 2 to 6 dB was solely caused by heavy vehicles. These results revealed that, each vehicle class moving at different speeds in mixed traffic flow is certainly responsible for the rise in traffic noise level in its own way. This shows the need for source level noise measures to be taken for reduction of noise levels.
+Thus, the current study further attempts to study the effect of both tire-pavement interaction and propulsion noise on overall noise levels with the objective of identifying the major factors affecting them. Accordingly, passenger cars of varying engine types were selected as test vehicles for assessing the effect of propulsion noise. To assess the impact of tire-pavement interaction, two asphalt and two cement concrete pavements were selected as test sections in the Warangal city, and Controlled Pass-By (CPB) and Coast-By (CB) measurements were conducted on these test sections at mid-night using a Sound Level Meter (SLM). Accordingly, capturing the vehicle noise level requires a clear distinction on assessing the effect of propulsion, and tire-pavement interaction. Thus, an approach for assessing the pass-by propulsion noise levels is used with logarithmic subtraction of relative energies of the sound pressure levels captured from CPB and CB methods. Further, an added advent to pass-by methods using the vehicle jack was developed and the respective tire-pavement noise levels were measured in this case study. In comparison, tire-pavement noise levels quantified using the developed method showed a good correlation with standard CB noise levels, with an R2 value of 0.965. On an average, petrol vehicles are producing 4 dB to 5 dB less propulsion noise levels compared to diesel powered vehicles. Moreover, tire-pavement noise levels are hugely affected by pavement types, and showed considerable increase of 3 dB to 9 dB on cement concrete pavements in comparison with asphalt pavements. Tire-pavement and  vehicle noise levels were reaching similar edge on overall fine-tuned A-weighed noise levels, at speeds exceeding 60 kmph for all selected test vehicles. This shows the dominance of tirepavement interaction on roadusers (people outside the vehicle including pedestrians). Thus, the study attempts to measure the effect of tire-pavement interaction on commuters (driver and passengers), who are under continuous noise exposure throughout the travel, unlike momentary exposure by roadusers. To avoid the effect of vehicle vibrations on SLM inside the vehicle, a new method is proposed using a handheld SLM and a 3-axis stabilizer mounted SLM. The noise levels captured using both sound level meters were compared at different vehicle speeds ranging from 40kmph to 70 kmph. The stabilizer mounted SLM had shown 1 to 2 dB lower noise levels compared to handheld SLM. Average variation of 3 to 5 dB was observed between asphalt and cement concrete pavements, with the highest noise being produced by cement concrete pavements. Even though several researches in the past had measured the in-vehicle noise as perceived by commuters, the method adopted in this study is first of its kind in tire-pavement noise research where the noise levels due to reduced effect of tremor vibrations experienced by the driver at the ear level were captured. Overall, the dominance of tire-pavement interaction on overall noise at most speeds was clearly observed, which is hugely influenced by the change in pavement type. This shows the immediate need for constructing low noise pavements to mitigate the tire-pavement noise at the source level. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Road traffic emissions are one of the major sources of air pollution in urban areas. Various hazardous gases, including Carbon Monoxide (CO), Nitrogen Oxides (NOx), Hydrocarbons (HC), Particulate Matter (PM2.5 and PM10), Sulphur Dioxide (SO2), Carbon Dioxide (CO2), Formaldehyde (HCHO), Volatile Organic Compounds (VOC), Lead (Pb), Ammonia (NH3), and others, are present in the air across any urban roadway network. The concentration of air pollutants close to the main traffic routes is much higher than the regional background levels, putting the local people in danger and exposing them disproportionately to air pollution caused by traffic. The efficient investigation of the status of air quality in urban areas on both road mid-block sections and signalized intersections needs to be performed for better planning and designing of roadway network considering traffic volume growth. The present study deals with measuring, analysing, and modelling of concentrations of different pollutants observed in three medium scaled cities namely Warangal, Tirupathi and Vijayawada.
+The present study measures the concentration of six different pollutants namely Carbon Monoxide (CO), Carbon Dioxide (CO2), Formaldehyde (HCHO), Total Volatile Compounds (TVOC), Particulate Matter (PM2.5), and Particulate Matter (PM10) using portable equipment. The study also obtains field data related to traffic volume, temperature, signals, queuing, proportional share of different types of vehicles and Air Quality Index (AQI) at road midblock sections and signalized intersections. The study carries out a detailed analysis on pollution data, volume data and AQI data obtained from different locations. The study also analyses the variation of concentration of different pollutants and AQI with respect to traffic volume and time of the day.
+The present study proposed concentration model with respect to different pollutants (CO, CO2, HCHO, TVOC, PM2.5, and PM10) considering traffic flow observed at road mid-block sections and signalised intersections. The other variables such as proportion of vehicle types, temperature and signal control parameters are also included in the model development for predicting test estimate of concentration and AQI index. The present study also developed an emission model to estimate CO, CO2 and O2 emissions using age of the vehicle, emission norms and vehicle type as independent variables. The study also implemented different machine learning tools like Support Vector Regression (SVR) and Artificial Neural Networks (ANN) to develop air concentration and AQI models. The validation of models was performed successfully with different set of data collected in the field indicate their suitability under mixed traffic condition. The sensitivity analysis is performed with different combinations of model input variables namely traffic volume and percentage of 3W. The status of air quality is defined based on AQI values obtained when there is incremental change in the traffic volume from 0 to 7000 PCU/hr and percentage of 3W from 0 to 30%.
+The concentration models developed in the study indicate that the variation in variables such as traffic volume, proportional share of vehicle types and signal control parameters would have a significant change in the concentration of pollutants. The study also identified from the emission model that age of the vehicle, emission norms and vehicle types are responsible factors for emissions. The study also signifies that the percentage of three wheelers could interpret the change in AQI. The findings of the study also illustrate the status of air quality is in moderate level in some regions and in satisfactory condition in some locations of the study areas according to Indian Air Quality Index (IND-AQI) standards. The study also infers that ANN models performed better in predicting the concentration of pollutants and AQI compared to MLR and SVM models. The results of the study provide insights to develop empirical guide for urban transportation planners and policy makers and traffic system designers to predict the level of pollution and AQI at various busy traffic facilities in the cities with similar characteristics.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The growing demand for public transportation is increasing over the decades. Terminals are infrastructures where pedestrians of various needs and characteristics make use of them. Within the available space, infrastructures are to be managed for efficient functioning of these terminals. Foot over bridges are typical elements where pedestrian movements takes place in both directions. The pedestrian movement on horizontal passageway varies to that of the inclined stairways. Understanding of pedestrian flow on these elements facilitate to arrive at the width of passageway and stairway. To study the pedestrian walking behavior on foot over bridges in intercity railway stations, pedestrian movement of video recording data on seven passageways, six stairway and six escalators were collected from three intercity railway stations namely Secunderabad, Warangal and Vijayawada. The width of passageways observed are 2.1m to 4.5m. The stairway widths observed are 2.0m to 3.6m with inclinations 300 to 340 . The Pedestrian flow characteristics such as maximum flow, optimal density and mean walking speed are determined for each facility from manual extraction from play back videos of collected video recordings. On the passageway, the maximum flow range from 43 to 99ped/m/min with optimal density 0.73 to 3.07ped/m2 . On stairway, the maximum flow range from 26 to 40ped/m/min attained at optimal densities 1.00 to 2.93ped/m2 . The mean walking speed on passageway and stairway are 67.33m/min and 38.49m/min. On escalator, a maximum flow of 51ped/m/min is attained with an optimal density of 3.55ped/m2.
+ Pedestrians walking speeds varies with individual’s characteristics such as gender, age and luggage on passageway and stairway. Also the pedestrian walking speed is effected by with infrastructure characteristics such as width as the space available per pedestrian varies. Hence the pedestrian walking speeds variation with individual’s characteristics and infrastructure width are studied.
+ The comparison of pedestrian walking speeds with different attributes showed that the walking speeds of middle aged female and aged female are similar and there does not exists a significant difference in their walking speeds. The mean walking speeds on passageway widths of 4.5, 3.5-3.6 and 2.1-2.3m are 64.85, 64.48 and 70.88m/min.
+           Comparison of pedestrian walking speeds on stairways showed that they does not vary significantly on stairways of width 2.0m to 3.6m for pedestrian densities falling less than 1.00ped/m2. Pedestrian walking speeds are compared to study the width effect on ascending and descending direction. Statistical results showed insignificant difference in mean walking speeds on stairways with width in ascending direction. The comparison of descending speeds showed significant difference in walking speeds with higher walking speeds on wider stairways. The mean descending walking speeds are 34.33m/min and 37.90m/min on 2.0m and 3.6m stairways with inclination 30o.  
+Pedestrian level of service on passageway and stairway are determined for the foot over bridges. Comparison of space occupancy with HCM 2010 and TCQSM 2007 showed that the space occupancy thresholds for various LOS are lower for passageways in intercity railway stations than those in HCM with the minimum space required is similar for LOS F and are higher than those of TCQSM. The pedestrian space requirement is higher on passageway in India than in China.
+Comparison of pedestrian LOS on stairways showed that the minimum space requirement per pedestrian is observed to be higher than those of Chinese and Americans. This is because the LOS standards defined for the in the earlier studies are for unidirectional stairway (ascending direction) and for the metro stations where the daily commuters with no/less luggage are more in proportions. The LOS thresholds are in higher range to those of sub-urban railway station. Whereas pedestrian in intercity railway stations are mostly luggage carrying making long hauling trips with various trip purposes and are not frequent visitors or users of railway stations. Hence the higher space are required to cater for the luggage and individuals require more room for free movement.
+To understand the perception of pedestrians in making a choice between stairway and escalator to ascend a passageway, six videos each of a minute are cropped form the video recording data of pedestrian flows collected on the six stairways in the three intercity railway stations. A questionnaire survey form is prepared to collect respondent’s stated preference in choosing between stairway and escalator for the excerpts. Questionnaire includes respondent’s characteristics such as age, gender, educational qualification, employment status, marital status, and frequency of visiting railway station. A binary logit model is developed and the model included the variables like pedestrian age, gender, qualification, employment, marital status, frequency, inclination, and time of day.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The increase in traffic growth rate leads to an increase in congestion and accidents at signalized intersections. The design and evaluation of signalized intersection play a vital role in improving the performance of traffic operations in urban roadway network. Excessive queue is formed at approaches of signalized intersections if the demand exceeds the saturation flow rate or when the service rate is less than the arrival rate. The analysis of vehicular queuing at approaches of signalized intersection is inevitably required in order to improve the quality of service in traffic flow operations at signalized intersections.
+The present study is aimed at quantifying and analyzing the queue formation at the approaches of signalized integrations in India. The field data collected at selected signalized intersection is used to analyze the appropriateness of different methods available in literature to quantify the queuing of vehicles at approaches of signalized intersection under mixed traffic conditions. Quantification of vehicle queue using queueing theory and Highway Capacity Manual (HCM 2010) revealed that the applicability of these methods is very limited under Indian mixed traffic conditions. The study develops the best suitable models for predicting number of vehicles and length of queue at the intersection approaches by identifying the influencing factors in the field. The queue length models suggested in the study incorporate factors such as approach width, volume, signal timings, vehicle types dimension and their proportions. Statistical test confirms the validity of the proposed model on the signalized intersections have similar characteristics. A new criterion is developed for defining the LOS at approaches of signalized intersections by taking queue length as a measure of effectiveness. The appropriate ranges of queue length are suggested between A to F LOS labels. Further, microscopic simulation model VISSIM has been deployed to simulate operations of signalized intersection for analyzing queue length under different traffic volume and vehicle mix after calibrating and validating model parameters based on field queue length, roadway parameters and traffic data.
+At certain traffic, the influence of vehicle composition on simulated queue length has been observed. Simulated queue lengths are obtained by adding the proportion of other vehicle types to the all-car traffic stream. With a proportion of other vehicle types as the second class of vehicles in the traffic stream, the percentage increase in simulated queue length values are found. The level of service evaluated using VISSIM is contrasted to the LOS calculated using  observed queue length. The criteria proposed in the study could be incorporated in the INDOHCM (2017) manual for analysing queueing behaviour and evaluating operational performance of signalised intersection. The present study suggested methodology for estimating the number of vehicles accommodating in queue formed at an approach of signalized intersection operating in a non-lane based higher volume conditions.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The total road network in India is 64 lakh km, out of which about 90% are bituminous (asphalt) roads. Bituminous concrete, a dense-graded asphalt mixture is widely used in the construction of wearing courses in flexible pavements. Moisture sensitivity of asphalt mixture is the major cause of premature failure. Various additives are used to increase the service life of asphalt pavements and to mitigate moisture damage. Warm mix additives and hydrated lime are two well-accepted additives. The use of warm mix additives in asphalt mixtures reduces emissions during production and maintains required workability at reduced temperatures. Due to the reduced rate of aging of warm mix asphalt binder, warm mix asphalt mixtures are expected to exhibit enhanced fatigue resistance compared to hot mix asphalt. However, the fatigue life of warm mix asphalt can reduce due to the potential for increased moisture damage. Traditionally, hydrated lime has been used as an antistripping additive. Hydrated lime is a non-commercial additive which is widely used in hot mix asphalt as filler and an anti-stripping agent due to its availability and cost-effectiveness over other additives. Hydrated lime changes the surface chemistry of the aggregates and thus results in stronger adhesion between aggregate and binder. Thus, the presence of hydrated lime in asphalt mixtures enhances its moisture resistance apart from reducing the aging. However, due to the filler effect of lime, the increase in stiffness is expected to reduce the fatigue life of the asphalt mixture. The fatigue performance of asphalt mixtures consisting of such a combination of additives especially when subjected to moisture conditioning process is not well understood. Thus, there is a need to quantify the precise role of hydrated lime on the fatigue life of unconditioned and moisture conditioned hot mix asphalt and warm mix asphalt.
+This study quantifies the influence of moisture damage and hydrated lime on the fatigue life of large-sized prismatic beam specimens of hot mix asphalt and warm mix asphalt. To moisture condition large-sized prismatic beam specimens, a moisture conditioning process is initially established. Such beams are required for evaluating the fatigue characteristics of asphalt mixtures in a four-point beam bending test. The current moisture conditioning protocols are aimed at cylindrical specimens alone and no guidelines are available for prismatic beams; especially when these beams are compacted to lower air void content. In this study, prismatic beam specimens of bituminous concrete mixed with VG-30 binder were prepared. Warm mix asphalt was produced using a surfactant based warm mix additive.
+Hydrated lime was added to both hot mix asphalt and warm mix asphalt. Prismatic beams with target air voids of 4 ± 0.5% and with dimensions of 0.38 ± 0.006 m (length) × 0.050 ± 0.002 m (width) × 0.063 ± 0.002 m (height) were produced. These specimens were subjected to partial vacuum saturation by submerging completely in water. The vacuum pressures and durations were adjusted such that the desired saturation could be achieved. The saturated bituminous concrete beam specimens were mechanically weakened through the freeze-thaw conditioning. It is observed that the influence of additives is negligible on the degree of saturation. Both unconditioned and moisture conditioned specimens of hot mix asphalt and warm mix asphalt with and without hydrated lime were subjected to fatigue testing using four-point beam bending at three strain levels (400, 600, and 800 microstrain). The collected data was analyzed appealing to various post-processing methods, and it was seen based on the evolution of flexural stiffness and energy dissipation that the beneficial effect of warm mix additives or hydrated lime was witnessed at lower strain level (400 microstrain) and not at higher strain levels (600 and 800 microstrain).
+This study also quantifies the effects of moisture and hydrated lime on viscoelastic dissipation and dissipation due to damage in both hot mix asphalt and warm mix asphalt. Three models are used to separate damage dissipation from total dissipation. The pseudostrain concept, constitutive assumption approach, and a linear viscoelastic model (Burger's model) are used to compute damage dissipation. The sensitivity of the three approaches on moisture damage, the addition of warm mix asphalt additive and hydrated lime, and the effect of three strain levels (400, 600, and 800 microstrain) are analysed based on the proportion of damage dissipation. The Burgers model is found to be sensitive to moisture damage, warm mix asphalt additive, and hydrated lime at all strain levels. In summary, moisture conditioning process to saturate large-sized prismatic beam specimen to be tested for fatigue is established initially. Subsequently, the influence of moisture damage and hydrated lime on fatigue life of hot mix asphalt and warm mix asphalt is quantified based on the evolution of flexural stiffness and energy dissipation. Finally, the total energy dissipated is apportioned into viscous dissipation and dissipation due to damage using three approaches.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urbanisation is taking place rapidly all around the world. Urban population will be two thirds of world’s population by the year 2050. Because of urbanization there is noticeable impact on social, environmental and economic conditions in positive and negative manner as well. As population increases, need and dependency on private vehicles increases. So, increase in private vehicles on urban roads leads to negative impact on the environment and quality of life. Achieving sustainability in urban lives is the biggest challenge for urban transportation planners. From the past few decades, it has been proved that, Transit-Oriented Development (TOD) can be a tool for achieving sustainability as TOD will be addressing the sustainability aspects like socio, economic and environmental.
+TOD is a well-known concept for more than five decades; however research is still going on and has seen resurgence in recent years. Developing countries are trying to establish their own policy, design and implementation strategy for TOD. Hence, the research work is mainly focused on developing a framework for Implementation of TOD in developing countries. By looking at the ground realities and understanding of existing situation, an attempt is made to know, how TOD can be implemented and what are the possible ways to incorporate TOD concept into current urban scenario? To address these queries, in this research a frame work for implementation of TOD is proposed. The proposed framework consists of several steps in sequence as follows:
+To carry out the analysis and application of the framework of the present study Hyderabad Metropolitan Area (HMA) is selected. Based on the population and employment densities across the study area, it is divided into urban and sub-urban area to have more sensible approach. First phase is identification of feasible TOD locations: In this step, Spatial Multi Criteria Analysis (SMCA) is adopted to identify the most important/feasible TOD locations for urban area (within GHMC). SMCA process involves four layers of data viz., transit network, traffic flow characteristics of road, bus network and land-use details. As a result of this analysis, a total of 34 urban TODs are identified. In a similar way, analysis is carried out for sub-urban area (rest of HMA) and a total of 35 sub-urban TODs are identified. The 34 urban TODs are further processed to typology in next step. Also, an attempt is made to rank/prioritise all the TODs present in urban area by using Analytical Hierarchy Process (AHP). This will help the authorities to make decisions in stage wise implementation process.
+Further, TOD typology is performed at two different levels, one is at city level and other is at sub-area level, for better understanding of exiting built-environment conditions. A city-level typology is performed by considering 34 urban feasible TODs by using four criteria’s namely urban morphology, transportation system, built environment, and land use. As a result of this analysis, 23 types of TODs (or urban forms) are categorised. Further, based on this data a TOD priority strategy is drawn to ease the decision making process of the authorities. Also, an attempt is made to derive sub-area level TOD typology for Gachibowli-Hitech city Area (GHA). To perform this analysis, parameters considered are Mix land use Index, Plot ratio, Proportion of Transport Area, Development Mix Index, and Intersection Density. K-Means clustering technique is used to categorise identified 20 TODs in GHA and as a result of it five clusters (namely activity centre, balanced, commercial, mixed use, residential neighbourhood TODs) are formed. Design proposals and implementation strategies are suggested based on typology derived. The design parameters such as plot ratio, development mix, land use mix index, affordable housing, and proportion of transport area, NMT facilities, and open space preservation are considered to strengthen the TOD area. Subsequently, a schematic generalized TOD model is developed to address the identified challenges (viz., local markets, parking, traffic circulation etc.) for Indian dense cities context.
+In final stage, TOD Index is measured for GHA to evaluate the design proposals. For calculating the TOD Index, parameters considered are transit facility capacity, density, economic development, land use diversity and street design. For these parameters, weightages are assigned based on their role in making successful TOD. Calculating the TOD Index before and after proposals would give the exact improvement happening based on given proposals. As a result of it, an average of 22% increase in TOD Index is observed based on before and after design proposals. And also, an attempt is made to know the impact of TOD via, property value assessment through percentage change in residential property value. Thus the proposed framework implemented on Hyderabad Metropolitan area and the results obtained are satisfactory. So, the research methodology can be applied to any dense cities in developing countries.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urban arterials exhibit deteriorated capacity and poor level of service in many developing countries in recent times. The increase in vehicular population on urban roads is one of the major reasons to reach the congestion stage which exhibit a picture that the roadway is not able to cater the higher demand. In addition to the vehicular population, interference of the road side activities with the ongoing traffic flow is another major cause for deteriorating performance of traffic flow characteristics. These road side activities usually occur on edge of the road or on the shoulder or sometimes on the carriageway itself at dense urban streets which is referred as side friction. Side friction includes presence of several activities such as pedestrain movement, street vendors, bus-stops, auto-stands, on-street parking etc. Some of these activites may occur for some time of the day or the whole duration of the day and sometimes these activities cover certain width of the road. The interaction of these activities with traffic stream affects the ongoing vehicular traffic flow behavior and results in deteriorated capacity of the urban arterials. Therefore, the present study attempts to analyse the presence of side friction and its impact on traffic stream parameters such as stream speed, PCU values of subject vehicle types, and roadway capacity.
+Field data was collected on different locations of the multi-lane divided urban roads at midblock sections in two cities of India namely Telangana and Andhra Pradesh. The videography technique was used for collection of traffic flow data on four-lane and six-lane divided carriageways. Roadside friction data were also recorded during videography survey along with traffic flow data. Although there are sevral side friction activities present on the roadway but some of them cause reduction on traffic flow performance. The factors considered for present study include pedestrian movement on the road, parking manuovers, entry-exit vehicles and wrong movement of vehicles. All the side friction parameters are quantified though regression analysis and provided with weighing factors for each of the side friction activity. The influence of the total side friction on stream speed at selected study sections is analysed and further classified into various levels from very low side friction to high side friction. It is found that the reduction in stream speed is quite significant at medium to higher levels of side friction. However, no significant change in stream speed is observed at low levels of side friction. Speed-prediction models are proposed as a function of traffic volume and side friction and validated with field data.
+As there are six different vehicle types such as car, motorized two wheeler, motorized three wheeler, Bus, light commercial vehicle, non-motorized vehicles identified in the field. The PCU values of all vehicle types have been examined to check their sensitivity under various factors namely traffic volume, side friction, proportional shares and carriageway width. The study established linear relations to predict PCU of subject vehicle types through multiple regression analysis under various factors affecting it. The study also deploys the soft computing method as an adaptive neuro-fuzzy inference system (ANFIS) to model and optimize PCU of selected vehicle types based on specified criteria. A comparative analysis showed that the PCUs suggested by ANFIS model are yielding better reliable values than that conventional multiple linear regression (MLR) model values on low to high side friction levels. The study finds side friction is a noticeable factor that causes a significant change in the PCU of a vehicle type and capable of altering traffic flow measurements.
+Further, influence of side friction on capacity of the urban mid-block sections has been analysed. Capacity values of the selected road section are determined by developing speed and volume diagram. The capacity of section with very low side friction is determined and reductions in capacity values are estimated. It has been observed that the reduction in capacity is found to be significant at various levels of side friction. The carriageway width is another parameter identified as influencing the capacity of roadway section to a great extent. Study suggested adjustment factors for determining road capacity based on side friction and carriageway width. Further, capacity model for the multilane divided urban roads is proposed in the study considering lower to higher side friction levels, prevailing traffic and roadway conditions.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due to the rapid development of infrastructure, there is a depletion of natural resources of pavement materials. Aggregates are the primary raw material for pavement and building construction. The world is facing a scarcity of availability of excellent quality aggregates, which increases the cost of construction. With these shortcomings, there is a search for alternative materials. Alternative materials include recycled materials, wastes from the industries etc.
+In the current study, two types of recycled materials, namely Reclaimed Asphalt Pavement (RAP) and Recycled Concrete Aggregates (RCA), are used as a base course material in the pavements stabilizing with cement and emulsified asphalt at various stabilization levels. The stabilization levels include low, medium and high (2.0%, 4.0%, 6.0%) in cement stabilization. For Emulsified Asphalt stabilization, at the lower side, at the optimum and higher side of optimum emulsified asphalt contents were considered. The recycled aggregates are replaced with Virgin Aggregates (VA) in various proportions (1:1, 1:3, 3:1) along with recycled aggregates alone and compared with VA in the case of Cement Treated Bases (CTB). Whereas five mix proportions were considered for Emulsified Asphalt Treated Bases (EATB), in which three are RAP-VA blends (25% RAP, 50% RAP and 75% RAP) and two are RCA blends (25% RCA and 50% RCA)
+From the laboratory performance evaluation, the compaction characteristics, UCS, ITS, and fatigue life of CTB are significantly influenced by the RAP content in the mix. RAP and RCA bases require more than 6% cement content or 28 days of curing period to serve as pavement bases according to the Indian specifications. Self-cementing properties and Heterogeneity nature is observed in cement-treated RCA bases. The fatigue life is maximum at the 6% cement content and the 25% replacement of recycled aggregates than other combinations. In the case of EATB, RAP content emulsified asphalt content influence the bases' fatigue and permanent deformation characteristics. The residual binder content present in the mix significantly influences the rutting characteristics. The lower side of optimum emulsified asphalt content is suitable for the mixes having 50% or more RAP content. The sensitivity towards emulsified asphalt content is significantly less for EATB prepared with RCA. Treated bases reduce the overall thickness of the pavement and save the conventional aggregate materials.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport and Communication are the essential part of any country's development. In India the road passenger transport accounts for 80% of total land transport and the growth of passenger traffic is estimated to be more than 12% per year. The State Transport Undertakings (STUs) were set up under the RTC Act 1950 to provide an efficient, adequate, economical and properly coordinated transport service and in doing so carry on its activities on business principles. They have been particularly bedevilled by the dichotomy of the competing claims of profit maximisation and service maximisation. While on one hand the social responsibilities were being heaped on these undertakings, they were being subjected to trenchant criticism for accumulation of losses. The result was that STUs ended up blaming the burden of these social responsibilities to cover their internal inefficiencies and lack of growth. The productivity of any organisation depends mainly on the utilisation of three resources viz. Capital, Material and Human. Out of these the last resource is the most important factor of production that activates other resources and keeps the wheel moving.
+The Indian STUs are holding fleets over 1,18,000 and employing more than 7.9 lakhs of people. This shows that the STUs are labour intensive organisations and moreover it spends 65% of the total revenue for manpower. But it incurred a total accumulated loss of 14,048.70 crores till 2003. The virtual lack of dedication, poor concern for economy in expenditure, absence of real stakes on the part of sizable proportion of employees in the day to day functioning of the STUs are the major handicaps coming in the way of efficient operation. The capital contribution provided by the Central and State Government declined since the beginning of the last decade and the STUs were expected to manage their finances through their own resources. It is absolutely essential for the future survival of the STUs to figure out ways to improve their productivity and profitability. Therefore STUs are in a position to depend on and develop its manpower and their efficiency and effectiveness in order to achieve the organisational goal.
+The purpose of this research is to propose an integrated approach of optimising the STUs resources with a target of improving their profitability. This study has made an attempt in modelling the efficiency and effectiveness performance indicators of the human resource of the STUs to predict and optimise the profit at all levels of its operation.
+Since the STUs are working in heterogeneous conditions, any performance modelling will be impeded without their classification. Separating the STUs into groups based on their performances means that the members of the same group are more similar to each other than to members in the other groups. Any model constructed with homogeneous group data will have a good prediction capability. Cluster Analysis is an efficient tool for this purpose and hence used for dividing the STUs with respect to their characteristics. To locate the appropriate model to be applied for a new STU or a bifurcated STU, a classification procedure is prescribed and this classification procedure is efficient in its prediction. Discriminant Analysis is applied for the purpose of establishing this classification, which also extracted performances predominant in differentiating the groups.
+Factor Analysis is employed to explore the original underlying factors of the performance of the STUs. This analysis discloses the performances to be optimised and the performance to be achieved. The conventional models employed for the purpose of predicting the profit level and its optimisation is based on some assumptions between the predicting and predictor variables. Also while testing their statistical validity, it may lead to the omission of some variables, which may carry some important informations though they are minor. Therefore Artificial Neural Network is used to build a model for performance optimisation, which is having the advantage of mapping the complex nonlinear relationship without making complex dependency assumptions among input and output parameters. Also omission of any information is not effected in Artificial Neural Network for the want statistical validity.
+The above methodology is applied to optimise the performances of the STUs in India. The study divides the STUs into 5 peer groups and an efficient classification function has been evolved. The factor analysis divides the entire performance measures into 5 factors. This factorisation directs the performances to be treated. ANN captured the relationship between Revenue and Cost factors with the Manpower factors. The partitioning the weights of this ANN reveals that Manpower efficiency and effectiveness are predominant in determining the Revenues and Costs of the STUs. The performances of Andhra Pradesh State Road Transport Corporation and Jeeva Transport Corporation of Tamil Nadu has been taken for optimisation to a state of 'no loss – no profit'.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“Future Follows Past” is the key for the time series forecasting. The present study aims at developing a strategy for traffic forecasting using the principles of time series modelling.
+With the irreversible path of economic liberalisation in India, it is expected that the next millennium may experience a 7% growth in GDP as against the current 6%. Consequently, transport demand growth of around 14% per annum is expected, most of which is to be served by highway sector. Added to this, increased vehicular ownership has been contributing to higher vehicular movements on the highways.
+Future traffic estimates form the basic input for decision making in highway design, operations or maintenance. Decisions influenced by inaccurate traffic forecasts may result in economic losses. The magnitude of such losses will be enormous in view of large-scale investments involved in highway system development.
+Traffic, an economic outcome, is highly complex with inherent random fluctuations. Hence, modelling should account for the random variations which is possible only through the quantitative forecasting techniques, either causative or time dependent. However, due to constraints of data availability for causative forecasts, time series modelling, which is reasonably accurate, has become popular.
+A critical review of literature has revealed several approaches ranging from simple to very complex formulations. With the knowledge of the applicability of suitable models based on literature review, it is proposed to attempt traffic forecasting through univariate as well as multi variate techniques.
+In addition to the conventional EWMAM and ARIMA techniques in the family of univariate models, Modified Seasonal Auto Regressive Moving Average (MS ARMA) and Combined Forecasting (CF) have also been tried, the former to overcome the complexity in the multiplicative form of ARIMA, while the later to take advantage of combination of two forecasting methods for improving the accuracy of the forecasts. As stated already, a multiple time series forecasting strategy (MULTISEF) is also suggested in the present study to reflect the impact of economic developments of the surroundings on the traffic coming on to the highway at any specific location.
+Unless traffic data is available on a continuous basis for reasonably longer periods, use of even highly sophisticated modelling techniques may fail to give accurate forecasts. Realising this, the Ministry of Surface Transport (MOST), Govt. of India has initiated a research scheme R3, Phase-III, "Establishment of Permanent Traffic Counting Stations (PTCS) on National Highways in Andhra Pradesh" and entrusted the task of establishing PTCS to the Centre for Transportation Engineering, Regional Engineering College, Warangal. Accordingly, at three locations, one each on NH5, NH7 and NH9 in Andhra Pradesh, Automatic Traffic Counters cum Analysers (ATCA) have been used and continuous round the clock classified directional traffic volume data is collected. Even though, traffic data at all the sites is available, the data collected at Sher Mohammed Pet has been taken for demonstrating the proposed modelling approaches in detail.
+For the proposed multiple time series forecasting (MULTISEF) strategy, entire country is divided into 15 zones following the standard principles of zonal delineation. Data such as population density, agricultural area, agricultural output, number of industries, industrial output, number of workers, number of vehicles and GDP from all the zones, during the study period (1993 to 1997) has been compiled from the secondary sources like NIC-NET, Bureau of Statistics and census reports. In addition, Origin-Destination (O-D) information is collected through the conduct of roadside interviews organised at four different locations covering the entire stretch of Hyderabad-Vijayawada on NH9. Traffic contributions from each of the zones on to the link at Sher Mohammed Pet are extracted.
+Multiple time series regression models with lagged values of predictor variable set (independent variables) and time series traffic data as criterion variable (dependent variable) are developed and the model, which is statistically more relevant has been taken for forecasting. ARIMA models are fit separately for each individual independent variable. Computer programs have been written for calibrating and forecasting using the models developed in this study. With the help of the calibrated model parameters, forecasts are made for a horizon period of 1 year and validated by comparing with the actual data, exclusively set aside, using the standard statistical tools namely Percent Error (PE), Mean Percentage Error (MPE), Mean Absolute Percentage Error (MAPE), Theil's U-Statistic, Mc Laughlin's Batting Average (MBA) and Durban Watson (DW) Statistic. For multiple time series forecasting models, the values of the independent variables for the year 1997 are obtained through the ARMA models using the time series information of the respective variables. These values are used to get daily traffic volumes.
+It is observed that the modified additive seasonal ARMA (MS ARMA) process is out performing all the univariate methods except the combined method based on Error Variance criteria (CF2). Another highlight of the suggested MS ARMA is that the DW statistic is observed to be close to '2' in comparison with other methods, indicating near white noise series. In case of MULTISEF, with U-statistic less than 1 and MBA value greater than 300, clearly indicate that the forecasts obtained through this method are better than the naive forecasts. The DW statistic is almost equal to 2 indicating that the errors (residuals) are purely random without any patterns remaining in the data. In addition, MAPE is observed to be only 9.4%, which is small enough to make the approach acceptable.
+Sensitivity analysis is carried out by varying the rate of change of the three independent variables considered in MULTISEF viz. population density, agricultural output and industrial output from 0.5 to 2.0 @ 0.1 intervals, with all possible combinations, to obtain the rate of change of traffic. Tables and nomograms are developed with a view to make them useful to find the rate of change of traffic, given the rate of change of the independent variables observed in any given year with respect to the base year.
+It is hoped that, the highway sector getting unprecedented impetus with several developmental plans such as Golden Quadrilateral, State Highway projects with external assistance, the proposed forecasting strategy will be of utmost use in arriving at appropriate decisions that involve huge investments for the benefit of the community at large.
+</t>
+  </si>
+  <si>
+    <t>Behavioural Mode Choice Models for Intercity Rail-Road Passenger Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In this study, intercity rail-road passenger mode choice behaviour is modelled, incorporating user perceptions, so as to suggest various policy options to realise required modal mix in a given region. Intercity transport directly affects urban as well as regional transportation with strong and positive relationships between travel and socio-economic activity of the city pairs. The share of passenger trips within a given intercity corridor among the available modes of transport is of great importance in planning intercity transport services. Although it has been recognised that the road transport has to be encouraged for short travel and railways for long distance trips, no procedure has been suggested to demarcate the threshold limits for short and long distance passenger trips. The disaggregate analysis provides the basis for improving understanding of intercity passenger travel behaviour and in developing behaviourally consistent models of mode choice.
+Review of literature has revealed that there is no standard or agreed method of segmenting of intercity passengers for model development. Moreover, sample size used for model calibration in almost all the studies is considerably small. Most of the investigations, abroad, have segregated the trips either by trip length or by trip purpose, but have not integrated both the criteria. Except for a few, all the investigators of intercity passenger travel have employed objective measures like time and cost variables, but have not considered passenger attitudes, whose inclusion is found to be pertinent because of the spatial distribution of cities. This study is an attempt in addressing the various aspects of intercity passenger mode choice behaviour and to arrive at an appropriate policy on modal mix, particularly between rail and road transport.
+A review of the contemporary research in the field has offered an insight into the advantages and limitations of each modelling technique for the study on intercity mode choice behaviour. The Dogit model formulation, which has the ability to circumvent Independence of Irrelevant Alternative (IIA) restriction in Logit model, is employed in this study. Passenger data on attitudes like comfort, convenience etc. are obtained on psychometric rating scale. User perceived relative weights for various attributes are quantified using the method of successive categories. It is hypothesised that distinct market segments exist, which are formed based on trip length, income and trip purpose. An user-friendly computer program, “WAGIT” is developed to test the proposed methodology.
+Two major transport corridors of Andhra Pradesh, wherein competition exist between rail and road transport, have been chosen for a detailed study. Primary surveys are organised in 13 cities to elicit socio-economic, travel and attitudinal data from both train and bus passengers. Preliminary analysis has been undertaken to isolate the causal factors affecting the intercity mode choice behaviour. Mode choice models are then calibrated for different segments of passengers based on Dogit as well as Logit model formulations. It is found that the ability of Dogit models in explaining mode choice behaviour is better than that of Logit models, for all the segments of travel. These models are further examined for their validity in respect of statistical goodness of fit.
+Finally, models for low, middle and high income groups for short, medium and long distance travel are selected based on Dogit model formulation. Ingress time is found to be significant along with other variables for short travel, while comfort and frequency of service are the most significant variables for long distance travel. All the models are validated for their predictive ability in the study area. The effect of sample size on model coefficient estimates is also examined in this work.
+Geographical transferability of intercity mode choice models is tested by dividing the study area into three corridor regions and then segmenting the travel market in each region by trip length. Dogit models have shown better transferability potential compared to Logit models. Even though the models are not transferable as a whole, comfort variable shows potential for transferability. Segregation of intercity passengers has enhanced the ability of models to be transferred from one area to another. In general, it can be concluded that the models are geographically transferable based on their predictive ability criteria with reasonable percentage error.
+Probability surfaces of choosing the train are constructed for several combinations of significant explanatory variables by varying them within a specified range. By using these surfaces, bus share contour diagrams are drawn so as to identify various policy options to realise required bus share for short and medium distance intercity passenger travel.
+The present work suggests that the disaggregate modelling approach offers better explanation of intercity passenger mode choice behaviour. Models calibrated based on Dogit model formulation explain more variation existing in the data, compared to Logit models, even in a binary mode situation.
+The limitations that still exist in the proposed methodology are then presented and scope for further research is identified.
+</t>
+  </si>
+  <si>
+    <t>Strategic Planning To Model Urban Growth At  Regional Level Using Gravity -Oppurtunity  Technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Till date cities are planned as individual entities and treated as isolated points. But the mechanisms at work reflect interdependencies through spatial processes of diffusion and interaction promoting the concept of "system-of-cities" oriented towards slowing down primate city growth and inducing necessary growth impetus by locating manufacturing industry near growth centres.
+In order to go about the process existing modelling techniques need to be modified to efficiently combine the effects of distance and opportunities through the formulation of Gravity-Opportunity models. These models overcome the deficiency of the gravity formulation wherein supply side aspects of phenomenon are not directly accounted for. Since the phenomenon of urban growth involves many aspects and all of them cannot be incorporated into the modelling procedure expert opinion apart from investor's and individual choice preferences in the form of domain knowledge is obtained to finetune the results of the model as well as assisting in the policy formulation and selection processes. In this study, Goal Programming and Analytic Hierarchy Process types of decision models are employed to select the alternative that fulfills the objectives most, overcoming the limitations of the subjective type of decision-making process.
+The impact of the changes in technologies especially transport and communications will and would have profound influence on the spatial setting of urban centres be it large metropolitan areas or small and medium sized settlements. The basic problem that is faced today is the "Locational Dilemma" It is concentration versus Dispersal. Steady changes have been triggered making major economic activities such as industry, trade and commerce more "foot loose" made possible by the logistical linkages that are offered by these technologies.
+With the expansion of basic infrastructure ations, power and water, spatial phenomena such as "diffusion" can be adopted to manipulate the location of manufacturing industry in such a manner that the population is efficiently arranged in order to contain the growth of cities.
+Against this background, this research is an effort not only to identify spatial mechanisms that can be adopted to formulate growth strategies that are responsive to the changing needs of managing urban growth, but develop a framework that is comprehensive in the field of "Landuse Transportation Planning" to accurately assess the impact of implementing a strategy.
+A review of the research effort thus far has been mainly oriented towards model building aspects using mathematical techniques. In this study, the landuse transportation interaction is investigated in detail to arrive at consensus of obtaining opinion of the three major players in the development of urban areas namely "the individual, (people) the investor (firm) and the expert (analyst)" becomes necessary. By this process a clear insight is obtained and accordingly a methodology is developed culminating in the form of a "spatial planning framework".
+Hyderabad, the capital city of Andhra Pradesh, the fastest growing metropolis of the country registering a decadal growth rate of 67% during 1981–91 is experiencing problems as any other city of the country. In order to alleviate the problems associated with such a phenomenon, a framework is evolved to assess the impact of alternate growth strategies that are formulated for the purpose of achieving an efficient arrangement of population and employment in the "influence region" of the city (a major deviation from the past practices of urban planning) by adopting a spatial setting of "System of cities" to integrate growth of the primate city with that of the lower order settlements in its influence region. The outcome of the study has been encouraging, reflected by the results that have been obtained.
+This research has established that gravity opportunity type of allocation function better than the gravity model which relies heavily on the deterrance parameters as can be observed from the allocation of population to the city and that of growth centres in proportion to the opportunities that are available. The logistics of the evaluation and selection process through the usage of decision models enhances the operational ability of the suggested framework together with the domain knowledge that is developed.
+The exercise becomes all the more relevant when the country is poised to have an urban population in the ratio of 4:7 in 2001 as against 1:4 in the 1990's. Being a leader among the developing countries, India is on the threshold of taking-off into the 21st century in a big way with urban growth becoming a bane than a boon. In order to take corrective measures, this research has been aimed at developing a methodology that is comprehensive, responsive and workable in approach. It is hoped that this methodology could be adopted to any city of the country since the cities of the future are perceived to be "pillars of a nation's economy".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transportation infrastructure is vital for the development of any country. Owing to inherent advantages of road transport, particularly in providing accessibility and connectivity, majority of the population depends upon road based transport. The road network is normally being planned and developed for fulfilling the requirements of transportation, keeping the total transportation cost in mind. In the process of network development, many a time, the alignment of road may have to be finalised through the soil subgrades, which may not be suitable to bear the traffic loads with adequate strength (Chandrasekhar et al, 1999). It has been established that the stability and performance of road is reflected by soil subgrade. Roads constructed on soils with poor strength and expansive in their character are bound to fail resulting in poor pavement performance and increased maintenance costs (Jones and Holtz, 1973; Steinberg, 1992).
+Expansive soils, such as black cotton soils, are basically susceptible to detrimental volumetric changes, with changes in moisture regime. In monsoon, they take up water and swell, and in summer, they tend to shrink on evaporation of water, thus posing the problem of alternate swelling and shrinkage. This behaviour of expansive soils is attributed to the presence of mineral montmorillonite, which has an expanding lattice.
+Among several techniques adopted to overcome the problems posed by expansive soils, lime stabilisation gained prominence during the past due to its abundance and adaptability (Snethen et al, 1979). However, it is reported (Chen, 1988) that lime stabilisation suffers from the major drawback of difficulty in soil pulverisation and mixing of lime with it. Recent studies (Ramana Murty, 1998) indicated that CaCl₂ could be an effective alternative to conventional lime due to its ready dissolvability in water and ability to supply adequate calcium ions for exchange reactions. Though, it is claimed that the magnitude of leaching in highly expansive clays is negligible (Frydman et al, 1977), it is felt that the possible leaching of CaCl₂ (Kuula Vaisanen et al, 1995) over cycles of wetting and drying could be controlled by using sodium silicate (Na₂SiO₃) along with CaCl₂.
+In the recent past, reinforced earth technique has been tried effectively in solving majority of geotechnical engineering problems (Hausmann, 1990). With the introduction of geosynthetics, the reinforced earth technique gained prominence due to its adaptability for varying field conditions. Few researchers have tried (Haas et al., 1988; Al-Qadi and Bhutta, 1999) to introduce geosynthetic reinforcement layer in the pavement system to improve its performance and the results are encouraging. In majority of the previous studies, the reinforcement layer is used either at the pavement-subgrade interface as a separator or immediately below the wearing course to control the rut and crack formation. Limited studies (Kinney et al., 1998) are also made by placing the reinforcement in one of the layers of flexible pavement system laid over conventional non-swelling subgrades. However, the results are not conclusive in respect of the type and placement of the reinforcement layer for overcoming the problems related with expansive soil.
+Keeping in view the research findings outlined above, in the present work, experimentation is carried-out to investigate the influence of calcium chloride and sodium silicate on expansive soil behaviour. Further, investigation was also carried-out to study the effects of location of reinforcement layer in flexible pavement system on the overall pavement performance in terms of strength as well as control of crack propagation. Keeping in view of the high cost of geosynthetics, a trial was also made to investigate the possibility of using cheaper alternative reinforcement materials like bitumen coated chicken mesh and bitumen coated bamboo mesh. A methodical process, involving experimentation in the laboratory under controlled conditions, followed by small-scale field experimentation and finally on the off-lane test track sections, was followed.
+The outcome of the present investigations is in-conformity with the earlier findings in respect of the suitability of lime as a stabilising agent. However the experimentation with strong electrolytes such as calcium chloride has indicated that 1% commercial grade calcium chloride solution has higher diffusion capability for better stabilisation. Further, it is observed that chemical stabilisation of expansive soil subgrades is possible by allowing diffusion of 1% commercial grade calcium chloride solution and 1% sodium silicate solution into the surrounding soil by merely filling the chemical solutions one after the other (without pressure injection) in the pre-bored holes for better results.
+The improvement of the pavement performance is cognizable for all the three reinforcement materials tried viz. geogrid, bitumen coated chicken mesh and bitumen coated bamboo mesh. Though geogrid and bitumen coated chicken mesh provide better interlocking of soil particles than the bitumen coated bamboo mesh, geogrid has scored over the bitumen coated chicken mesh with respect to improvement in the performance levels. Hence, further studies were carried-out with geogrid as the reinforcement material. Placement of geogrid in the subbase is found to be more effective in controlling the crack propagation compared to its location in the subgrade. The evidence is seen from the observation of the crack propagation for the section with geogrid in subgrade even during the first cycle of wetting and drying.
+It is observed from the test track studies that the maximum heave of the chemically treated stretch (Calcium Chloride - Sodium Silicate) is only about one-thirds of that observed for the other stretches. The chemically treated stretch has shown a decrease of 18% in the rebound deflection value, which could be due to the decreased subgrade heave and increased stiffness by cementation bonds due to calcium silicate gel formation. Further, the placement of geogrid in either the subgrade or the subbase/base course has resulted in insignificant reduction in heave values. The rebound deflection of the stretch with geogrid reinforcement in the subbase has decreased by 15% and 26% when compared with untreated stretch for dry and wet seasons respectively.
+Adaptability of any treatment for practical use depends entirely upon its structural performance and economic viability. Hence, detailed structural and economical analysis were carried-out for all the alternative treatments tried in the test track study. It is observed that "geogrid in subbase course" has resulted in maximum reduction in compressive strain followed by alternative treatments viz. "chemical treatment" and "geogrid in subgrade". The alternative of "geogrid in subbase" is more economical as it is giving maximum NPV and IRR values vis-a-vis the other alternatives. This alternative is closely followed by the "chemically treated subgrade" case.
+From the structural and economic analysis, the following rankings for different treatments are arrived at in the descending order.
+1. Geogrid in Subbase 
+2. Chemical Treatment 
+3. Geogrid in Subgrade 
+It is felt necessary that the above results need to be further investigated over on-lane test track with normal traffic operations, before recommending for implementation.
+</t>
+  </si>
+  <si>
+    <t>Freight Transportation is an important infrastructural facility that contributes to the national economy by linking the industrial and agricultural production with consumption. Highways and Railways are the most important modes for the freight movement at regional level. Accurate estimation of the transportation demand for freight movement is a prerequisite for developing efficient transportation systems. While the planning of Railway system is institutionalized, the Highway sector, being a monopoly of private undertakings and individuals, is least organized and unplanned. In controlled economies such as India, the share between these two major modes is more or less predetermined on the basis of other policy vectors.
 While developing the Highway transportation system it is observed that there are no established procedures to either quantify the travel demands or develop a network that satisfies the present or expected desires. The review of literature around the world has revealed that the Highway sector, though neglected, has an important role to play for the movement of expensive consumer goods, packed products, perishable commodities etc., while the Railways has exclusive advantages for bulk commodity movement over longer distances. It is also observed that little literature is available for scientific estimation of the highway goods movement which is a vital input for system development.
 An attempt is, therefore, made in this study to develop the highway freight transportation demand models at regional level by considering the basic mechanism of freight movement. The excess production, excess consumption and spatial separation of the regions are found to be the most important controlling factors for the regional freight transfers. In this context delineation of regions plays an important role for estimating the inter-regional and intra-regional freight movement. In this study a hypothesis has been presented to delineate the transportation regions for India together with a detailed discussion on the division of study area into micro regions. Hyderabad Region with 10 districts in its hinterland has been chosen for detailed study in this work.
 A pilot study was organised for quantifying the economic, social, demographic and transportation characteristics and a Factor Analytic study has been undertaken to isolate the basic causal factors affecting the Highway travel. On the basis of the findings a hypothesis is proposed to model the Highway freight movement as a function of the causal variables embedded in the mechanism of freight movement.                                       Detailed surveys have been organised in the region for measuring the actual Highway freight transportation that is explained subsequently through the calibration of freight transportation models on the basis of the proposed hypothesis. These models were examined for their validity in respect of statistical goodness of fit as well as predictive ability in the region. They form basic tools for forecasting the future flows for four different horizon years and three anticipated growth options of the region.
@@ -743,17 +1151,50 @@
 The limitations that still exist in the proposed methodology are then presented and scope for further research is identified.</t>
   </si>
   <si>
-    <t>sfdsdf</t>
-  </si>
-  <si>
-    <t>gchbcgc</t>
+    <t>The Transport Sector is an important sector of the economy and accounts for 14% of the total public sector outlay in the Seventh Five Year Plan of India, and while this allocation is grossly inadequate in relation to the massive needs of this sector, it becomes all the more important to ensure that the limited resources and funds available are utilised to the best advantage by obtaining maximum possible economies in the planning, investigation, designs and execution of Transport Projects, and in this task the development of methodologies and tools of analysis for exercising optimal choices in respect of both inter-modal and intra-modal problems in Transportation Planning and investment decisions has a major role to play so as to secure the best returns to the economy.
+A review of available world technical literature as well as literature on Project Appraisal, Investment Analysis, and Social Cost-Benefit Analysis, including World Bank literature, shows that while techniques are available for comparison and choice between any two alternative pre-formulated projects by calculation of Net Present Value, Internal Rate of Return, Benefit-Cost Ratio, etc., there are no methodologies available for optimal choice of decisive parameters at the stage of initial formulation of the Projects themselves, and in the absence of  such methodologies it can often happen that two inefficiently formulated Projects have been compared by the various appraisal techniques mentioned, and the less inefficient Project of the two chosen for implementation, while a more efficient Project superior to either of them has not been considered at all as it has escaped the stage of Project Formulation itself. A need thus exists for optimisation procedures and methodologies for arriving at optimal solutions. The present work seeks to fill this void in available literature and offers methodologies and solutions in respect of some of the important parameters involved. As such, it is a totally new and original contribution.
+The presently available methods of appraisal of Transport Projects have been brought together in a recent book by John W. Dickey and Leon H. Miller, "Road Project Appraisal for Developing Countries," published in 1984 by John Wiley &amp; Sons. Both the authors have worked on a large number of World Bank Projects, and they have been teaching at the Economic Development Institute of the World Bank and at Virginia Polytechnic and State University. The present thesis goes beyond the methods and approaches contained in this book and breaks new ground by presenting a new Unified Theory applicable to all modes of Transport.
+The author presents a methodology for optimisation based on the construction of Unit Cost Curves, which is applicable to a wide variety of problems in Transportation Planning, both inter-modal and intra-modal, relating to major investment decisions.                                                                                                                                                                                              Hitherto, no optimisation methodology has existed for determination of the optimal choice of important Civil Engineering Parameters in the location and construction of railways and highways or for determining the break-even levels of traffic density at which, for example, the construction of a highway is preferable to the construction of a railway, or within the same mode of transport whether we should adopt a two-lane roadway or a 4-lane roadway, or in the case of a railway whether to build a double-line versus single-line, or at higher levels of traffic density a 3-line (triple track) versus a double-line. Another case of choice is whether to double a Metre Gauge or convert the gauge. In all such cases of choice, the optimisation methodology developed and presented by the author presents a rational and universal method of choice by plotting the Unit Cost Curves for the proposed infrastructures, whether it be a road or a railway, showing the unit costs for each proposed infrastructure for carrying one passenger-kilometre or one tonne-kilometre at various levels of traffic density on that infrastructure and obtaining the break-even levels at their points of intersection.
+While the proposed methodology is universal, the present thesis deals at length with the optimal selection of Civil Engineering parameters in Railway Projects, and explains in detail the procedure for construction of Unit Cost Curves and Break-Even Analysis in respect of only two important parameters, viz., Gauge and Ruling gradient, on account of the constraints of time, effort, and paucity of data, but indicates the scope for further work in respect of the other parameters. The important topic of Upgradation of Metre Gauge in preference to its conversion into Broad Gauge is also covered.
+One important finding is that while, on the face of it, it would appear that the problems of optimal selection of Ruling Gradient and of optimal choice of Gauge are two altogether different and dissimilar problems and as a matter of fact in the past these two issues were so treated and dealt with separately, the unified methodology presented in this thesis shows that the problems are essentially identical and can be subjected to identical treatment under this Methodology. We also gain the additional insight that what is common to both the problems is the matter of train loads and train speeds. Just as a steeper Ruling Gradient means smaller train loads and lower train speeds as compared to a flatter one, the train loads and speeds on the Metre Gauge are lower than on the Broad Gauge, and thus in reality both the problems are identical, an insight which was missed in the past but which becomes crystal clear automatically in the analysis based on the Unit Cost Curves Methodology developed in this thesis. This further leads to the logical conclusion that upgradation of Metre Gauge so as to permit larger train loads and higher speeds on the M.G. will be preferable to B.G. conversion in the medium term, and conversion into B.G. will be justified only after still higher levels of traffic density are reached at a later date. Additional insights into the inter-relationships between Unit Costs and Train Loads and Speeds and Transport Capacity are also available in this methodology.
+ The actual data of expenditures on the B.G. and M.G. systems of Western Railway for the year 1983-84 (summarised in Appendix I) have been analysed and utilised for deriving the Unit Costs and constructing the U.C. Curves. In fact, this is for the first time in the long history of 135 years of the Indian Railways that such an attempt has been made to utilise available statistics and construct Unit Costs Versus Traffic Density Curves. Although the Indian Railways have an old and established statistical organisation which collects vast quantities of data and statistics, they are global or aggregated data and do not directly give the figures of Unit Costs or the costs of detentions to locomotives, coaches and wagons. Thus, this involved an enormous amount of work. Moreover, many of the costs are joint costs which have to be apportioned gauge-wise, traction-wise, and as between passenger services and goods services on the basis of certain ratios which have been evolved in the past by the Statistical Directorate of the Ministry of Railways. These ratios can be accepted as broadly correct. However, one important merit of the methodology of break-even analysis presented in this thesis is that within reasonable limits, changes in these ratios as well as other parameters do not have a major effect on the end results, viz., the break-even levels of traffic density which finally matter for the relevant investment decisions. This is because the break-even level of traffic density occurs at the point of intersection of the two Unit Cost Curves corresponding to the two alternative proposals, and this point of intersection shifts only within narrow margins even when the U.C. Curves themselves shift within a larger range. Thus with this saving grace, we find in this methodology a powerful tool of analysis which can be put to use for practical cases of investment decision even if the traffic costing data available are not quite perfect but within acceptable limits of accuracy. Even so, this is only a temporary expedient, and it is absolutely necessary to set up urgently a permanent data-collection and cost-analysis machinery for collection of accurate and reliable data on a continuing basis for all modes of transport. Certain refinements are necessary in the collection and analysis of Railway Statistics.
+The paper emphasizes the need for proper phasing of capital inputs for generating additional transport capacity progressively in such a way as to keep pace with the gradual building up and growth of traffic so as to minimise premature capital investments in the light of Discounted Cash Flow theory.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                Since the correct initial choice of the important civil engineering parameters discussed in this paper makes a very substantial difference to the capital costs as well as recurring operating costs of transportation projects, whether a road or a railway or any other mode of transport, it is necessary in the larger interests of our national economy to adopt this optimisation methodology on a wide scale in making investment decisions in respect of transport-capacity-generating projects, both in regard to inter-modal and intra-modal decisions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development of cities across the globe is unstoppable and it‟s very difficult to carefully plan cities. In this situation, understanding pedestrian movements is very essential for design facilities with respect to safety, security, level of service and low cost. Religious occasions, congregations at carnivals, political rallies, and crowd at terminals are occasions pertaining to crowd congregations. These congregations act as serious intimidations for the crowd, because a large number of people moving in limited space results in crowd stampedes. Most of the crowd crushes occurr in developing countries during large congregations and more people die when compared with developed countries (Andrade et al. 2006). Prassana Kumar et al. (2015) stated that on an average more than 70 people per year lost their lives due to stampedes in India. Indian states of Maharashtra and Andhra Pradesh are in top the list of more than 300 deaths in the 15 years (2001-15). Hence, it is very important to study crowd behavior to increase public safety. Understanding crowd behavior and the tools required to forecast crowd behavior are necessary in planning and design facilities such as bus terminals, train platforms, etc.
+Three locations were selected for the study: Location-1 is situated in Vijayawada, Andhra Pradesh, India, whereas Location-2 is situated in Medaram, Telangana, India and Location-3 is situated in NIT, Warangal, Telangana. Data was collected by placing digital camera on top of the building. The videos were taken from a high-raise point near the location to avoid occlusion problem during tracking. Camera stands were used to ensure the videos recorded were steady, without any disturbance that might affect the frames at various stages of analysis. Markings were made on the road sections. Distance measurements were made using a standard tape such that the speeds could be cross-checked while extracting data using software.
+Various parameters extracted from the video include people count, density, speed of individual persons, and crowd flow. Number of persons in a frame was counted using background subtraction technique. Speed and tracking of each individual were extracted using TRACKER software. Pixel coordinates were converted to real coordinates using the method of Wolf and Dewitt (2000).
+In microscopic analysis, parameters like age, gender, group size, child carrying, child holding, and people with and without luggage were considered. For statistical analysis, ANOVA and Pearson correlation tests were performed using SPSS. From these tests, it was concluded that, there was a significant effect of age, gender, density and luggage on the crowd walking speed. Gender has more significant effect on speed followed by luggage and age. MLR, ANN, ANFIS models were developed for the modelling of crowd speed using the above mentioned factors in the study. The developed model was validated using RMSE (Route Mean Square Error) and MAE (Mean Absolute Error) values. Based on RMSE and MAE values, ANFIS model was observed to be better-fitted model when compared to other models. Gender, density and luggage have a negative effect on speed of the crowd while age has a conflicting effect on speed of the crowd. The increase in number of female persons in the crowd leads to speed reduction. Generally, the speed of the female person is low compared to male. Density is found to have an adverse effect on speed, whereas, at low crowd density, the speed of the crowd was high due to fewer interactions between persons and more space for overtaking. The speed was observed to be low at high crowd density because of more interactions between persons and little space for overtaking. Further, it was observed that luggage has an adverse effect on crowd speed. The speed of people with luggage is low when compared to people without luggage. Children and the old people were negatively associated with crowd speed. Also, as the number of children and the old people increases, it was found that the speed of crowd decreased. Additionally, younger and elder persons were positively associated with crowd speed. As the number of younger and elder persons increased, the speed of the crowd was observed to be higher.
+In macroscopic analysis, flow parameters such as free flow speed (Uf), optimum speed (Uo), jam density (Kj), optimum density (Ko) and maximum flow (Qm) were estimated from the fundamental relationships. Flow–density and speed–flow relationships were then calibrated from the speed–density relationship. To determine the crowd characteristics, two single-regime speed–density models were used Model I - Greenshield‟s (L) and Model II - Underwood (E). Model I gave the minimum MAPE and RMSE values, which implies that Model-I gives better prediction than Model II for crowd movement. In real conditions, it is not possible to model the entire traffic mass as a single regime due to the existence of both uncongested and congested flow. A multi-regime model concept is thus essential to represent different flow conditions. For two-regime model, the speed–density relationship is developed for two regimes by introducing a breakpoint to distinguish between two different regimes. This breakpoint is identified by K-means clustering analysis using SPSS software. The final selection of the breakpoints was determined using a visual approach. Four models i.e., Model I, II, III and IV representing L-L, L-E, E-L, and E-E were used to determine the crowd characteristics in two-regime model. The minimum MAPE and RMSE values of the crowd characteristics (speed, density and flow) were obtained using Model III (E-L). Three-regime models consider uncongested flow, transitional flow and congested flow regimes. In three-regime models, the speed–density relationship is developed for three regimes by introducing breakpoints to distinguish between three different regimes. Four models i.e., Model I, II, III and IV representing L-L-L, E-E-E, E-E-L, and E-L-E were used to determine the crowd characteristics in three-regime model. Model-II (E-E-E), with the lowest MAPE and RMSE values when compared to all the four models, provided the best predictions. MAPE and RMSE values of the best multi-regime models were less than that of the best single-regime model. Therefore, multi-regime models provide better predictions than single-regime model. Of the multi-regime models, MAPE and RMSE values of three-regime models were less when compared to two-regime model, which implies that the three-regime model gives better predictions than two-regime models.
+In capacity analysis, buffer space is introduced in this study to study the influence of overtaking within the crowd while evacuation. Therefore, this study is divided into two cases: presence of buffer space and absence of buffer space. The height and length of the bottleneck are constant. Five varied widths of bottlenecks which consisted of 80, 100, 120, 140, and 160 centimeters repectively were chosen. In this experiment, 30 and 50 individuals were involved in two different compositions. The evacuees were divided into two groups and assigned different walking responsibilities for every test (move slowly, and move fast). The groups were diverse and comprised male and female. Since the entire group of 50 was of same age group, the group was divided so as to incorporate the effect of age variation within the group. One group of evacuees was designated by the colour of their caps (white). Whereas, persons without caps represent normally acting participants, while the persons with caps follow specific instructions.
+The first step in density estimation was the conversion of video into frames, and the next step was to divide the entire area (50 m2) into equal number of grids having a grid size of 0.5 × 1 meter. Further, using the manual count method, the number of persons in each grid was noted, and finally, the average values of densities (people/area) for all frames in each grid were computed. The whole study area was divided into grids, in order to calculate the density in each grid because it was not uniform throughout the study area. This also gives us an idea of the path/ route of evacuation chosen by most individuals at the time of evacuation. In crowd analysis, another issue involves the tracking of people and finding the location of the same person in a series of images. For this a free open source software TRACKER was used, which tracks persons semi-automatically.
+From the experimental study, total time, time gaps, flow, specific flow and densities were extracted. It was observed that the total time decreased as the bottleneck width increased, for both compositions in cases with and without buffer space. The buffer space effect in the reduction of total time was more in case of 50 persons, when compared to 30 persons. It was observed that flow increased as the width of the bottleneck increased, and this increase in flow is due to the formation of dynamic layer, as noted by some researchers in their studies. It was observed that, specific flow was decreasing as the width of the bottleneck increases and specific flows were more for without buffer space as compared to with buffer space. Trajectories were plotted in order to know the route choice of each individual throughout the evacuation period in the study area. It can be identified that lateral occupancy of persons is more in the case of without buffer space as compared to with buffer space, for both compositions (N = 30 &amp; 50).
+Arching phenomenon was observed at the entry of exits; this was apparent when a crowd with highly anticipated speed tries to pass through a door in limited amount of time because of which the exit gets congested, and the crowd becomes arc-shaped. It can be observed that densities were decreasing as the width of the bottleneck increased. Density value was observed to be higher for groups of fifty, when compared to groups of thirty people for the same width of bottleneck. High densities were observed near the bottleneck opening when the flow gushing in goes beyond the capacity of the bottleneck, leading to jamming at the bottleneck. It can be observed that, flow of crowd increases as the width of bottleneck increases and this increase is stepwise, and not linear. When the crowd enters the bottleneck, formation of lanes occurs inside the bottleneck as width increases due to zipper effect. For a width of 80 cm, formation of lanes is absent. As the width increases from 80 cm to 100 cm, two lanes were formed and these lanes were continued and laterally expanded up to a width of 140 cm. For a width of 160 cm, it can be clearly observed that three lanes were formed. It can also be observed that the distance between these lanes does not influence bottleneck width (B).
+Five types of distributions (i.e., exponential, displaced exponential, Gamma, displaced Gamma and semi-random) were tested to cover the random, intermediate and composite headways. Five types of distributions mentioned above have been compared with the observed data and tested with goodness of fit (χ2 test). It was found that, among five types of distributions, semi-random distribution is observed to be the best fit for the observed data. The percentage of constrained headways (ϕ) observed in case of 50 persons was more than that of 30 persons. This implies that free flow decreases with increase in number of persons. In order to estimate the capacity of bottleneck, Buckley model is used. It can be observed that, capacity of bottleneck increases as the width of the bottleneck increases and this increase in capacity is because of the dynamic layer formations due to zipper effect. It can also be observed that, capacity of bottleneck with buffer space is more compared to capacity without buffer space. The obtained capacities were compared with capacities from different experimental studies done in relation to pedestrian flows at bottlenecks. For comparison, Kretz and Muller studies were considered because of their similarity with this study. Capacities obtained in this study were lower than that of capacities obtained from Kretz and Muller. The reason behind the reduction in capacities was Kretz and Muller didn't consider the formation of dynamic layers, hence the effective utilization of width concept was absent, resulting in larger capacities in their study.
+Further, the same experimental study area and participants were used for the estimation of capacity of doors. Five varied widths of the doors consisting of 80, 100, 120, 140, and 160 centimeters were chosen for single doors and doors of 100 cm width selected for double doors. Parameters such as total time, time gaps, and densities were extracted and analyzed in terms of various relations such as time gap versus door width, total time versus door width, and flow versus door width. Crowd trajectories and density plots were drawn for different door widths. Capacities were estimated both for single and double doors and comparison of capacities for different door widths was performed. Average time gaps and total times were observed to decrease as the width of the door increased, for cases with and without buffer space. In case of single and double doors, the total time was more in case of 50 persons than for 30 persons. Observations from trajectories have revealed a phenomenon called arching. In case of double doors, it was observed that evacuees were choosing the congested door rather than an uncongested one due to herding behavior. Herding behavior occurred when people were not making individual decisions but behaving as a group. In the evacuation scenario, herding behavior means that, the evacuees choose the most congested exit rather than the uncongested exit. Evacuees think that the congested exit is the most popular choice
+</t>
+  </si>
+  <si>
+    <t>DR.M.Venkata Ratnam</t>
+  </si>
+  <si>
+    <t>B. Raghuram Kadali</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2001/G.V.R Prasada Raju</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/2003/C.N.V. Satyanarayana Reddy</t>
+  </si>
+  <si>
+    <t>Professor in NITW(Civil Engineering)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -810,6 +1251,41 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -832,7 +1308,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -841,12 +1317,27 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1127,7 +1618,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1149,10 +1640,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1161,10 +1652,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1980</v>
       </c>
@@ -1175,16 +1666,13 @@
         <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -1193,9 +1681,13 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="48" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1208,10 +1700,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1220,10 +1712,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1996</v>
       </c>
@@ -1233,8 +1725,12 @@
       <c r="C2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1248,10 +1744,12 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="4" max="4" width="21.85546875" customWidth="1"/>
+    <col min="5" max="5" width="44.140625" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1266,10 +1764,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1278,10 +1776,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1997</v>
       </c>
@@ -1292,14 +1790,14 @@
         <v>31</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1997</v>
       </c>
@@ -1310,14 +1808,16 @@
         <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E3" s="3"/>
+        <v>269</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>270</v>
+      </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -1326,9 +1826,13 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:H4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="5" max="5" width="157.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1341,10 +1845,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1353,10 +1857,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="240" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1998</v>
       </c>
@@ -1367,14 +1871,16 @@
         <v>35</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>168</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>237</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="225" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1998</v>
       </c>
@@ -1385,14 +1891,16 @@
         <v>38</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E3" s="3"/>
+        <v>169</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="F3" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="315" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1998</v>
       </c>
@@ -1403,12 +1911,18 @@
         <v>41</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E4" s="3"/>
+        <v>170</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="F4" s="3" t="s">
         <v>36</v>
       </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1416,7 +1930,66 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="23.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1999</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1430,11 +2003,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>225</v>
+      <c r="D1" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1443,64 +2016,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="285" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>1999</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="180" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2000</v>
       </c>
@@ -1511,9 +2030,11 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>166</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>246</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>39</v>
       </c>
@@ -1524,9 +2045,12 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="38.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1539,10 +2063,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1551,10 +2075,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="270" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2001</v>
       </c>
@@ -1565,15 +2089,20 @@
         <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>164</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>273</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+      <c r="H2" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2001</v>
       </c>
@@ -1584,9 +2113,11 @@
         <v>49</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E3" s="3"/>
+        <v>165</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="F3" s="3" t="s">
         <v>39</v>
       </c>
@@ -1598,9 +2129,13 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="60.28515625" customWidth="1"/>
+    <col min="6" max="6" width="37" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1613,10 +2148,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1625,7 +2160,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="315" x14ac:dyDescent="0.25">
@@ -1639,15 +2174,17 @@
         <v>51</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" ht="225" x14ac:dyDescent="0.25">
+      <c r="G2" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2003</v>
       </c>
@@ -1658,9 +2195,11 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E3" s="3"/>
+        <v>161</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>267</v>
+      </c>
       <c r="F3" s="3" t="s">
         <v>36</v>
       </c>
@@ -1672,9 +2211,12 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="46.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1687,10 +2229,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1699,10 +2241,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="375" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2004</v>
       </c>
@@ -1713,15 +2255,17 @@
         <v>55</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>163</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>243</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="210" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2004</v>
       </c>
@@ -1732,9 +2276,11 @@
         <v>57</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E3" s="3"/>
+        <v>241</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="F3" s="3" t="s">
         <v>36</v>
       </c>
@@ -1746,9 +2292,15 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" customWidth="1"/>
+    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1761,10 +2313,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>220</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1773,10 +2325,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="300" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2005</v>
       </c>
@@ -1787,9 +2339,11 @@
         <v>59</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>160</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
       </c>
@@ -1804,9 +2358,15 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" customWidth="1"/>
+    <col min="4" max="4" width="29.28515625" customWidth="1"/>
+    <col min="5" max="5" width="48.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1819,10 +2379,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1831,10 +2391,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="240" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2006</v>
       </c>
@@ -1845,9 +2405,11 @@
         <v>61</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>159</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>247</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
       </c>
@@ -1859,7 +2421,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1877,10 +2439,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1889,10 +2451,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1982</v>
       </c>
@@ -1903,11 +2465,19 @@
         <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>107</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -1916,11 +2486,12 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="45.5703125" customWidth="1"/>
+    <col min="8" max="8" width="40.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1934,10 +2505,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1946,10 +2517,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2012</v>
       </c>
@@ -1960,14 +2531,19 @@
         <v>63</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>158</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G2" t="s">
         <v>65</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -1976,9 +2552,14 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="4" max="4" width="30.42578125" customWidth="1"/>
+    <col min="5" max="5" width="58.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1991,10 +2572,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2003,10 +2584,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2018</v>
       </c>
@@ -2017,14 +2598,16 @@
         <v>67</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>157</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>248</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2033,10 +2616,11 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="5" max="5" width="138.5703125" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" customWidth="1"/>
     <col min="7" max="7" width="40.5703125" customWidth="1"/>
   </cols>
@@ -2052,10 +2636,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2064,10 +2648,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2019</v>
       </c>
@@ -2078,17 +2662,19 @@
         <v>70</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>151</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2019</v>
       </c>
@@ -2099,17 +2685,19 @@
         <v>73</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E3" s="3"/>
+        <v>152</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="F3" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2019</v>
       </c>
@@ -2120,17 +2708,19 @@
         <v>75</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E4" s="3"/>
+        <v>153</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="F4" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2019</v>
       </c>
@@ -2141,15 +2731,17 @@
         <v>77</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E5" s="3"/>
+        <v>154</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>249</v>
+      </c>
       <c r="F5" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2019</v>
       </c>
@@ -2160,17 +2752,19 @@
         <v>79</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E6" s="3"/>
+        <v>155</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="F6" s="3" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="180" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2019</v>
       </c>
@@ -2181,9 +2775,11 @@
         <v>81</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" s="3"/>
+        <v>156</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>251</v>
+      </c>
       <c r="F7" s="3" t="s">
         <v>82</v>
       </c>
@@ -2195,110 +2791,119 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" customWidth="1"/>
+    <col min="3" max="3" width="56.140625" customWidth="1"/>
+    <col min="4" max="4" width="53.28515625" customWidth="1"/>
+    <col min="5" max="5" width="46.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="F1" s="6" t="s">
+      <c r="D1" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-    </row>
-    <row r="2" spans="1:10" ht="150" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="H1" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="13">
         <v>2020</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+    </row>
+    <row r="3" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="13">
+        <v>2020</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" spans="1:10" ht="195" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="E3" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="13">
         <v>2020</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="B4" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8" t="s">
+      <c r="E4" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" spans="1:10" ht="270" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <v>2020</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8" t="s">
-        <v>87</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
+        <v>213</v>
+      </c>
+      <c r="H4" s="16"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2306,101 +2911,109 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="39.7109375" customWidth="1"/>
+    <col min="5" max="5" width="118.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>225</v>
+      <c r="D1" s="10" t="s">
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="F1" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>222</v>
+      <c r="H1" s="7" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="165" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="A2" s="9">
         <v>2021</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>2021</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="1:8" ht="135" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="E3" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
         <v>2021</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="B4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" spans="1:8" ht="240" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <v>2021</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H4" s="7"/>
+        <v>210</v>
+      </c>
+      <c r="H4" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2408,12 +3021,13 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.42578125" customWidth="1"/>
-    <col min="3" max="5" width="41.5703125" customWidth="1"/>
+    <col min="3" max="4" width="41.5703125" customWidth="1"/>
+    <col min="5" max="5" width="73.5703125" customWidth="1"/>
     <col min="6" max="6" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2428,10 +3042,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2440,28 +3054,30 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
         <v>2022</v>
       </c>
-      <c r="B2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" t="s">
-        <v>184</v>
+      <c r="B2" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>180</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>261</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G2" t="s">
-        <v>186</v>
+      <c r="G2" s="6" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2472,33 +3088,35 @@
         <v>96</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>97</v>
+        <v>262</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="G3" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2022</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E4" s="3"/>
+        <v>139</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>265</v>
+      </c>
       <c r="F4" s="3" t="s">
         <v>71</v>
       </c>
@@ -2509,20 +3127,20 @@
         <v>2022</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G5" t="s">
-        <v>208</v>
+      <c r="G5" s="6" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2530,41 +3148,43 @@
         <v>2022</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="G6" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2022</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E7" s="3"/>
+        <v>142</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="F7" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G7" t="s">
-        <v>211</v>
+      <c r="G7" s="6" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -2572,20 +3192,20 @@
         <v>2022</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G8" t="s">
-        <v>209</v>
+      <c r="G8" s="6" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2594,12 +3214,14 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="32.85546875" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="52" customWidth="1"/>
+    <col min="5" max="5" width="94" customWidth="1"/>
+    <col min="6" max="6" width="70.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2613,10 +3235,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2625,52 +3247,64 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="F2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>204</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>256</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>255</v>
       </c>
       <c r="F3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2023</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>116</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>252</v>
       </c>
       <c r="F4" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2679,9 +3313,15 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="51.85546875" customWidth="1"/>
+    <col min="4" max="4" width="45.5703125" customWidth="1"/>
+    <col min="5" max="5" width="57" customWidth="1"/>
+    <col min="6" max="6" width="48" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -2694,10 +3334,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2706,7 +3346,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -2714,19 +3354,19 @@
         <v>2024</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2734,16 +3374,16 @@
         <v>2024</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2751,50 +3391,56 @@
         <v>2024</v>
       </c>
       <c r="B4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F4" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2024</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>120</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>253</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2024</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>121</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>259</v>
       </c>
       <c r="F6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2802,13 +3448,13 @@
         <v>2024</v>
       </c>
       <c r="B7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2816,19 +3462,19 @@
         <v>2024</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -2837,10 +3483,12 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
-  <dimension ref="A1:H4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="5" width="75" customWidth="1"/>
     <col min="6" max="6" width="66.140625" customWidth="1"/>
     <col min="7" max="7" width="43" customWidth="1"/>
@@ -2858,10 +3506,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2870,7 +3518,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -2878,16 +3526,16 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2895,19 +3543,19 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2915,30 +3563,57 @@
         <v>2025</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G4" t="s">
-        <v>190</v>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2025</v>
+      </c>
+      <c r="B5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D5" t="s">
+        <v>228</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>229</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="48.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -2951,10 +3626,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>220</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2963,10 +3638,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1983</v>
       </c>
@@ -2977,9 +3652,11 @@
         <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>108</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>234</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
@@ -2990,7 +3667,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3009,10 +3686,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3021,7 +3698,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3035,10 +3712,10 @@
         <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -3050,7 +3727,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3065,10 +3742,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>220</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3077,10 +3754,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="255" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1985</v>
       </c>
@@ -3091,9 +3768,11 @@
         <v>17</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>110</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>235</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
@@ -3104,7 +3783,66 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="93.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1986</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3119,10 +3857,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3131,64 +3869,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="270" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>1986</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="225" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1988</v>
       </c>
@@ -3199,9 +3883,11 @@
         <v>21</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>176</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>236</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
@@ -3212,15 +3898,18 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="5" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="160.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3231,10 +3920,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3243,10 +3932,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1989</v>
       </c>
@@ -3257,22 +3946,31 @@
         <v>23</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1989</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>175</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="F3" t="s">
+        <v>277</v>
+      </c>
+      <c r="L3" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -3281,10 +3979,13 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="5" max="5" width="64.42578125" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3299,10 +4000,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3311,10 +4012,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1992</v>
       </c>
@@ -3325,14 +4026,16 @@
         <v>25</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>172</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1992</v>
       </c>
@@ -3343,7 +4046,7 @@
         <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Downloads\mainnn\NITW-Transportation-Division-main\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E2E16E-6F76-4900-BAD9-0D39D0F63A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12150" firstSheet="12" activeTab="20"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="15" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -39,7 +40,8 @@
     <sheet name="2022" sheetId="25" r:id="rId25"/>
     <sheet name="2023" sheetId="26" r:id="rId26"/>
     <sheet name="2024" sheetId="27" r:id="rId27"/>
-    <sheet name="2025" sheetId="28" r:id="rId28"/>
+    <sheet name="2026" sheetId="29" r:id="rId28"/>
+    <sheet name="2025" sheetId="28" r:id="rId29"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -51,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="297">
   <si>
     <t>Year</t>
   </si>
@@ -587,9 +589,6 @@
     <t>Planning and Evaluation of Urban Bus Route Networks Based on Origin-Destination Information in A Multimode Environment</t>
   </si>
   <si>
-    <t>2008/81201</t>
-  </si>
-  <si>
     <t>https://media.licdn.com/dms/image/v2/C5103AQEdsBhjnc233g/profile-displayphoto-shrink_200_200/profile-displayphoto-shrink_200_200/0/1560254960329?e=2147483647&amp;v=beta&amp;t=NH0m6tvpm5uWPHOUe91O7fF8Cjl4-S4VuzNHp8vL8VQ</t>
   </si>
   <si>
@@ -686,13 +685,7 @@
     <t>Phd_Alumini/S2021/Utsav Vishal</t>
   </si>
   <si>
-    <t>Phd_Alumini/2019/Poojari Yugendar</t>
-  </si>
-  <si>
     <t>Phd_Alumini/S2020/Syed Mubashir Hussain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phd_Alumini/S2020/Kamineni Aditya </t>
   </si>
   <si>
     <t>Phd_Alumini/S2019/S. Srikanth</t>
@@ -1184,17 +1177,112 @@
     <t>Phd_Alumini/S2001/G.V.R Prasada Raju</t>
   </si>
   <si>
-    <t>Phd_Alumini/2003/C.N.V. Satyanarayana Reddy</t>
-  </si>
-  <si>
     <t>Professor in NITW(Civil Engineering)</t>
+  </si>
+  <si>
+    <t>Road accidents are widespread all over the world, and annual global road crash statistics (Association for Safe International Road Travel, 2016) state that nearly 1.3 million people die in road crashes each year, on an average 3,287 deaths a day with an additional 20-50 million are injured or disabled. According to WHO (World Health Organization 2015), nearly 3400 people die on the world's roads every day. Tens of millions of people are injured or disabled every year. In developing countries, the total number of road accidents is more than that of developed nations because of insufficient infrastructure for Road safety. Road safety is a term that describes the safety of road users by implementing sufficient improvement in infrastructure and policies to reduce road accidents.
+Geographical information system (GIS) has its application in all fields. This technology helps to digitalize all physical elements present in the city with their latitude and longitude as a georeferenced layer in GIS software. Hence, spatial analysis in GIS software can analyse the data imported as an attribute and then give the result. Greater Hyderabad Municipal Corporation (GHMC) has been selected as a study area. The study area is divided into two segments, namely MCH (Municipal Corporation of Hyderabad) and the rest of the GHMC area. It is observed that there are differences between accident rate, population density, and employment density between these two segments of the study area. Accident analysis has been carried out using Quantum GIS software for accidents from 2011 to 2015. The GIS analysis is carried out for accident, land use, and socio-economic characteristics and extracted TAZ (Traffic Analysis Zone) wise values of these parameters. Hazardous locations or blackspots are identified in the study area by the stretch-wise and area-wise approaches. The crash frequency method is used to identify the stretch-wise hazardous locations, whereas the area-wise approach has been made with the help of kernel density estimation by generating the hotspot map of the GHMC area.
+The main objective of the study is to develop land use based accident prediction models for the study areas. Therefore, an accident prediction model has been developed for GHMC, MCH, and the rest of GHMC areas considering Total Accidents and KSI accidents per year for each TAZ as dependent variables. While, the population density, employment density, and land-use proportions for each TAZ are considered independent variables. Generalized linear model, Poisson, and negative binomial techniques are used for developing the models. In each approach, the negative binomial model gives a better-fit model. The study found that the employment density, residential area, and road length are positively associated with road accidents, whereas mixed land use is negatively associated with road accidents.
+Sensitivity analysis has been carried out for checking the evaluation of the models. One-way sensitivity analysis is carried out using a single significant variable with the accident variable. At the same time, a set of significant variable combinations is used in two-way sensitivity analysis, which will show in the surface plot. It is observed that the sensitivity of the accident variables with the 10% change in the respective significant variables is presented for all models. With these results, crash modification factors are developed for critical TAZs.</t>
+  </si>
+  <si>
+    <t>The design and operation of signalized intersections plays a vital role in urban road networks, because, the efficient operation of urban road network depends on performance of signalized intersections. Saturation flow and control delay plays a major role in the capacity and Level of Service analysis of signalized intersections. Saturation flow analysis was conducted at eleven intersections from four different cities: Hyderabad, Visakhapatnam, Calicut and Raipur. The analysis established that the saturation flow depends not only on approach width but also on percentage of two-wheeler, percentage of three-wheeler, percentage of LCV and percentage of right turning vehicles. Control delay studies were conducted at six signalized intersections from two different cities: Hyderabad and Visakhapatnam. The analysis showed that, under mixed traffic conditions, control delay depends on cycle time, volume, degree of saturation and percentage of highly manoeuvrable vehicles.
+Saturation flow was found during saturated green intervals, by counting classified number of vehicles for every 5 second count interval. The first four vehicles in the queue on each approach, in each cycle were control delay at signalized intersections under mixed traffic conditions. The developed models are validated, and experimentation is carried out to determine the approach capacities for different traffic, geometric and signalization condition.ignored for saturation flow analysis. The average saturation flow rate was found for 40 cycles during saturated green intervals. The study resulted in the establishment of a relationship between saturation flow rate in pcu/h and its affecting variables under mixed traffic conditions. Also, in Indian traffic scenario, it is observed that most of the two wheelers and a small portion of three wheelers and cars stand beyond the stop line when green is given to another traffic movement from some another approach. This position of vehicles in traffic platoon resulted into saturation flow reduction. In the present study, the effect of encroaching vehicles on saturation flow is studied. Control delay is also one of the performance measures of the signalized intersection. Control delay studies are conducted at six signalized intersections during peak traffic hours. OSM tracker mobile application is used to collect field control delay. The control delay was measured using four vehicle types: two-wheeler, three-wheeler, car and LCV. The study also resulted into the construction of a control delay model in seconds per vehicle based on flow, degree of saturation and proportion of two wheelers and proportion of three-wheeler (highly manoeuvrable vehicles—motorized two-wheeler and three-wheeler fall into this category) using MATLAB fitting tool. The developed saturation flow model and control delay models are capable of predicting basic parameters of a four-legged urban intersection where the signal plan is such that the straight and right traffic flows from each of the approaches are released simultaneously. The developed models are useful to estimate saturation flow and</t>
+  </si>
+  <si>
+    <t>India currently generates over 700 tonnes of biomedical waste per day, a volume projected to rise with the ongoing expansion of healthcare services. Incineration remains a prevalent disposal method, yet it produces substantial quantities of Biomedical Waste Incinerated Ash (BMWIA), which poses serious environmental concerns due to the presence of hazardous constituents such as trace metals and respirable particulates. Nonetheless, BMWIA possesses pozzolanic potential attributed to its high concentrations of reactive oxides primarily silica, alumina, and calcium oxide. Its beneficial reuse in civil infrastructure, particularly in pavement base stabilization, represents a sustainable pathway to mitigate waste disposal issues while reducing the environmental footprint associated with Ordinary Portland Cement (OPC) consumption.
+This research focuses on evaluating the performance and sustainability of pavement base layers stabilized using BMWIA in two binder systems: OPC and alkali-activated geopolymer matrices. A comprehensive laboratory program was designed to study the effects of BMWIA content, activator composition (sodium silicate to sodium hydroxide ratio, SS:SH), curing temperature (ambient and 40°C), and curing durations (7, 28, 60, and 90 days) on the mechanical and durability characteristics of stabilized mixtures. The experimental investigation included assessment of unconfined compressive strength (UCS), indirect tensile strength (ITS), flexural strength (FS), indirect tensile modulus ratio (ITMR), fatigue performance, and resistance to moisture-induced deterioration via 12 wet–dry cycles.
+Among the geopolymer-stabilized specimens, the mix containing 20% BMWIA (CA: BMWIA = 80:20), activated at an SS:SH ratio of 50:50, demonstrated superior mechanical performance and structural integrity, achieving peak UCS at 100% optimum alkali content (OAC). Inadequate or excessive activator levels either limited geopolymerization or induced pore pressure and efflorescence, adversely affecting strength. For BMWIA–OPC blended mixes, reduced BMWIA-to-OPC ratios significantly enhanced ITS, ITMR, and FS values, with a 43.5% increase in FS observed between 7 and 28 days due to effective formation of C–A–S–H gels from cement hydration.
+All geopolymer mixes conformed to the IRC: SP:89-2018 durability standards, with minimal weight loss after wet–dry cycles, reflecting low permeability and high environmental resistance. The optimized geopolymer mix also exhibited enhanced fatigue life, attributed to the formation of a dense, cohesive internal matrix. Environmental assessment revealed that geopolymer mixes incorporating BMWIA yielded the lowest carbon footprint (322.84 kg CO₂e/m³), reflecting a 47.76% reduction compared to other stabilized mixes. From an economic perspective, geopolymer stabilization emerged as the most cost-efficient option, estimated at ₹97.55 lakh/km, resulting in cost savings of up to ₹39.84 lakh/km relative to conventional pavement.
+Furthermore, structural analysis based on mechanistic design principles in accordance with IRC:37-2018 demonstrated that stabilized bases effectively reduced tensile and compressive strains, enabling pavement thickness reductions of up to 39% without compromising long-term performance. The study conclusively establishes that BMWIA, when optimally utilized in OPC and geopolymer binder systems, is a technically viable, economically beneficial, and environmentally sustainable material for flexible pavement base construction applicable to both low- and high-volume traffic scenarios.</t>
+  </si>
+  <si>
+    <t>A significant highway network in India comprises flexible pavements, and thus, their design, construction, and maintenance are crucial for a sustainable transportation system. The flexible pavement design optimises the pavement layers against fatigue cracking (bottom-up cracking) and rutting over the service life. However, premature failures are observed on the pavement during its service life. The early failures could be due to several reasons, including inferior materials, poor construction quality, and excess vehicular loads than the design load. Among all the factors influencing the distresses on a flexible pavement, vehicular load on the pavement is an essential factor to be considered at every step of pavement design and maintenance. Thus, the present study is initiated to characterize the magnitude of vehicular loads applied on the pavement by considering all the significant contributing factors.
+The pavement distresses assumed to occur uniformly along the left- and right-wheel path of the vehicles within a lane. However, there can be a significant difference in the magnitude of particular distress in the left and right-wheel paths due to the transverse slope. Transverse slope significantly affects the magnitude of wheel load transmitted to the top of the pavement surface in each wheel path. For example, the magnitude of wheel load would be higher on the outer wheel path with reference to the median for a dual carriageway. This results in higher distress in the outer wheel path when compared to the inner wheel path. In a similar manner, rough pavement surfaces deteriorate at a much faster rate than relatively smooth ones as the magnitude of dynamic loads increases with an increase in pavement surface roughness. Such effects are often not taken into account in stress analysis and subsequent distress quantification. Thus, the main focus of the current study is to quantify the magnitude of excess wheel loads acting on the top of pavement surface due to the combined effects of pavement roughness and transverse slope for an effective pavement design. A fully loaded truck movement using TruckMaker software was simulated on a pavement surface by varying the pavement roughness and the transverse slope.
+The guidelines on flexible pavement design and maintenance followed in various countries consider the static load obtained from the axle load survey for the pavement analysis. However, the loads applied on the pavement are moving loads and have dynamic characteristics. In a moving vehicle, the wheel load applied on the pavement varies from its static load, and they are called dynamic loads. The magnitude and frequency of dynamic loads depend on the magnitude of undulations in a pavement, vehicle speed, load carried by the vehicle, and the stiffness and damping characteristics of various components in a vehicle. In the studies carried out on dynamic loads, the loads applied are regarded as a stochastic random process, and they are quantified using a factor termed Dynamic Load Coefficient (DLC). DLC is a ratio of the standard deviation of loads applied over a section to the average load. DLC determines the variation of loads applied due to the vertical acceleration induced in a vehicle traversing over rough pavement. Thus, the present study is intended to characterize the effect of pavement factors and vehicle parameters on the dynamic loads generated by a vehicle. The pavement factors include the pavement roughness, and the vehicle parameters include the vehicle speed and Gross Vehicle Weight (GVW). The study involved simulation of full vehicle models of three different commercial vehicles on generated pavement profiles and measurement of dynamic loads. Due to variation in vehicle parameters and pavement factors, the commercial vehicles operating under different conditions observed to produce dynamic loads, which are 4–60% higher than their static loads. Further, the average load applied by the axles of a truck on the pavement is sensitive to the distribution of payload over the truck's loading platform. Therefore, the trucks when loaded to the maximum legal load limit, and only when the load is located between one-third and two-thirds part of the loading platform, the average load applied by all the axles are found to be within the legal axle load limit.
+A relationship is developed between the DLC, vehicle speed, GVW, and pavement roughness to incorporate the dynamic loads into the pavement analysis. To develop the relationship, the full vehicle models were simulated on the real road profiles measured in the field. The simulations were carried out in TruckMaker vehicle dynamics software with three full vehicle models, whose rear axle configuration represents a single axle, tandem axle, and tridem axle.                                                                                                                                                                                                                                                                                                            The DLC value for different simulation conditions was quantified, and further, the relationship was developed using linear regression analysis. Further, the effect of pavement cross-slope on vehicular loading in the inner wheel path is assessed by simulating the vehicle models on road models with 0%, 2% and 2.5% cross-slope. The DLC values were calculated for three vehicles for the LWP (left wheel path) and RWP (right wheel path) separately. To determine the effect of the camber, DLC values of half-axle, i.e., wheels in left wheel path and right wheel path, are calculated separately. From the statistical analysis, there is no significant variation between the DLC values due to the variation of camber. However, the change in camber is expected to apply a higher load in the LWP. To determine extra load applied on the LWP due to the camber change, the load difference between LWP and RWP is calculated for three truck types at different cross-slope conditions, and the difference is expressed in percentage. For the three different trucks, the excess load applied in the LWP is from 4 to 5.5%.
+The effective load applied for different conditions of pavement and vehicle can be determined from the developed relations, and the load can be used to analyse pavement. Critical responses for a flexible pavement section were determined using Finite Element (FE) analysis by considering the viscoelastic properties of asphalt layers and moving loads. It is observed that, compared to the strain due to time invariant loads, the maximum tensile strains due to dynamic loads are about 6 to 16% greater for single axle, 5 to 11% greater for tandem axle, and 11 to 18% greater for tridem axle. Similarly, compared to the strain due to time invariant loads, the maximum compressive strains due to dynamic loads are about 30 to 50% greater for single axle, 24 to 40% greater for tandem axle, and 9 to 21% greater for tridem axle. The analyses of the effect of vehicle speed and overload on the pavement damage indicated that the fatigue life of the asphalt concrete layer is strongly dependent on the load amplitude and the vehicle speed. Consequently, factors such as overloading or low-speed traffic could adversely affect the service life of the pavement.</t>
+  </si>
+  <si>
+    <t>Road networks usually constitute the essential transport infrastructure in urban areas. It is an arrangement of linked roads constructed to facilitate the mobility of various vehicles. A road network is a subset of spatial networks that exhibit topological and geometrical variations to be measured, evaluated, and analysed.
+A good transportation network structure improves the accessibility, mobility and safety of the road users, thereby decreasing the travel time and travel cost. The efficient investigation and utilization of existing transportation infrastructure with novel and relevant approaches are necessary to develop transportation system performance. The present study analyses the existing road network in different locations and clusters of Hyderabad Metropolitan Area (HMA) concerning distinct aspects.
+Specific integrated and Knowledge-based expert system like Geographical Information Systems (GIS) is being availed in urban road network planning to enhance the performance and quality of the transport structure. The present study implements various tasks such as location finding, multiple ring buffer analysis, data extraction and data analysis using a GIS platform. The potentials of GIS in the decision-making process of road network structural performance are also explored.
+Connectivity, accessibility, maturity, and development are identified as the essential road network structural evaluation criteria. Connectivity is measured using Aggregate Transportation Score (ATS) with nodes and links as the components. Accessibility is computed as the Accessibility Index (AI) as the sum of weighted opportunities (or) urban services. Similarly, maturity is analysed as Fractal Dimension (FD), considering the built-up area as the primary component. Road network development is evaluated as Road Network Density (RND), with network length and area essential components. The present study also tries to examine the interdependency between structural evaluation criteria of urban road networks. From different perspectives, the urban road network structure evaluation led to Road Network Structural Performance Index (RNSPI) development. RNSPI evaluates the overall performance of the road network structure at different locations in the city and provides the combined effect of the road network structural evaluation criteria. The present study identifies the places with vulnerable road network structures using RNSPI.                                                                                                                                                                                             It is intended to observe the variation of human settlements pattern in the city. The study establishes the relationship between human settlements quantified in terms of population density and road network structural evaluation criteria using Multiple Linear Regression (MLR), Artificial Neural Networks (ANN), and Adaptive Neuro-Fuzzy Inference System (ANFIS) methods. The results are noteworthy when the association of population density with RNSPI was found using regression analysis. The locations with good road network structural performance have higher human settlements. The present work also attempts to develop different models to predict the urban road network accessibility based on the road network structural components, such as number of nodes, number of links, built-up area, network length, and area. The road network structural components are considered as input and the accessibility index is the output. The present work also explains the prediction capabilities of different modelling techniques used based on various validation statistics. Optimal combinations of different road network structural components are proposed for enhancing the accessibility index wherever necessary using the Least Mean Square (LMS) Error algorithm.
+The study helps the urban transportation planning authorities analyse the existing road network situations to optimize the road network for organic growth in the study area. The policymakers can now implement policies that can balance the road network's connectivity, accessibility, maturity, and development. The study may be further extended to other urban cities, including other elements like land use and temporal variation of the network structure. The application of knowledge-based expert systems (GIS) and tools of Artificial Intelligence such as ANN and ANFIS help improve the decision-making process.</t>
+  </si>
+  <si>
+    <t>Roundabouts in India pose significant safety challenges due to the heterogeneous nature of traffic and unpredictable driver behaviour, yet the factors governing path change decisions and conflict risk at roundabout entries remain insufficiently understood. This study examined the factors influencing drivers' path change behaviour at roundabout entries under mixed traffic conditions. Existing literature has largely focused on homogeneous traffic conditions, leaving a gap in understanding how mixed traffic dynamics, particularly the presence of vulnerable road users such as two-wheelers, influence entry–circulating vehicle interactions and conflict severity. Data were collected from eleven arms of five roundabouts in Bhopal, Madhya Pradesh, and Karimnagar and Siddipet towns in Telangana, using traffic camera footage and videographic surveys, from which vehicle volumes, speeds, trajectories, and time to collision values were extracted using Kinovea and DataFromSky software. Entry–circulating vehicle interactions were analyzed by applying a binary logit (BL) model and machine learning techniques. Random forest (RF), K-nearest neighbors (KNN) and extreme gradient boosting (XGBoost) were applied to identify key factors influencing the path change behaviour. Larger gaps between circulating vehicles significantly decreased the probability of choosing an evasive manoeuvre by the driver entering the roundabout, whereas higher circulating and entry speeds significantly increased the probability of choosing an evasive manoeuvre. Car drivers were the least likely to perform evasive manoeuvres, and the XGBoost model yielded superior predictive performance among the other models.
+To evaluate the conflict risk encountered by the drivers of different vehicle types entering the roundabout, time to collision (TTC) was used as a surrogate safety measure (SSM) and it was observed that two-wheelers (TW) exhibited the lowest median TTC values followed by auto-rickshaws (ARs), cars and light commercial vehicles (LCVs).
+Also, 3,631 interactions involving entering TW’s and other circulating vehicle types was examined to determine conflict risk. A Support Vector Machine (SVM) was developed to classify interactions between entering TW’s and circulating vehicles at roundabout entries as either “severe” or “non-severe” conflicts. From the SVM plot the thresholds for TTC values with varying entry speeds were calculated. TW–TW interactions had the highest percentage of severe conflicts (37.1%) followed by TW–AR (34.6%) and TW–LCV interactions had the lowest percentage of severe conflicts (23.9%).
+Furthermore, the results from the BL model revealed that higher entry and circulating volumes, wider entries, and higher circulating speeds increase conflict severity, while wider weaving sections, larger central islands, splitter islands, and larger circulating gaps reduce it. The key contributions of this study include the application of machine learning and binary logit models for driver path change behaviour analysis, the use of TTC as a surrogate safety measure for conflict risk assessment, the development of SVM-based speed-dependent TTC thresholds for conflict classification, and the identification of factors influencing conflict severity at roundabout entries under mixed traffic conditions. Overall, this study highlights the influence of traffic and geometric factors on driver’s behaviour at roundabouts and establishes that two-wheelers are excessively exposed to severe conflicts, highlighting the need for targeted design and management strategies to improve the safety at roundabouts in mixed traffic environments.</t>
+  </si>
+  <si>
+    <t>One of the major areas of concern in the field of transportation engineering is traffic safety. Among the various road feature categories, horizontal curves have a higher rate of crashes than other components of the road network, and are considered crucial aspects of the transportation network. The reason for their significance in crashes is that drivers are surprised by unexpected changes in the characteristics of the road, which can cause them to speed up or make crucial driving decisions that result in crashes. When there is some discrepancy between what drivers may perceive as a safe speed and the real speed at which a feature can be negotiated successfully, driver errors and accidents are more likely to happen. According to the previous literature, it is not enough to determine the speed or speed reduction of a single class of vehicle because the impact of geometry varies depending on the type of vehicle and all vehicles together. So, there is need for evaluation of geometric design consistency under mixed traffic conditions for increasing the highway safety.
+In developing nations like India, the police department, insurance company, and hospitals serve as the main sources of accident data. So, it is possible that the information from these sources may be or might not be reliable as they are not carried out in the transportation perspective. Also, majority of transportation authorities have little funds, making it a difficult assignment for them to find the best ways in order to increase traffic safety across the entire network of roads. So, the aim of this study is to identify and classify specific horizontal curves on two-lane rural highways that exhibit a high potential for safety improvements.
+Failure on a highway isn't just defined by collisions; it's also defined by uncertainties that cause drivers to deviate from their initial manoeuvres or slow down the vehicle as they manoeuvre the horizontal curve. Due to differences in roadway alignment, undivided horizontal curves provide a serious safety issue, which forces motorists to take a different path than they intended. If this differential is not taken into consideration, vehicles may leave their lane and may run off the road, which increases the likelihood of a major collision. Current road geometric design processes disregard stochastic aspects, resulting in inadequate traffic safety considerations. In the current study, the design factors are treated as random using reliability-based analysis. Also, previous studies related to reliability analysis were solely concerned with establishing a direct connection between collisions and the probability of non-compliance (Pnc), omitting any discussion of the impact of geometric features on accidents or the indirect effects of geometric features and vehicle characteristics on Pnc. The current study aims to account uncertainties  using reliability as a tool that considers slow down the vehicle while they manoeuvre the horizontal curve and to develop thresholds of reliability index based on operating speed design consistent measure as a surrogate safety measure rather than using crash data.
+In this study, classical topography survey and video graphic survey was carried out on the field using total station and video camera respectively. The data collected comprises speed data and geometric data of 66 horizontal curves (Lane based analysis was carried out). A total of 17,754 free flowing vehicle speeds have been extracted from the video graphic survey and used in the analysis. Several past studies have developed speed reduction models from tangent to curve section for evaluating design consistency. However, there are significant differences between established models, independent variables, and regression coefficients of various models. There is no one model that is widely recognized, as evidenced by this difference, which can be related to variations in driver behaviour from one location to another. So, the present study developed the speed reduction models for each vehicle type and its relationship with geometric characteristics and existing site conditions. The current study also proposes thresholds of reliability index associated with sight distance, super elevation and system for various operating speed ranges based on design consistent measure. In addition, established the relationship of geometric characteristics and vehicle characteristics with the design consistency levels.
+Findings from the speed reduction model developed shows that, there exists positive correlation between the inverse of square root of radius with the 85th percentile speed reduction value (ΔV85). Similarly negative correlation between the minimum available sight distance (ASD) with ΔV85. Nomograms has been developed from the models, which concludes that, for a constant radius, as the minimum ASD increases, the speed reduction decreases, which implies that the curved section’s consistent level is increasing. Similarly, for a constant minimum ASD, if the radius is increased, the speed reduction is decreased which implies the curved section’s consistent level is increased. Also, as the approach tangent speed increases, the curves that fall below the design consistent region decreases. This study also suggested the procedure to adopt variable safe speed limits for each vehicle type based on design consistency model developed, which can be used as a prior warning information to enhance safety on horizontal curves.
+Findings from the reliability analysis shows that, the threshold values of reliability indices associated with sight distance, super elevation and system is increasing as the operating speed increases, for the section to be a consistent design section. The results from the Binary Logit  Model show that the consistency level is significantly affected by deflection angle and operating speed. From Binary Logit Model (BLM) results, the conclusion is that an increase in the value of deflection angle will significantly increase the probability of In-Consistent level, which indicates uncertainties that cause drivers to change the path of vehicle or rate of deceleration of the vehicle while maneuvering the curve will be increased. Whereas, increase in the operating speed will significantly increase the probability of In-Consistency level.</t>
+  </si>
+  <si>
+    <t>The socioeconomic status of individuals in India is improving day by day leading to an increase in vehicle ownership. People tend to move from place to place in their vehicles especially for trips within the city. Private vehicles provide comfort, safety, and flexibility at the time of travel compared to public transport. Due to the increase in the number of vehicles on road, traffic problems such as congestion occur. To combat this, vehicles coming on the road must be reduced. This can happen by encouraging people to use public transportation rather than private vehicles. This can be done by Advanced Public Transportation system (APTS), in which the main aim is to improve public transport by giving the road user accurate information on bus arrival times, running status and also to the policymakers to check route status for optimizing the number of buses on the route based on demand. Studies have been carried out from time to time for providing information. Alternatively, managing the traffic coming on a road is the solution to the congestion problem. This can be achieved through ITS techniques like Advanced Traveler Information System (ATIS) and Advanced Traffic Management System (ATMS). The main information required in both applications is travel time. Based on travel time provided to the users, they will select the best possible route and travel mode, either public or private transport. Based on travel time data, the management centers can assign traffic on different routes to reduce the burden on a single route. Also, for APTS, giving information to the travelers regarding bus arrival times requires travel time as input. So, to identify or reduce congestion, travel time information is an essential requirement. Hence, travel time modeling for both private and public transport is required to estimate and predict travel time. There are a number of data collection techniques which are used to collect travel time data. Instead of using costly equipment, low-cost data collection techniques like mobile applications can be tried. In India, where traffic composition is heterogeneous, travel time modeling is a challenging assignment.
+The main objective of the present research is to develop a travel time prediction model in mixed traffic conditions in India. Here in urban areas, traffic is heterogenic with 2-wheelers, 3-wheelers along with cars and heavy vehicles (HV) using the same lane where discipline is not observed. In this work, different vehicle classes during different traffic conditions during the day have been studied. From the literature collected, Global Positioning System (GPS) is considered to be an efficient travel time data collection technique. However, alternate data collection techniques in place of handheld GPS instruments are studied, and it has been found that mobile GPS applications can be used. For this study, the mobile application Open Street Map (OSM) Tracker, which is a free application available from Google Play Store, was used and is compared with the Trimble handheld GPS instrument. A person carrying both a handheld GPS instrument and a mobile phone with OSM tracker travelled by different categories of vehicles to check the usability of the mobile application. The results show that the mobile application and handheld instrument show similar results in terms of distance, speed, and time. The mobile application records the data for 1-second interval continuously during the survey but the data points recorded from handheld instrument shows less than the actual time recorded as it cannot record data where obstruction occurs for the instrument from receiving signal like tall buildings, trees, etc. As the work is scheduled in urban areas, mobile internet connection was uninterrupted and the mobile application was able to continuously record data.
+Traffic volume studies have been conducted to identify peak hour. Based on the studies, three different times of the day, peak flow condition (17:30 hours - 18:30 hours), Intermediate flow condition (10:30 hours - 11:30 hours), and free-flow condition (05:00 hours - 06:00 hours) have been considered for data collection. Based on the modal share, 2-wheeler, 3-wheeler, and cars were identified as the travel modes for data collection as the work focuses on private transportation. A person carrying a mobile phone with the application travelled using each of the vehicle classes. Travel time data like speed, distance, travel time, stopping time were extracted from the data collected from the mobile application. This data along with traffic volume data and modal share was used to develop a travel time model. The effect of modal share on travel time was checked by using different traffic compositions which was done using VISSIM software. The results show that the percentage variation of the vehicle class present in the traffic stream will affect the travel time and needs to be considered for modeling. First, a simple Multiple linear regression equation was developed and the root mean square error value was calculated. To reduce the error, non-linearity was checked and models were developed accordingly. Machine learning methods like artificial neural network (ANN) and support vector machine (SVM) were also adopted, when nonlinear relation between the dependent and independent variables cannot be established mathematically. Out of these, the SVM model with radial kernel predicts travel time better compared to other models.</t>
+  </si>
+  <si>
+    <t>Increase in traffic flow demand on urban roads invites significant challenges in evaluation of operational performance and traffic flow characteristics. The complexity in analysis and modelling of traffic flow further increases due to presence of side friction in a form of curb-side bus stop. The present study examines the traffic stream characteristics at eight curbside bus stops sections and analyses time headway distribution patterns on multilane divided urban roads. The study also examines various factors to develop a multiple liner regression models for estimation of average time headway at bus stop section and validate the models to characterize the relationship between traffic flow parameters and time headway across the entire carriageway, different lanes and between different vehicles. The analysis focuses on the impact of lane position, traffic volume, dwell time, and follower vehicle type on time headway.
+The study calculates the mean time headway using a fitted headway distribution model and determine the capacity of the road sections using time headway method. Factors influencing capacity are identified and capacity reduction model (PRC) is developed. Capacity is further assessed by constructing speed-flow diagrams and validated field capacity as estimated through the time headway method. The study also determines the capacity of the bus stop section by using adjustment factors outlined in Indo-HCM (2017). However, PRC values estimated based on Indo-HCM guidelines are notably higher than those derived from the proposed PRC model.
+Consequently, the study endeavours to develop innovative nomograms for estimating adjustment factors across a broad spectrum of bus frequencies and dwell times. Dynamic traffic characteristics, including acceleration and deceleration, are analysed and linear and non-linear models are developed with a 95% confidence interval. Additionally, the study employed a VISSIM microsimulation model, calibrated and validated to accurately reflect local traffic conditions at curbside bus stops. Traffic operational performance was systematically assessed by varying carriageway widths, adjusting bus frequencies, and at different V/C ratios at simulated bus stops with and without bus bay. Furthermore, the study reveals that reducing the taper ratio of the bus bay to 1:9 degrees provides smoother integration of a bus into the main vehicular traffic stream, minimizing speed differentials and reducing disruptions in the bus stop influencing area. The outcomes based on the present study gives insights to selection of potential design alternatives that enhance the overall traffic flow and operational efficiency around bus stops.</t>
+  </si>
+  <si>
+    <t>Unplanned urbanization has led to the settlement of migrants from rural areas close to railway lines, exposing them to the continuous noise levels from the moving trains. These high, intense noise levels annoy and adversely affect the health of individuals living near railway lines. Every ambient noise study employs the source-path-receiver structure to explore the overall behavior of sound. Therefore, noise control techniques are necessary to modify the noise source mechanism, transmission path characteristics, and receiver perception. Among these techniques, eliminating railway noise at the source is the most effective method for mitigating noise. This study evaluated different train types, including various speeds and lengths, to determine their correlation with noise levels. Results showed that train speed had the strongest correlation with noise levels, the driving factor for maximum noise levels. When the train speed increases by 10 km/h, noise levels rise by 2.8 to 3 dBA. In the case of freight trains, the train length is a key parameter in the emission of railway noise when compared to passenger trains. The study also identified the type of trains with the highest noise levels, and a detailed examination of the mechanism responsible for this phenomenon was carried out. Multiple linear regression models for maximum and equivalent noise levels were developed for passenger and freight trains. In addition to source parameters, the current study evaluates a noise pollution hotspot: a railway-level crossing, where several activities related to transportation noise were involved. Train honking, train movement, road vehicles, and pedestrians contribute to the noise level at a railway-level crossing. Train horns are generally blown as trains approach railway level crossings and are mandatorily used to alert road users. However, the train horns are considered a nuisance to the nearby residents. A comprehensive noise monitoring survey was conducted at an access-controlled level crossing. Further, an Artificial Neural Network (ANN) based railway noise prediction model was developed to forecast maximum (Lmax) and equivalent (Leq) noise levels. Results revealed that train horns produced impulsive sound signals that fall under high-frequency one-third octave bands, causing severe irritation to trackside inhabitants.
+Noise levels are affected by changes in distance, intervening barriers, and atmospheric conditions along the transmission path between the source and the receiver. This study explored the variance of railway noise in an urban setting over various measuring distances, including 25, 50, 100, and 200 m, with variables such as air temperature, humidity, and wind conditions. Results showed that the effect of the wind was more significant for larger distances between the source and the receiver. For every 1 m/s increase in wind speed within a distance of 50 m, the average sound attenuation induced by the upwind phenomena was 0.2 dBA. The impact of air temperature changes on received sound level from a moving source was insignificant within the range of temperatures considered in the study. The effect of humidity was observed to be less at shorter distances but at larger distances, increasingly attenuates noise levels.
+Along the transmission path, the presence of a wall between the source and receiver can act as a noise barrier resulting in a reduction in intensity of noise. In urban areas, railway boundary walls are constructed to prevent encroachments of railway lands and to avoid pedestrians trespassing the railway tracks. This study aims to evaluate effectiveness of such a boundary wall in reducing noise and proposes an improved alternative through Computational Fluid Dynamics (CFD) simulations. Various noise barriers with different geometry, shape, and surface materials were simulated and verified through field study measurements. Noise attenuation was evaluated by measuring railway noise spectra at different positions, including 0.5 m in front and behind the barrier and at the facade of the residential area. Results showed that as barrier height increased, insertion loss also increased, with a maximum attenuation of 17 dBA achieved with a rectangular barrier of height 6 m. The most effective noise barrier for reducing railway noise was a T-shaped barrier with a height of 6 m and a projection length of 2 m, with an insertion loss of 22 dBA. This study recommends constructing the barrier with soft materials on its surface to reflect and absorb sound waves effectively.
+In the last phase of this study, the impact of railway noise on the residents living along the railway line at several distances was assessed by measuring the noise inside houses. Additionally, a human perception survey was conducted to investigate the relationship between noise levels and annoyance during daily activities such as working, resting, conversing, eating, talking on the phone, and reading. Structural Equation Models (SEM) were employed to analyze the complex relationships between annoyance, disturbance, and health effects. The outcomes of this study reveal that both passenger and freight trains exceeded the permissible noise limits, with an excess of 36.8% and 15% during daytime and 75.15% and 41.8% during nighttime, respectively. The primary factors contributing to annoyance were identified as the source type and location of noise exposure. The annoyance levels associated with the time of noise exposure negatively impacted disturbances to daily activities and subsequent health effects. This phenomenon suggests a psychological adaptation known as habituation, where residents along railway lines gradually become accustomed to the noise over time. Furthermore, the cumulative impact of disturbances to daily activities can indirectly influence long-term health. Proximity to the railway line amplifies the relationship between annoyance and health effects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S. Padma Tejaswi </t>
+  </si>
+  <si>
+    <t>Urban travel patterns are evolving, necessitating the development of improved planning and travel demand forecasting methods. As cities experience rapid urbanisation and motorisation, longer commutes become prevalent. Unfortunately, heavy reliance on private vehicles hinders the adoption of sustainable transport modes. Recognising this challenge, interest in sustainable transportation alternatives has surged due to their potential to reduce automobile dependence. As countries prioritise sustainability, the transportation sector is transforming rapidly with mass rapid transit systems. However, understanding the decision-making processes behind trip chaining and mode choice is necessary to utilise the provided infrastructure. Thus, a planned approach incorporating a good understanding of travel behaviour is essential for achieving sustainability.
+Traditional mode choice models often neglect these underlying causal relationships between trip chaining and mode choice behaviour, necessitating the development of new models. This research addresses this gap by employing a novel approach, combining Structural Equation Modelling (SEM) with discrete choice techniques that effectively determine modal share. While extensive research has explored factors influencing mode choices and first/last mile connectivity, few studies have delved into the underlying hierarchy of decision-making processes. Understanding this hierarchy, which illustrates causal relationships, is crucial for modelling travel decisions, as trip structure depends on choice behaviour and vice versa. A more holistic understanding of mode choice behaviour is achieved by incorporating mediating effects of trip chaining and mode choice alongside traditional factors.
+Hyderabad city in Telangana, India, is taken as the study area, and the hierarchical relationships between trip chaining and mode choice using the SEM method are developed due to its inherent strength in handling latent causal relationships. Two models were  developed - one for active/public transport modes and the other for private modes. These two models were analysed for work and non-work purposes, thus making up four models altogether. Through these causal relationships, SEM analysis provides the total effects of sociodemographic variables on mode choices and trip chain types. Findings reveal that the decision-making process is distinct for public transport users and private mode users for work and non-work trips. Additionally, this study draws insights from choice riders to extract the driving factors behind their choices. Confirmatory factor analysis is employed to validate the identified factors.
+Furthermore, this research work explores the maximum willingness of individuals to spend on travel, which is the upper limit of the travel time (Travel Time Frontier (TTF) / Travel Time Budget (TTB)). As the TTF/TTB is based on individual perceptions and is not directly measurable, the Stochastic Frontier Analysis (SFA) model is employed to estimate this unobserved frontier value based on the production frontier function of SFA. A separate analysis is carried out to assess the expected frontier values for public and private mode users, and the findings show that public transport users have higher TTB than private mode users.
+Additionally, this study explores two primary approaches to analyse travel demand: travel time budget (TTB), representing the maximum time that travellers are willing to spend, and travel time expenditure (TTE), which reflects actual time spent travelling. The distinction between these approaches is especially crucial when planning for heavy infrastructure systems like metro rail, as it has substantial implications for travel choices. Metro rail systems significantly impact travel time expenditures due to their higher speeds, increasing the margin between expenditure and budget. This influence prompts travellers to reconsider their mode and departure time choices in the short run. In the long term, this may lead to a change in origin and destination choices. Such discrete changes have the potential to induce additional travel, either by covering longer distances or more activity participation. To assess the impact of the discrete choices, Hyderabad metro rail users are considered for the analysis, and the results indeed reveal the change.
+Despite their enormous significance to transport planning, TTBs are rarely used in the analysis. This study promotes their integration, emphasising the need for a deeper understanding of their role in shaping travel behaviour. It offers valuable insights for planners and policymakers to develop effective strategies promoting sustainable transportation in developing countries. By integrating these concepts, this research provides a holistic understanding of travel behaviour, leading to improved decision-making and the development of sustainable transportation systems that meet the dynamic needs of these countries.</t>
+  </si>
+  <si>
+    <t>DYNAMICS OF URBAN TRAVEL DECISIONS, UNVEILING THE LINK BETWEEN TRAVEL TIME BUDGETS AND COMMUTING MODE
+CHOICES</t>
+  </si>
+  <si>
+    <t>Prof. C.S.R.K Prasad</t>
+  </si>
+  <si>
+    <t>Uncontrolled T-intersections are the major bottlenecks in the roadway system, causing traffic congestion and delays. At these intersections, the drivers seldom follow the priority of rules or right of way and as a result different vehicles moving at varying speeds from different directions will attempt to cross and turn at the same time. In developing countries like India, despite fluctuations in road accident statistics, road accidents and fatalities at these intersections increase every year. The right-turning vehicle movements on both minor and major roads at these intersections are highly complex due to ambiguities in driver behaviour. Right-turn vehicles may misjudge the vehicle gap and speed of conflicting through vehicles on major roads when crossing the intersection, leading to a higher number of road accidents and fatalities at these locations. Therefore, gaining knowledge about the behaviour of right-turn vehicles that leads to conflicts which is essential to reduce the number as well as the severity of accidents at uncontrolled T-intersections.
+Many researchers have studied the behaviour of right-turn vehicle drivers based on vehicle gap acceptance decision. However, right-turn vehicles often attempt risky turning manoeuvres, also known as abnormal driving paths, by accepting smaller gaps between through traffic, a behaviour that significantly contributes to accidents. The present study aims to analyse the effect of various factors on right-turn vehicle driving path change behaviour as well as safety and to evaluate the level of safety of right-turn vehicles at uncontrolled T-intersections under mixed traffic conditions.
+To carry out the present work, eight uncontrolled T-intersections were selected in three different cities (Viz., Warangal, Visakhapatnam, and Vizianagaram) in India. The roadway geometric details (viz., width of each approach road and median width) of the selected study intersections were measured from the field using a rodometer. The traffic characteristics, vehicle characteristics, driver behavioural characteristics, and traffic conflicts were extracted from video data using Kinovea software. For evaluating the right-turn vehicle safety at uncontrolled T-intersections, this study used surrogate safety measures such as post encroachment time (PET), time to collision (TTC), T₂min, and safety margin (SM). The questionnaire survey was also conducted in order to collect driver perceptions about risky driving behaviour of right-turn vehicles. A binary logit model (BLM) was developed to investigate the factors influencing the probability of abnormal driving path behaviour of right-turn vehicles on both minor and major roads. The model results show that the manoeuvring speed of right-turn vehicles, the running speed of conflicting through vehicles, vehicle gap, and waiting time are the important explanatory variables significantly affecting drivers' choice in selecting a driving path while crossing the intersection. Additionally, a structural equation modelling (SEM) was developed using questionnaire data to identify the factors influencing risky driving behaviour at uncontrolled T-intersections. The results indicate that driver behaviour questionnaire (DBQ) factors such as driver speed violations and aggressive driving violations, are the main predictors of risky driving behaviour. Furthermore, the theory of planned behaviour questionnaire (TPBQ) factor such as driver attitude, has a significant effect on risky driving behaviour.
+The Threshold limits of PET, TTC, and T₂min are defined using the k-means clustering technique. The severity of right-turn vehicle conflicts has an inverse relationship with SSMs. Moreover, minor right-turn vehicle conflicts have lower threshold limits than major right-turn vehicle conflicts. The results concluded that the TTC predicts severe conflicts better compared to PET and T₂min. An ordered logit model was developed to examine the factors influencing the conflict severity of right-turn vehicles from minor as well as major roads. The results show that two-wheelers in both right-turn vehicles and conflicting through vehicles are at high risk than auto-rickshaws, cars, light commercial vehicles, and buses. The important factors that play a major role in predicting the severity of right-turn vehicle conflicts are vehicle speeds, traffic volume, abnormal driving paths, vehicle gap, and waiting time. In order to identify the influence of vehicle type on the frequency of right-turn vehicle conflicts, a generalized poisson regression model (GPRM) was developed, and results indicate that the composition of vehicle type and traffic volume has a significant effect on the severity of right-turn vehicle conflicts.
+A Tobit regression model was employed to analyse the relationship between the safety margin and independent variables, which was then used to develop nomograms for assessing right-turn vehicle safety at uncontrolled T-intersections. The SM model results showed that the speed of the conflicting through vehicle, vehicle gap, and number of lanes are the most significant factors for predicting the safety margin at uncontrolled T-intersections: The nomograms are developed to determine the level of safety of right-turn vehicles at uncontrolled T-intersections based on factors such as vehicle gap, vehicle speed, and the number of lanes on the major road. Further, k-means clustering was used to define the safety level based on the safety margin indicator. The combined SMI data is divided into three groups: unsafe, tolerable, and safe.</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2003/C.N.V. Satyanarayana Reddy</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2008/81201</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2019/Poojari Yugender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phd_Alumini/S2020/Kaminenei Aditya </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1286,6 +1374,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1308,7 +1402,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1317,7 +1411,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1338,6 +1431,12 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1618,7 +1717,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1640,10 +1739,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1652,7 +1751,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -1669,7 +1768,7 @@
         <v>106</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>8</v>
@@ -1681,7 +1780,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1700,10 +1799,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1712,7 +1811,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -1726,10 +1825,10 @@
         <v>29</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -1744,7 +1843,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1764,10 +1863,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1776,7 +1875,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1808,16 +1907,16 @@
         <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -1826,7 +1925,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1845,10 +1944,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1857,7 +1956,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -1874,7 +1973,7 @@
         <v>168</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
@@ -1894,7 +1993,7 @@
         <v>169</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>39</v>
@@ -1914,7 +2013,7 @@
         <v>170</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>36</v>
@@ -1930,7 +2029,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1948,10 +2047,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1960,7 +2059,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -1977,7 +2076,7 @@
         <v>167</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>39</v>
@@ -1989,7 +2088,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2004,10 +2103,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2016,7 +2115,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2033,7 +2132,7 @@
         <v>166</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>39</v>
@@ -2045,7 +2144,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2063,10 +2162,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2075,7 +2174,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2092,14 +2191,14 @@
         <v>164</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2116,7 +2215,7 @@
         <v>165</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>39</v>
@@ -2129,7 +2228,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2148,10 +2247,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2160,7 +2259,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="315" x14ac:dyDescent="0.25">
@@ -2181,7 +2280,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2198,7 +2297,7 @@
         <v>161</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>36</v>
@@ -2211,7 +2310,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2229,10 +2328,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2241,7 +2340,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2258,7 +2357,7 @@
         <v>163</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
@@ -2276,10 +2375,10 @@
         <v>57</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>36</v>
@@ -2292,7 +2391,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2313,10 +2412,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>221</v>
+        <v>217</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2325,7 +2424,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2342,7 +2441,7 @@
         <v>160</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
@@ -2358,7 +2457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2379,10 +2478,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2391,7 +2490,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2408,7 +2507,7 @@
         <v>159</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
@@ -2421,7 +2520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2439,10 +2538,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2451,7 +2550,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2468,16 +2567,16 @@
         <v>107</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2486,7 +2585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2505,10 +2604,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2517,7 +2616,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2534,7 +2633,7 @@
         <v>158</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>64</v>
@@ -2543,7 +2642,7 @@
         <v>65</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -2552,7 +2651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2572,10 +2671,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2584,7 +2683,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2601,13 +2700,13 @@
         <v>157</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -2616,7 +2715,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2636,10 +2735,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2648,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2665,13 +2764,13 @@
         <v>151</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2688,13 +2787,13 @@
         <v>152</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2711,13 +2810,13 @@
         <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2734,7 +2833,7 @@
         <v>154</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>64</v>
@@ -2755,13 +2854,13 @@
         <v>155</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>211</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2778,7 +2877,7 @@
         <v>156</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>82</v>
@@ -2791,7 +2890,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2802,108 +2901,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="D1" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
+      <c r="H1" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
     </row>
     <row r="2" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
+      <c r="A2" s="12">
         <v>2020</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="E2" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="F2" s="13" t="s">
+      <c r="E2" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="2"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="13">
+      <c r="A3" s="12">
         <v>2020</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E3" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="F3" s="13" t="s">
+      <c r="E3" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="F3" s="12" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
+        <v>210</v>
+      </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>2020</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="E4" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="F4" s="13" t="s">
+      <c r="E4" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H4" s="16"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
+        <v>296</v>
+      </c>
+      <c r="H4" s="15"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2911,7 +3010,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2920,100 +3019,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>220</v>
+      <c r="D1" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="F1" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="165" x14ac:dyDescent="0.25">
-      <c r="A2" s="9">
+      <c r="H1" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
         <v>2021</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9" t="s">
+      <c r="E2" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>2021</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="H2" s="8"/>
-    </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
         <v>2021</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="B4" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
-        <v>2021</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="H4" s="8"/>
+      <c r="H4" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3021,7 +3122,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3042,10 +3143,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3054,33 +3155,33 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+      <c r="A2">
         <v>2022</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" t="s">
         <v>144</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>180</v>
+      <c r="C2" t="s">
+        <v>179</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>137</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2022</v>
       </c>
@@ -3088,17 +3189,19 @@
         <v>96</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E3" s="3"/>
+      <c r="E3" s="3" t="s">
+        <v>279</v>
+      </c>
       <c r="F3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>202</v>
+      <c r="G3" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3115,14 +3218,14 @@
         <v>139</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2022</v>
       </c>
@@ -3135,15 +3238,17 @@
       <c r="D5" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E5" s="3"/>
+      <c r="E5" s="3" t="s">
+        <v>282</v>
+      </c>
       <c r="F5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2022</v>
       </c>
@@ -3156,12 +3261,14 @@
       <c r="D6" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E6" s="3"/>
+      <c r="E6" s="3" t="s">
+        <v>278</v>
+      </c>
       <c r="F6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>205</v>
+      <c r="G6" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3178,21 +3285,21 @@
         <v>142</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>2022</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>105</v>
@@ -3200,12 +3307,14 @@
       <c r="D8" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E8" s="3"/>
+      <c r="E8" s="3" t="s">
+        <v>281</v>
+      </c>
       <c r="F8" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>204</v>
+      <c r="G8" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -3214,7 +3323,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3235,10 +3344,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3247,7 +3356,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3260,11 +3369,11 @@
       <c r="D2" t="s">
         <v>114</v>
       </c>
-      <c r="E2" s="11" t="s">
-        <v>254</v>
+      <c r="E2" s="10" t="s">
+        <v>251</v>
       </c>
       <c r="F2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3278,16 +3387,16 @@
         <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>252</v>
       </c>
       <c r="F3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3300,11 +3409,11 @@
       <c r="D4" t="s">
         <v>116</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>252</v>
+      <c r="E4" s="10" t="s">
+        <v>249</v>
       </c>
       <c r="F4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3313,7 +3422,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3334,10 +3443,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3346,7 +3455,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3357,19 +3466,19 @@
         <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D2" t="s">
         <v>117</v>
       </c>
       <c r="F2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G2" t="s">
         <v>189</v>
       </c>
-      <c r="G2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2024</v>
       </c>
@@ -3379,14 +3488,17 @@
       <c r="D3" t="s">
         <v>118</v>
       </c>
+      <c r="E3" s="10" t="s">
+        <v>286</v>
+      </c>
       <c r="F3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2024</v>
       </c>
@@ -3394,16 +3506,19 @@
         <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D4" t="s">
         <v>119</v>
       </c>
+      <c r="E4" s="10" t="s">
+        <v>287</v>
+      </c>
       <c r="F4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3416,14 +3531,14 @@
       <c r="D5" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>253</v>
+      <c r="E5" s="10" t="s">
+        <v>250</v>
       </c>
       <c r="F5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3436,11 +3551,11 @@
       <c r="D6" t="s">
         <v>121</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>259</v>
+      <c r="E6" s="10" t="s">
+        <v>256</v>
       </c>
       <c r="F6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -3454,10 +3569,10 @@
         <v>122</v>
       </c>
       <c r="F7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2024</v>
       </c>
@@ -3465,16 +3580,19 @@
         <v>130</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D8" t="s">
         <v>123</v>
       </c>
+      <c r="E8" s="10" t="s">
+        <v>280</v>
+      </c>
       <c r="F8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -3483,8 +3601,47 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E2" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
@@ -3506,10 +3663,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3518,7 +3675,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3532,13 +3689,13 @@
         <v>134</v>
       </c>
       <c r="F2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -3546,19 +3703,22 @@
         <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D3" t="s">
         <v>135</v>
       </c>
+      <c r="E3" s="10" t="s">
+        <v>284</v>
+      </c>
       <c r="F3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2025</v>
       </c>
@@ -3566,49 +3726,71 @@
         <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D4" t="s">
         <v>136</v>
       </c>
+      <c r="E4" s="10" t="s">
+        <v>283</v>
+      </c>
       <c r="F4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" t="s">
         <v>185</v>
       </c>
-      <c r="G4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2025</v>
       </c>
       <c r="B5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D5" t="s">
-        <v>228</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="18" t="s">
-        <v>278</v>
+        <v>225</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>275</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2025</v>
+      </c>
+      <c r="B6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G5" r:id="rId1"/>
+    <hyperlink ref="G5" r:id="rId1" xr:uid="{00000000-0004-0000-1C00-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3626,10 +3808,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>221</v>
+        <v>217</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3638,7 +3820,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3654,8 +3836,8 @@
       <c r="D2" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E2" s="11" t="s">
-        <v>234</v>
+      <c r="E2" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -3667,7 +3849,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3686,10 +3868,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3698,7 +3880,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3715,7 +3897,7 @@
         <v>109</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -3727,7 +3909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3742,10 +3924,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>221</v>
+        <v>217</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3754,7 +3936,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3771,7 +3953,7 @@
         <v>110</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -3783,7 +3965,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3801,10 +3983,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3813,7 +3995,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3830,7 +4012,7 @@
         <v>177</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -3842,7 +4024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3857,10 +4039,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3869,7 +4051,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3886,7 +4068,7 @@
         <v>176</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -3898,7 +4080,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3920,10 +4102,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3932,7 +4114,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="90" x14ac:dyDescent="0.25">
@@ -3958,19 +4140,19 @@
         <v>1989</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D3" t="s">
         <v>175</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>275</v>
+      <c r="E3" s="16" t="s">
+        <v>272</v>
       </c>
       <c r="F3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="L3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -3979,7 +4161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4000,10 +4182,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -4012,7 +4194,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -4029,7 +4211,7 @@
         <v>172</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E2E16E-6F76-4900-BAD9-0D39D0F63A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF84533A-01C0-4395-A9AC-4DFBC5116715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="15" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="15" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -676,9 +676,6 @@
     <t>Phd_Alumini/S2023/G.Shravan Kumar</t>
   </si>
   <si>
-    <t>Phd_Alumini/S2021/J.Jaya Shankar</t>
-  </si>
-  <si>
     <t>Phd_Alumini/S2021/Prashanth Shekar Lokku</t>
   </si>
   <si>
@@ -1276,6 +1273,9 @@
   </si>
   <si>
     <t xml:space="preserve">Phd_Alumini/S2020/Kaminenei Aditya </t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2021/J.Jaya Krishna</t>
   </si>
 </sst>
 </file>
@@ -1739,10 +1739,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1751,7 +1751,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -1768,7 +1768,7 @@
         <v>106</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>8</v>
@@ -1799,10 +1799,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1811,7 +1811,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -1825,10 +1825,10 @@
         <v>29</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>269</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -1863,10 +1863,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1875,7 +1875,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1907,10 +1907,10 @@
         <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -1944,10 +1944,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1956,7 +1956,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -1973,7 +1973,7 @@
         <v>168</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
@@ -1993,7 +1993,7 @@
         <v>169</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>39</v>
@@ -2013,7 +2013,7 @@
         <v>170</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>36</v>
@@ -2047,10 +2047,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2059,7 +2059,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2076,7 +2076,7 @@
         <v>167</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>39</v>
@@ -2103,10 +2103,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2115,7 +2115,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2132,7 +2132,7 @@
         <v>166</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>39</v>
@@ -2162,10 +2162,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2174,7 +2174,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2191,14 +2191,14 @@
         <v>164</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2215,7 +2215,7 @@
         <v>165</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>39</v>
@@ -2247,10 +2247,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2259,7 +2259,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="315" x14ac:dyDescent="0.25">
@@ -2280,7 +2280,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2297,7 +2297,7 @@
         <v>161</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>36</v>
@@ -2328,10 +2328,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2340,7 +2340,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2357,7 +2357,7 @@
         <v>163</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
@@ -2375,10 +2375,10 @@
         <v>57</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>36</v>
@@ -2412,10 +2412,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2424,7 +2424,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2441,7 +2441,7 @@
         <v>160</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
@@ -2478,10 +2478,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2490,7 +2490,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2507,7 +2507,7 @@
         <v>159</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
@@ -2538,10 +2538,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2550,7 +2550,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2567,16 +2567,16 @@
         <v>107</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2604,10 +2604,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2616,7 +2616,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2633,7 +2633,7 @@
         <v>158</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>64</v>
@@ -2642,7 +2642,7 @@
         <v>65</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -2671,10 +2671,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2683,7 +2683,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2700,13 +2700,13 @@
         <v>157</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -2735,10 +2735,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2764,13 +2764,13 @@
         <v>151</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2787,13 +2787,13 @@
         <v>152</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2810,13 +2810,13 @@
         <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2833,7 +2833,7 @@
         <v>154</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>64</v>
@@ -2854,13 +2854,13 @@
         <v>155</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2877,7 +2877,7 @@
         <v>156</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>82</v>
@@ -2911,10 +2911,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>3</v>
@@ -2923,7 +2923,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
@@ -2942,7 +2942,7 @@
         <v>148</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>68</v>
@@ -2966,13 +2966,13 @@
         <v>149</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="7"/>
@@ -2992,13 +2992,13 @@
         <v>150</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="7"/>
@@ -3029,10 +3029,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>3</v>
@@ -3041,7 +3041,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3058,13 +3058,13 @@
         <v>145</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>207</v>
+        <v>296</v>
       </c>
       <c r="H2" s="7"/>
     </row>
@@ -3082,13 +3082,13 @@
         <v>146</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H3" s="7"/>
     </row>
@@ -3106,13 +3106,13 @@
         <v>147</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H4" s="7"/>
     </row>
@@ -3143,10 +3143,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3155,7 +3155,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
@@ -3172,7 +3172,7 @@
         <v>137</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>71</v>
@@ -3189,13 +3189,13 @@
         <v>96</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>138</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>68</v>
@@ -3218,7 +3218,7 @@
         <v>139</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>71</v>
@@ -3239,7 +3239,7 @@
         <v>140</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>64</v>
@@ -3262,7 +3262,7 @@
         <v>141</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>64</v>
@@ -3285,7 +3285,7 @@
         <v>142</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>82</v>
@@ -3308,7 +3308,7 @@
         <v>143</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>87</v>
@@ -3344,10 +3344,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3356,7 +3356,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3370,7 +3370,7 @@
         <v>114</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F2" t="s">
         <v>194</v>
@@ -3387,10 +3387,10 @@
         <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F3" t="s">
         <v>186</v>
@@ -3410,7 +3410,7 @@
         <v>116</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F4" t="s">
         <v>199</v>
@@ -3443,10 +3443,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3455,7 +3455,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3489,7 +3489,7 @@
         <v>118</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F3" t="s">
         <v>188</v>
@@ -3512,7 +3512,7 @@
         <v>119</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F4" t="s">
         <v>194</v>
@@ -3532,7 +3532,7 @@
         <v>120</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F5" t="s">
         <v>196</v>
@@ -3552,7 +3552,7 @@
         <v>121</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F6" t="s">
         <v>188</v>
@@ -3586,7 +3586,7 @@
         <v>123</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F8" t="s">
         <v>186</v>
@@ -3616,10 +3616,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3628,7 +3628,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3663,10 +3663,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3675,7 +3675,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3709,7 +3709,7 @@
         <v>135</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F3" t="s">
         <v>184</v>
@@ -3732,7 +3732,7 @@
         <v>136</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F4" t="s">
         <v>184</v>
@@ -3746,22 +3746,22 @@
         <v>2025</v>
       </c>
       <c r="B5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" t="s">
         <v>224</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>225</v>
-      </c>
-      <c r="D5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3769,16 +3769,16 @@
         <v>2025</v>
       </c>
       <c r="B6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>290</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -3808,10 +3808,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3820,7 +3820,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3837,7 +3837,7 @@
         <v>108</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -3868,10 +3868,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3880,7 +3880,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3897,7 +3897,7 @@
         <v>109</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -3924,10 +3924,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3936,7 +3936,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3953,7 +3953,7 @@
         <v>110</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -3983,10 +3983,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3995,7 +3995,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -4012,7 +4012,7 @@
         <v>177</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -4039,10 +4039,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -4051,7 +4051,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -4068,7 +4068,7 @@
         <v>176</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -4102,10 +4102,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -4114,7 +4114,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="90" x14ac:dyDescent="0.25">
@@ -4140,19 +4140,19 @@
         <v>1989</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D3" t="s">
         <v>175</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -4182,10 +4182,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -4194,7 +4194,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -4211,7 +4211,7 @@
         <v>172</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF84533A-01C0-4395-A9AC-4DFBC5116715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="15" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="8550" firstSheet="22" activeTab="27"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -40,8 +39,9 @@
     <sheet name="2022" sheetId="25" r:id="rId25"/>
     <sheet name="2023" sheetId="26" r:id="rId26"/>
     <sheet name="2024" sheetId="27" r:id="rId27"/>
-    <sheet name="2026" sheetId="29" r:id="rId28"/>
-    <sheet name="2025" sheetId="28" r:id="rId29"/>
+    <sheet name="2025" sheetId="28" r:id="rId28"/>
+    <sheet name="2026" sheetId="29" r:id="rId29"/>
+    <sheet name="Sheet1" sheetId="30" r:id="rId30"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="300">
   <si>
     <t>Year</t>
   </si>
@@ -440,9 +440,6 @@
   </si>
   <si>
     <t>Rama Kanth Angatha</t>
-  </si>
-  <si>
-    <t>Ramesh K</t>
   </si>
   <si>
     <t>G. Ramulu</t>
@@ -1277,11 +1274,32 @@
   <si>
     <t>Phd_Alumini/S2021/J.Jaya Krishna</t>
   </si>
+  <si>
+    <t>The primary aim of transportation is to facilitate movement of people and goods in a safe and efficient manner. To meet the objectives of transportation, there are many challenges from an engineering perspective. Among them, geometric design is the foremost requisite in planning and functional design of a roadway system. Generally, design speed is a speed used to determine the dimensions of highway geometric design elements. Many investigators have recognized that the design speed concepts, as applied to the present conditions of traffic, may not assure consistency in highway geometric design and may lead to incorrect driver expectations between successive elements of the roadway. In order to improve highway safety, the geometric design consistency evaluation is one of the promising strategies for designers.
+Present study aims to assess the horizontal alignment design consistency of two-lane rural highway sections by developing the operating speed model best suits to safety criterion design. Field data collected on 41 sites in various parts of National Highways. The geometric variables like curve radius, curve length, degree of curvature, deflection angle, and preceding tangent length are collected using total station instrument. The speed data collected at various horizontal curve sections and the preceding tangents of the curve sections are analysed to assess the 85th percentile speed of vehicle types such as Car, Motorized Two-wheeler (2W), Motorized Three-wheeler (3W), Light commercial vehicle (LCV), Trucks and Buses. The different statistical distribution analysis is carried out for speed of individual vehicle type and mixed traffic speed data. It is found that vehicle type speed data was either follows normal distribution or Log-normal distribution whereas, mixed traffic speed data follows more than one type of statistical distribution. The most common fit observed on mixed traffic speed data were Beta distribution. Thereafter, the cumulative curves of best fit distribution are drawn to estimate the 85th percentile speed.
+Pearson correlation analysis was performed between the 85th percentile speed of vehicles and geometric variables to find the strong correlated geometric variables with speed. All subset regression analysis was performed with field data and operating speed equations are established. The evaluation of geometric design consistency is performed with radius and classified curved sections to define new threshold limits suitable for all vehicle types under mixed traffic conditions. K-mean clustering analysis was performed to define threshold criteria for passenger car and heavy vehicle types. The threshold criteria used for evaluating safety level based on overall score rating of each curved section for study. The result finds the criteria proposed in present study for assessment of highway design consistency yields appropriate results with heavy vehicle class under nonuniformed traffic conditions. This study revealed that the operating speed of passenger cars at horizontal curve sections have high geometric sensitivity with radius less than 350 m, whereas the operating speed of heavy commercial vehicles showed high geometric sensitivity with radius less than 450 m.
+The difference in operating speed on curve and approach tangent sections was estimated to find the differential speeds of each vehicle type. Further, the 85th percentile speed differential (ΔV₅) estimated at a location is compared with a differential of 85th percentile operating speed (ΔV₈₅) measured at same location. Sensitivity analysis has been performed to verify the significant parameters on ΔV₅ of various vehicle types. The study develops all subset regression models to forecast operating speed reduction on horizontal curve locations by examining the relation between ΔV₅ and ΔV₈₅. The findings showed that the ΔV₈₅ undervalues ΔV₅ by 5.0 kmph, 4.0 kmph, 3.0 kmph, 6.5 kmph and 9.0 kmph for Car, 2W, 3W, LCV, and HCV, respectively. The operating speed differential model for Car is used for developing the nomograms for assessing the road geometric safety on two-lane rural highways.
+The first-order reliability method and system reliability analysis are performed by considering stopping sight distance and superelevation for estimating reliability index values and probability of non-compliance. The analysis showed a high probability of non-compliance with superelevation than the stopping sight distance as design elements. The k-means clustering analysis performed for developing safety evaluation criterion by considering the estimated reliability indices. The study defines criteria based on stopping sight distance, superelevation, and system reliability as unsafe, tolerable, and safe. Finally, the study designed calibration charts by using varying middle ordinates at various levels of probability of non-compliance for evaluating the safety consequences of different design alternatives.</t>
+  </si>
+  <si>
+    <t>This research provides a comprehensive examination of right-turn maneuvers at uncontrolled intersections. These intersections are critical points in road networks where vehicles navigate without the aid of traffic signals or signage. The research delves into several key aspects of right-turn maneuvers, including occupancy time, critical gap behavior, departure capacity, the dynamics of acceleration, and intersection delay. Data for this study was collected at ten intersections, employing videography to gather traffic data and Differential Global Positioning System (DGPS) technology to capture individual vehicle characteristics. Occupancy time analysis was conducted for both single-stage and two-stage crossings, with a specific focus on the statistical distribution of these crossing types. Single-stage crossing occupancy times typically exhibit heavy-tailed, nearly symmetrical profiles with smaller scale parameters. In contrast, two-stage crossings show higher mean values in occupancy time, displaying right-skewed distributions with prominent peaks. In a two-stage crossing scenario, the mean critical gap was found to be 1.21 times greater than that in a single-stage crossing. Two-stage crossings caused a 10% average capacity drop compared to single-stage ones. Moreover, a 10% rise in two-stage crossings led to a 40% decrease in right-turning movement capacity. Furthermore, multiple regression models were formulated to provide insights into occupancy time, departure capacity, and longitudinal and lateral acceleration/deceleration dynamics. The study introduces a new delay model for uncontrolled intersections that combined different delay components. Notably, exit delay is minimal, while turning delay contributes significantly, encompassing 72% of minor right-turn delay. Minor right-turning delay is 1.36 times the occupancy time. A novel service level gauge for minor approaches is developed using vehicle occupancy time and average volume to estimate vehicular delay. This criterion aids in evaluating uncontrolled intersection performance, enhancing traffic management and transportation planning decisions.</t>
+  </si>
+  <si>
+    <t>Ramesh  Babu  Kota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porous asphalt pavement (PAP) is designed to possess high air void contents, enabling efficient drainage of water from the pavement surface. These surfaces, including open-graded friction courses, porous friction courses, and drainage asphalt pavements, are gaining traction among organizations and industries globally. Urbanization significantly alters urban hydrology due to increased impervious surfaces, leading to stormwater runoff that introduces pollutants into nearby water bodies. Managing stormwater runoff and improving water quality in urban areas are shared objectives, often addressed through porous asphalt mixtures (PAM).
+The primary aim of this study is to investigate the impact of gradation and air void content design criteria on the drainage capacity and clogging mechanism of porous asphalt mixtures, utilizing field-collected materials from various locations and roads. Additionally, the study evaluates the performance of PAM in terms of permanent deformation, durability assessment, and stiffness parameters, considering the effect of compaction. Increased compaction levels reduce permeability and air void content, and the study compares results at each stage, calculating the refusal density value of the mixture.
+The study achieved porosity by analyzing the volumetric characteristics of aggregate packing. Aggregate shape characteristics significantly influence asphalt mix packing. A dry aggregate packing study was conducted for multiple selected gradations. Based on air void content and bulk density values, two gradations were further examined using a combination of medium viscosity binder and modified binder, and in the Open Gr-I and Gr-II packing studies, high air void content resulted from lower acceptable content, with Open Gr-II displaying higher bulk density. Following the packing studies, the Marshall Mix design procedure was used to select the optimum binder content for the four mixtures.
+Over time, the hydrological performance of permeable pavements degrades due to surface clogging from material accumulation. Evaluating the extent of surface clogging is crucial for determining permeable pavements' effectiveness and absorbed permeability. Location, site characteristics, and rain event frequency influence clogging rates. This study employed four different mixtures, creating samples exposed to simulated stormwater events to elucidate relationships between physical components and surface clogging development. Artificial neural network (ANN) models analysed and predicted clogging progression rates, examining the impact of aggregate gradation on permeability, sample thickness, and clogging material value.
+Regarding permanent deformation characteristics, a modified binder mixture exhibited high rut depths of 2.5 to 5.2 mm at different temperatures and mixtures. The VG30 binder showed a maximum rut depth of 12.2 mm in Open Gr-I and lower values at 50°C in Open Gr-II. Durability assessments revealed that both binders performed well, meeting the Cantabro loss limit. The porous asphalt mixture's resilient modulus value exceeded 2400 MPa, with the modified binders showing the highest values.
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1717,7 +1735,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1739,10 +1757,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1751,7 +1769,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -1768,7 +1786,7 @@
         <v>106</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>8</v>
@@ -1780,7 +1798,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1799,10 +1817,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1811,7 +1829,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -1825,10 +1843,10 @@
         <v>29</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>268</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -1843,7 +1861,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1863,10 +1881,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1875,7 +1893,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1889,7 +1907,7 @@
         <v>31</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
@@ -1907,16 +1925,16 @@
         <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -1925,7 +1943,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1944,10 +1962,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1956,7 +1974,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -1970,10 +1988,10 @@
         <v>35</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
@@ -1990,10 +2008,10 @@
         <v>38</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>39</v>
@@ -2010,10 +2028,10 @@
         <v>41</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>36</v>
@@ -2029,7 +2047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2047,10 +2065,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2059,7 +2077,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2073,10 +2091,10 @@
         <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>39</v>
@@ -2088,7 +2106,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2103,10 +2121,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2115,7 +2133,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2129,10 +2147,10 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>39</v>
@@ -2144,7 +2162,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2162,10 +2180,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2174,7 +2192,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2188,17 +2206,17 @@
         <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2212,10 +2230,10 @@
         <v>49</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>39</v>
@@ -2228,7 +2246,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2247,10 +2265,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2259,7 +2277,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="315" x14ac:dyDescent="0.25">
@@ -2273,14 +2291,14 @@
         <v>51</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2294,10 +2312,10 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>36</v>
@@ -2310,7 +2328,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2328,10 +2346,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2340,7 +2358,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2354,10 +2372,10 @@
         <v>55</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
@@ -2375,10 +2393,10 @@
         <v>57</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>36</v>
@@ -2391,7 +2409,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2412,10 +2430,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2424,7 +2442,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2438,10 +2456,10 @@
         <v>59</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
@@ -2457,7 +2475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2478,10 +2496,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2490,7 +2508,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2504,10 +2522,10 @@
         <v>61</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>36</v>
@@ -2520,7 +2538,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2538,10 +2556,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2550,7 +2568,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2567,16 +2585,16 @@
         <v>107</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -2585,7 +2603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2604,10 +2622,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2616,7 +2634,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2630,10 +2648,10 @@
         <v>63</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>64</v>
@@ -2642,7 +2660,7 @@
         <v>65</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -2651,7 +2669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2671,10 +2689,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2683,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2697,16 +2715,16 @@
         <v>67</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -2715,7 +2733,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2735,10 +2753,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2747,7 +2765,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2761,16 +2779,16 @@
         <v>70</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2784,16 +2802,16 @@
         <v>73</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2807,16 +2825,16 @@
         <v>75</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2830,10 +2848,10 @@
         <v>77</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>64</v>
@@ -2851,16 +2869,16 @@
         <v>79</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -2874,10 +2892,10 @@
         <v>81</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>82</v>
@@ -2890,7 +2908,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2911,10 +2929,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>3</v>
@@ -2923,7 +2941,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
@@ -2939,10 +2957,10 @@
         <v>84</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>68</v>
@@ -2963,16 +2981,16 @@
         <v>86</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="7"/>
@@ -2989,16 +3007,16 @@
         <v>89</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="7"/>
@@ -3010,7 +3028,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3029,10 +3047,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>3</v>
@@ -3041,7 +3059,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3055,16 +3073,16 @@
         <v>91</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H2" s="7"/>
     </row>
@@ -3079,16 +3097,16 @@
         <v>93</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H3" s="7"/>
     </row>
@@ -3103,16 +3121,16 @@
         <v>95</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H4" s="7"/>
     </row>
@@ -3122,7 +3140,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3143,10 +3161,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3155,7 +3173,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
@@ -3163,22 +3181,22 @@
         <v>2022</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3189,19 +3207,19 @@
         <v>96</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>68</v>
       </c>
       <c r="G3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3215,10 +3233,10 @@
         <v>98</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>71</v>
@@ -3236,16 +3254,16 @@
         <v>100</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3259,16 +3277,16 @@
         <v>102</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3282,16 +3300,16 @@
         <v>104</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>82</v>
       </c>
       <c r="G7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3299,22 +3317,22 @@
         <v>2022</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>105</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -3323,7 +3341,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3344,10 +3362,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3356,7 +3374,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3370,10 +3388,10 @@
         <v>114</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3387,16 +3405,16 @@
         <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3410,10 +3428,10 @@
         <v>116</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -3422,7 +3440,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3443,10 +3461,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3455,10 +3473,10 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -3466,16 +3484,19 @@
         <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
         <v>117</v>
       </c>
+      <c r="E2" s="10" t="s">
+        <v>296</v>
+      </c>
       <c r="F2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G2" t="s">
         <v>188</v>
-      </c>
-      <c r="G2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3489,13 +3510,13 @@
         <v>118</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3506,19 +3527,19 @@
         <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D4" t="s">
         <v>119</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3532,13 +3553,13 @@
         <v>120</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3552,24 +3573,27 @@
         <v>121</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2024</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>298</v>
       </c>
       <c r="D7" t="s">
         <v>122</v>
       </c>
+      <c r="E7" s="15" t="s">
+        <v>297</v>
+      </c>
       <c r="F7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3577,22 +3601,22 @@
         <v>2024</v>
       </c>
       <c r="B8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D8" t="s">
         <v>123</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -3601,46 +3625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E2" s="10"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3663,10 +3648,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3675,24 +3660,27 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>133</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>299</v>
       </c>
       <c r="F2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3700,22 +3688,22 @@
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="F3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" t="s">
         <v>182</v>
-      </c>
-      <c r="D3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G3" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3723,22 +3711,22 @@
         <v>2025</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G4" t="s">
         <v>184</v>
-      </c>
-      <c r="G4" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3746,22 +3734,22 @@
         <v>2025</v>
       </c>
       <c r="B5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" t="s">
         <v>223</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>223</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="D5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>274</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3769,28 +3757,67 @@
         <v>2025</v>
       </c>
       <c r="B6" t="s">
+        <v>286</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>289</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>290</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G5" r:id="rId1" xr:uid="{00000000-0004-0000-1C00-000000000000}"/>
+    <hyperlink ref="G5" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E2" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3808,10 +3835,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3820,7 +3847,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3837,7 +3864,7 @@
         <v>108</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -3848,8 +3875,17 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3868,10 +3904,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3880,7 +3916,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3897,7 +3933,7 @@
         <v>109</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -3909,7 +3945,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3924,10 +3960,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3936,7 +3972,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3953,7 +3989,7 @@
         <v>110</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -3965,7 +4001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3983,10 +4019,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3995,7 +4031,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -4009,10 +4045,10 @@
         <v>19</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -4024,7 +4060,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4039,10 +4075,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -4051,7 +4087,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -4065,10 +4101,10 @@
         <v>21</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -4080,7 +4116,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4102,10 +4138,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -4114,7 +4150,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="90" x14ac:dyDescent="0.25">
@@ -4128,7 +4164,7 @@
         <v>23</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
@@ -4140,19 +4176,19 @@
         <v>1989</v>
       </c>
       <c r="B3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -4161,7 +4197,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4182,10 +4218,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -4194,7 +4230,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -4208,10 +4244,10 @@
         <v>25</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -4228,7 +4264,7 @@
         <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Downloads\mainnn\NITW-Transportation-Division-main\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="8550" firstSheet="22" activeTab="27"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="8550" firstSheet="20" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="304">
   <si>
     <t>Year</t>
   </si>
@@ -1294,6 +1294,18 @@
 Over time, the hydrological performance of permeable pavements degrades due to surface clogging from material accumulation. Evaluating the extent of surface clogging is crucial for determining permeable pavements' effectiveness and absorbed permeability. Location, site characteristics, and rain event frequency influence clogging rates. This study employed four different mixtures, creating samples exposed to simulated stormwater events to elucidate relationships between physical components and surface clogging development. Artificial neural network (ANN) models analysed and predicted clogging progression rates, examining the impact of aggregate gradation on permeability, sample thickness, and clogging material value.
 Regarding permanent deformation characteristics, a modified binder mixture exhibited high rut depths of 2.5 to 5.2 mm at different temperatures and mixtures. The VG30 binder showed a maximum rut depth of 12.2 mm in Open Gr-I and lower values at 50°C in Open Gr-II. Durability assessments revealed that both binders performed well, meeting the Cantabro loss limit. The porous asphalt mixture's resilient modulus value exceeded 2400 MPa, with the modified binders showing the highest values.
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phd_Alumini/S2025/S. Padma Tejaswi </t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2024/Ramesh Babu Kota</t>
+  </si>
+  <si>
+    <t>Previous Faculty/B.P.Chandrashekhar</t>
+  </si>
+  <si>
+    <t>Previous Faculty/TS Reddy</t>
   </si>
 </sst>
 </file>
@@ -1420,7 +1432,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1455,6 +1467,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1868,6 +1881,7 @@
     <col min="4" max="4" width="21.85546875" customWidth="1"/>
     <col min="5" max="5" width="44.140625" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1912,6 +1926,9 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3594,6 +3611,9 @@
       </c>
       <c r="F7" t="s">
         <v>187</v>
+      </c>
+      <c r="G7" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
@@ -3767,6 +3787,9 @@
       </c>
       <c r="F6" s="17" t="s">
         <v>289</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -3938,6 +3961,9 @@
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="G2" s="3" t="s">
+        <v>302</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="8550" firstSheet="20" activeTab="22"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="8550" firstSheet="18" activeTab="24"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="307">
   <si>
     <t>Year</t>
   </si>
@@ -1306,6 +1306,15 @@
   </si>
   <si>
     <t>Previous Faculty/TS Reddy</t>
+  </si>
+  <si>
+    <t>Previous Faculty/Dr. Francis Christopher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phd_Alumini/S2020/Eswar Sala </t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2019/D.Harinder</t>
   </si>
 </sst>
 </file>
@@ -1817,6 +1826,7 @@
   <cols>
     <col min="4" max="4" width="21.42578125" customWidth="1"/>
     <col min="5" max="5" width="48" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1863,6 +1873,9 @@
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -2917,7 +2930,9 @@
       <c r="F7" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>306</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2982,7 +2997,9 @@
       <c r="F2" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>305</v>
+      </c>
       <c r="H2" s="15"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="8550" firstSheet="18" activeTab="24"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="8550" firstSheet="23" activeTab="28"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,6 @@
     <sheet name="2024" sheetId="27" r:id="rId27"/>
     <sheet name="2025" sheetId="28" r:id="rId28"/>
     <sheet name="2026" sheetId="29" r:id="rId29"/>
-    <sheet name="Sheet1" sheetId="30" r:id="rId30"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -53,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="313">
   <si>
     <t>Year</t>
   </si>
@@ -1316,12 +1315,36 @@
   <si>
     <t>Phd_Alumini/S2019/D.Harinder</t>
   </si>
+  <si>
+    <t>Chintakayala Lalitha Sree</t>
+  </si>
+  <si>
+    <t>Transit oriented development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urban transportation systems have undergone continuous transformation, yet cities in developing nations continue to face persistent challenges, including inadequate infrastructure, operational inefficiencies, and fragmented institutional planning. These interconnected issues influence not only urban mobility but also economic productivity, social equity, and urban liveability. In response, planning approaches such as Transit-Oriented Development (TOD) have emerged as transformative frameworks advocating compact urban growth, mixed land use, walkability, and transit-centred accessibility. Although TOD has gained global recognition, its implementation in countries like India remains constrained by weak integration between high-capacity transit systems and the quality of first- and last-mile access infrastructure. This limitation highlights the need to move beyond infrastructure-centric planning towards a broader understanding of the transit ecosystem, where the interaction between users and surrounding access infrastructure ultimately determines the effectiveness of transit-oriented areas.
+The existing literature on TOD assessment frameworks have progressively evolved from conventional land-use and accessibility indicators toward multidimensional approaches incorporating Density, Diversity, Design, Distance to Transit, Destination Accessibility, Demand Management, Desirability, Dissonance, and Deference to Environment. However, these “D” proliferated frameworks continue to underrepresent the experiential dimension of mobility, particularly the operational and perceptual quality of transit-accessing infrastructure (TAI) such as sidewalks and carriageways. From a theoretical perspective, dependence on carriageways for pedestrian movement deviates from the fundamental principles of TOD, which prioritise dedicated, safe, and continuous pedestrian infrastructure. Nevertheless, in developing urban contexts, carriageways frequently become an unavoidable component of the station access environment due to discontinuous sidewalks, encroachments, informal activities, and inadequate pedestrian facilities. Their persistent use reflects underlying infrastructural deficiencies and behavioural adaptations, making their evaluation essential for understanding mobility realities around transit stations. Simultaneously, evaluating sidewalks remains equally critical, as their physical and perceptual quality directly influences whether users remain within designated pedestrian spaces or shift toward carriageway usage. Together, the assessments of both facilities provide a deeper understanding of how closely transit areas align with or deviate from the intended principles of TOD from the user's point of view.
+Addressing these gaps, the present research introduces a user-centric Transit Ecosystem Index (TEI) to evaluate TAI within the station influence areas. The framework conceptualises these elements not merely as physical infrastructure, but as active determinants of user behaviour, accessibility, and modal integration. To achieve this objective, the study adopts a mixed-method framework integrating engineering assessment, behavioural modelling, and multi-criteria decision analysis. The methodology combines the Analytic Hierarchy Process (AHP) and Technique for Order Preference by Similarity to Ideal Solution (TOPSIS) to establish benchmark-based infrastructure performance, while Ordinal Logistic Regression (OLR) is employed to quantify the behavioural influence of user perceptions. The TEI is structured around two complementary dimensions: Optimised Level of Service (OLOS), which represents objective infrastructure performance, and Desirability Scores (DS), representing subjective user experiences. Normalised odds ratios derived from OLR are incorporated as variable weights within the decision-making framework, enabling perceptual responses to be transformed into measurable infrastructure performance indicators. This integration bridges statistical inference with practical planning evaluation. Unlike conventional TOD indices that primarily measure the spatial potential of station areas through static built-environment indicators, the TEI evaluates the operational and experiential realisation of TOD by integrating observed infrastructure performance with user desirability and behaviourally derived attribute weights.
+Empirical investigations were conducted across selected metro and suburban rail station influence areas characterised by high-density land use and intense multimodal interactions typical of TOD environments. Comprehensive field audits and user perception surveys were undertaken to evaluate both sidewalks and carriageways under diverse operational conditions. The findings demonstrate a strong and statistically significant relationship between infrastructure quality and user desirability. Sidewalk infrastructure emerged as the strongest determinant of overall transit ecosystem performance, significantly influencing perceptions of safety, comfort, continuity, and willingness to adopt non-motorised travel. Factors such as effective width, surface condition, obstructions, potential for vehicular conflicts, and path continuity strongly influenced users' preference for sidewalk use. At the same time, carriageway usage was found to be influenced by variables such as sidewalk discontinuity, vehicular interactions, encroachments, and perceived walking convenience. These findings reveal that carriageway usage is not merely a behavioural anomaly, but a measurable response to deficiencies in pedestrian infrastructure. Even in areas served by high-capacity transit systems, inadequate pedestrian environments significantly reduced perceived accessibility and weakened overall TOD performance. Conversely, improvements in pedestrian infrastructure, along with strategic interventions addressing carriageway-related deficiencies, can enhance alignment with TOD principles. Transforming carriageway constraints into pedestrian-oriented and sustainable mobility solutions, such as dedicated public transport corridors, improved street design, traffic calming measures, and context-sensitive operational improvements, has the potential to significantly enhance user satisfaction, accessibility, safety, and multimodal integration. 
+The study further demonstrates that conventional Level of Service (LOS) measures and existing TOD indices are insufficient in capturing the behavioural and perception-driven realities of urban mobility in developing contexts. By integrating infrastructure audits with behavioural modelling, the proposed TEI offers a comprehensive, empirically grounded, and context-sensitive framework for evaluating transit station ecosystems. The framework not only identifies the variables influencing sidewalk and carriageway usage, but also enables assessment of whether transit station environments are progressing toward or deviating from the intended principles of TOD.
+This research contributes to the advancement of urban transport evaluation by shifting the analytical focus from static infrastructure provision toward dynamic, user-centred ecosystem assessment. The findings provide practical insights for planners, engineers, and policymakers to design transit environments that are efficient, inclusive, safe, and resilient. Ultimately, the study reinforces that sustainable urban mobility depends not only on the availability of transit infrastructure but also on how effectively that infrastructure is experienced, perceived, and utilised by its users.
+</t>
+  </si>
+  <si>
+    <t>Prof. C.S.R.K. Prasad and Prof. Bhadradri Raghuram Kadali</t>
+  </si>
+  <si>
+    <t>https://www.nitw.ac.in/CIVDeptAssets/images/phd62.jpg</t>
+  </si>
+  <si>
+    <t>Development of User centric Transit Ecosystem Index (TEI): A Framework for Integrating Optimized Level of Service and Desirability Score of Transit Accessing Infrastructure.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1419,6 +1442,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman "/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman "/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Times New Roman "/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1441,7 +1479,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1477,6 +1515,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1759,7 +1804,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
     <col min="3" max="5" width="42.28515625" customWidth="1"/>
@@ -1768,7 +1813,7 @@
     <col min="8" max="8" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1794,7 +1839,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1980</v>
       </c>
@@ -1822,14 +1867,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="21.42578125" customWidth="1"/>
     <col min="5" max="5" width="48" customWidth="1"/>
     <col min="7" max="7" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1855,7 +1900,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1996</v>
       </c>
@@ -1878,7 +1923,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75">
       <c r="G3" s="2"/>
     </row>
   </sheetData>
@@ -1889,7 +1934,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="21.85546875" customWidth="1"/>
     <col min="5" max="5" width="44.140625" customWidth="1"/>
@@ -1897,7 +1942,7 @@
     <col min="7" max="7" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1923,7 +1968,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="60">
       <c r="A2" s="3">
         <v>1997</v>
       </c>
@@ -1944,7 +1989,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>1997</v>
       </c>
@@ -1975,13 +2020,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="5" max="5" width="157.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2007,7 +2052,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1998</v>
       </c>
@@ -2027,7 +2072,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>1998</v>
       </c>
@@ -2047,7 +2092,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4" s="3">
         <v>1998</v>
       </c>
@@ -2067,7 +2112,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
     </row>
@@ -2079,12 +2124,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2110,7 +2155,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1999</v>
       </c>
@@ -2138,9 +2183,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2166,7 +2211,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2000</v>
       </c>
@@ -2194,12 +2239,12 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2225,7 +2270,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2001</v>
       </c>
@@ -2249,7 +2294,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>2001</v>
       </c>
@@ -2278,13 +2323,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="60.28515625" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2310,7 +2355,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="315">
       <c r="A2" s="3">
         <v>2003</v>
       </c>
@@ -2331,7 +2376,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>2003</v>
       </c>
@@ -2360,12 +2405,12 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="46.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2391,7 +2436,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2004</v>
       </c>
@@ -2412,7 +2457,7 @@
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>2004</v>
       </c>
@@ -2441,7 +2486,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="24.7109375" customWidth="1"/>
     <col min="4" max="4" width="23.42578125" customWidth="1"/>
@@ -2449,7 +2494,7 @@
     <col min="6" max="6" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2475,7 +2520,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2005</v>
       </c>
@@ -2496,7 +2541,7 @@
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75">
       <c r="G3" s="2"/>
     </row>
   </sheetData>
@@ -2507,7 +2552,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="3" width="27.7109375" customWidth="1"/>
@@ -2515,7 +2560,7 @@
     <col min="5" max="5" width="48.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2541,7 +2586,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2006</v>
       </c>
@@ -2570,12 +2615,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="5" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2601,7 +2646,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1982</v>
       </c>
@@ -2635,13 +2680,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="45.5703125" customWidth="1"/>
     <col min="8" max="8" width="40.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2667,7 +2712,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2012</v>
       </c>
@@ -2701,14 +2746,14 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="4" max="4" width="30.42578125" customWidth="1"/>
     <col min="5" max="5" width="58.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2734,7 +2779,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2018</v>
       </c>
@@ -2765,14 +2810,14 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="138.5703125" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" customWidth="1"/>
     <col min="7" max="7" width="40.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2798,7 +2843,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2019</v>
       </c>
@@ -2821,7 +2866,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>2019</v>
       </c>
@@ -2844,7 +2889,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4" s="3">
         <v>2019</v>
       </c>
@@ -2867,7 +2912,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="409.5">
       <c r="A5" s="3">
         <v>2019</v>
       </c>
@@ -2888,7 +2933,7 @@
       </c>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="409.5">
       <c r="A6" s="3">
         <v>2019</v>
       </c>
@@ -2911,7 +2956,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="409.5">
       <c r="A7" s="3">
         <v>2019</v>
       </c>
@@ -2942,7 +2987,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="34.140625" customWidth="1"/>
     <col min="3" max="3" width="56.140625" customWidth="1"/>
@@ -2950,7 +2995,7 @@
     <col min="5" max="5" width="46.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -2978,7 +3023,7 @@
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
     </row>
-    <row r="2" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="409.5">
       <c r="A2" s="12">
         <v>2020</v>
       </c>
@@ -3004,7 +3049,7 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="409.5">
       <c r="A3" s="12">
         <v>2020</v>
       </c>
@@ -3030,7 +3075,7 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="409.5">
       <c r="A4" s="12">
         <v>2020</v>
       </c>
@@ -3064,13 +3109,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="39.7109375" customWidth="1"/>
     <col min="5" max="5" width="118.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3096,7 +3141,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="8">
         <v>2021</v>
       </c>
@@ -3120,7 +3165,7 @@
       </c>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="8">
         <v>2021</v>
       </c>
@@ -3144,7 +3189,7 @@
       </c>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4" s="8">
         <v>2021</v>
       </c>
@@ -3176,7 +3221,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23.42578125" customWidth="1"/>
     <col min="3" max="4" width="41.5703125" customWidth="1"/>
@@ -3184,7 +3229,7 @@
     <col min="6" max="6" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3210,7 +3255,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="409.5">
       <c r="A2">
         <v>2022</v>
       </c>
@@ -3233,7 +3278,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>2022</v>
       </c>
@@ -3256,7 +3301,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4" s="3">
         <v>2022</v>
       </c>
@@ -3277,7 +3322,7 @@
       </c>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="409.5">
       <c r="A5" s="3">
         <v>2022</v>
       </c>
@@ -3300,7 +3345,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="409.5">
       <c r="A6" s="3">
         <v>2022</v>
       </c>
@@ -3323,7 +3368,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="409.5">
       <c r="A7" s="3">
         <v>2022</v>
       </c>
@@ -3346,7 +3391,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="409.5">
       <c r="A8" s="3">
         <v>2022</v>
       </c>
@@ -3377,7 +3422,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
     <col min="4" max="4" width="52" customWidth="1"/>
@@ -3385,7 +3430,7 @@
     <col min="6" max="6" width="70.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3411,7 +3456,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2">
         <v>2023</v>
       </c>
@@ -3428,7 +3473,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3">
         <v>2023</v>
       </c>
@@ -3451,7 +3496,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4">
         <v>2023</v>
       </c>
@@ -3476,7 +3521,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="51.85546875" customWidth="1"/>
     <col min="4" max="4" width="45.5703125" customWidth="1"/>
@@ -3484,7 +3529,7 @@
     <col min="6" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3510,7 +3555,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -3533,7 +3578,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3">
         <v>2024</v>
       </c>
@@ -3553,7 +3598,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4">
         <v>2024</v>
       </c>
@@ -3576,7 +3621,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="409.5">
       <c r="A5">
         <v>2024</v>
       </c>
@@ -3596,7 +3641,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="409.5">
       <c r="A6">
         <v>2024</v>
       </c>
@@ -3613,7 +3658,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75">
       <c r="A7">
         <v>2024</v>
       </c>
@@ -3633,7 +3678,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="409.5">
       <c r="A8">
         <v>2024</v>
       </c>
@@ -3664,7 +3709,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
     <col min="3" max="3" width="54" customWidth="1"/>
@@ -3674,7 +3719,7 @@
     <col min="8" max="8" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3700,7 +3745,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2">
         <v>2025</v>
       </c>
@@ -3720,7 +3765,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -3743,7 +3788,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4">
         <v>2025</v>
       </c>
@@ -3766,7 +3811,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="409.5">
       <c r="A5">
         <v>2025</v>
       </c>
@@ -3789,7 +3834,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="409.5">
       <c r="A6">
         <v>2025</v>
       </c>
@@ -3820,9 +3865,14 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="36.140625" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" customWidth="1"/>
+    <col min="5" max="5" width="36.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3848,10 +3898,33 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E2" s="10"/>
+    <row r="2" spans="1:8" ht="409.5">
+      <c r="A2">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>311</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3859,12 +3932,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="48.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3890,7 +3963,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1983</v>
       </c>
@@ -3911,15 +3984,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3927,13 +3991,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="10.140625" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3959,7 +4023,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1984</v>
       </c>
@@ -3990,9 +4054,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4018,7 +4082,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1985</v>
       </c>
@@ -4046,12 +4110,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="93.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4077,7 +4141,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1986</v>
       </c>
@@ -4105,9 +4169,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4133,7 +4197,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1988</v>
       </c>
@@ -4161,7 +4225,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" customWidth="1"/>
@@ -4170,7 +4234,7 @@
     <col min="6" max="6" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4196,7 +4260,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="90">
       <c r="A2" s="3">
         <v>1989</v>
       </c>
@@ -4214,7 +4278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="409.5">
       <c r="A3">
         <v>1989</v>
       </c>
@@ -4242,7 +4306,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="30.7109375" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
@@ -4250,7 +4314,7 @@
     <col min="6" max="6" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4276,7 +4340,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1992</v>
       </c>
@@ -4296,7 +4360,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="60">
       <c r="A3" s="3">
         <v>1992</v>
       </c>

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Downloads\mainnn\NITW-Transportation-Division-main\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Documents\PA_catts(A)\mainnn\NITW-Transportation-Division-main\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="8550" firstSheet="23" activeTab="28"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" firstSheet="11" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="320">
   <si>
     <t>Year</t>
   </si>
@@ -1339,12 +1339,33 @@
   <si>
     <t>Development of User centric Transit Ecosystem Index (TEI): A Framework for Integrating Optimized Level of Service and Desirability Score of Transit Accessing Infrastructure.</t>
   </si>
+  <si>
+    <t>Transportation Engineering</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2024/ANGATHA RAMA KANTH</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2023/T. Arjun Kumar</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2022/Pallavi G</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2019/P. Sharat Chandra</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S1998/R. Murugesan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professor (Department of Civil Engineering) at Nandha Engineering College Erode, Tamil Nadu </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1457,6 +1478,12 @@
       <color theme="10"/>
       <name val="Times New Roman "/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1479,7 +1506,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1522,6 +1549,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1804,7 +1832,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
     <col min="3" max="5" width="42.28515625" customWidth="1"/>
@@ -1813,7 +1841,7 @@
     <col min="8" max="8" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1839,7 +1867,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1980</v>
       </c>
@@ -1867,14 +1895,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="21.42578125" customWidth="1"/>
     <col min="5" max="5" width="48" customWidth="1"/>
     <col min="7" max="7" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1900,7 +1928,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1996</v>
       </c>
@@ -1923,7 +1951,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75">
+    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="G3" s="2"/>
     </row>
   </sheetData>
@@ -1934,7 +1962,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="21.85546875" customWidth="1"/>
     <col min="5" max="5" width="44.140625" customWidth="1"/>
@@ -1942,7 +1970,7 @@
     <col min="7" max="7" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1968,7 +1996,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="60">
+    <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1997</v>
       </c>
@@ -1989,7 +2017,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5">
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1997</v>
       </c>
@@ -2020,13 +2048,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="5" max="5" width="157.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2052,7 +2080,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1998</v>
       </c>
@@ -2071,8 +2099,14 @@
       <c r="F2" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="409.5">
+      <c r="G2" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1998</v>
       </c>
@@ -2092,7 +2126,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5">
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1998</v>
       </c>
@@ -2112,7 +2146,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
     </row>
@@ -2124,12 +2158,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2155,7 +2189,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1999</v>
       </c>
@@ -2183,9 +2217,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2211,7 +2245,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2000</v>
       </c>
@@ -2239,12 +2273,12 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2270,7 +2304,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2001</v>
       </c>
@@ -2294,7 +2328,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5">
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2001</v>
       </c>
@@ -2323,13 +2357,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="60.28515625" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2355,7 +2389,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="315">
+    <row r="2" spans="1:8" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2003</v>
       </c>
@@ -2376,7 +2410,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5">
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2003</v>
       </c>
@@ -2405,12 +2439,12 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="46.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2436,7 +2470,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2004</v>
       </c>
@@ -2457,7 +2491,7 @@
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="409.5">
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2004</v>
       </c>
@@ -2486,7 +2520,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="24.7109375" customWidth="1"/>
     <col min="4" max="4" width="23.42578125" customWidth="1"/>
@@ -2494,7 +2528,7 @@
     <col min="6" max="6" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2520,7 +2554,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2005</v>
       </c>
@@ -2541,7 +2575,7 @@
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75">
+    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="G3" s="2"/>
     </row>
   </sheetData>
@@ -2552,7 +2586,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="3" width="27.7109375" customWidth="1"/>
@@ -2560,7 +2594,7 @@
     <col min="5" max="5" width="48.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2586,7 +2620,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2006</v>
       </c>
@@ -2615,12 +2649,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="5" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2646,7 +2680,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1982</v>
       </c>
@@ -2680,13 +2714,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="45.5703125" customWidth="1"/>
     <col min="8" max="8" width="40.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2712,7 +2746,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2012</v>
       </c>
@@ -2746,14 +2780,14 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="4" max="4" width="30.42578125" customWidth="1"/>
     <col min="5" max="5" width="58.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2779,7 +2813,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2018</v>
       </c>
@@ -2810,14 +2844,14 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="138.5703125" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" customWidth="1"/>
     <col min="7" max="7" width="40.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2843,7 +2877,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2019</v>
       </c>
@@ -2866,7 +2900,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5">
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2019</v>
       </c>
@@ -2889,7 +2923,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5">
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2019</v>
       </c>
@@ -2912,7 +2946,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.5">
+    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2019</v>
       </c>
@@ -2931,9 +2965,11 @@
       <c r="F5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" ht="409.5">
+      <c r="G5" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2019</v>
       </c>
@@ -2956,7 +2992,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="409.5">
+    <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2019</v>
       </c>
@@ -2987,7 +3023,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34.140625" customWidth="1"/>
     <col min="3" max="3" width="56.140625" customWidth="1"/>
@@ -2995,7 +3031,7 @@
     <col min="5" max="5" width="46.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -3023,7 +3059,7 @@
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
     </row>
-    <row r="2" spans="1:10" ht="409.5">
+    <row r="2" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="12">
         <v>2020</v>
       </c>
@@ -3049,7 +3085,7 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="1:10" ht="409.5">
+    <row r="3" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="12">
         <v>2020</v>
       </c>
@@ -3075,7 +3111,7 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" ht="409.5">
+    <row r="4" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>2020</v>
       </c>
@@ -3109,13 +3145,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="39.7109375" customWidth="1"/>
     <col min="5" max="5" width="118.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3141,7 +3177,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>2021</v>
       </c>
@@ -3165,7 +3201,7 @@
       </c>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" ht="409.5">
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>2021</v>
       </c>
@@ -3189,7 +3225,7 @@
       </c>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" ht="409.5">
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>2021</v>
       </c>
@@ -3221,7 +3257,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.42578125" customWidth="1"/>
     <col min="3" max="4" width="41.5703125" customWidth="1"/>
@@ -3229,7 +3265,7 @@
     <col min="6" max="6" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3255,7 +3291,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="409.5">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2022</v>
       </c>
@@ -3278,7 +3314,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5">
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2022</v>
       </c>
@@ -3301,7 +3337,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5">
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2022</v>
       </c>
@@ -3320,9 +3356,11 @@
       <c r="F4" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" ht="409.5">
+      <c r="G4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2022</v>
       </c>
@@ -3345,7 +3383,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="409.5">
+    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2022</v>
       </c>
@@ -3368,7 +3406,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="409.5">
+    <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2022</v>
       </c>
@@ -3391,7 +3429,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="409.5">
+    <row r="8" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>2022</v>
       </c>
@@ -3422,7 +3460,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
     <col min="4" max="4" width="52" customWidth="1"/>
@@ -3430,7 +3468,7 @@
     <col min="6" max="6" width="70.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3456,7 +3494,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2023</v>
       </c>
@@ -3472,8 +3510,11 @@
       <c r="F2" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="409.5">
+      <c r="G2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2023</v>
       </c>
@@ -3496,7 +3537,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5">
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2023</v>
       </c>
@@ -3521,7 +3562,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="51.85546875" customWidth="1"/>
     <col min="4" max="4" width="45.5703125" customWidth="1"/>
@@ -3529,7 +3570,7 @@
     <col min="6" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3555,7 +3596,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -3578,7 +3619,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5">
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2024</v>
       </c>
@@ -3598,7 +3639,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5">
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2024</v>
       </c>
@@ -3621,7 +3662,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.5">
+    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2024</v>
       </c>
@@ -3641,13 +3682,16 @@
         <v>194</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="409.5">
+    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2024</v>
       </c>
       <c r="B6" t="s">
         <v>128</v>
       </c>
+      <c r="C6" t="s">
+        <v>313</v>
+      </c>
       <c r="D6" t="s">
         <v>121</v>
       </c>
@@ -3657,8 +3701,11 @@
       <c r="F6" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75">
+      <c r="G6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2024</v>
       </c>
@@ -3678,7 +3725,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="409.5">
+    <row r="8" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2024</v>
       </c>
@@ -3709,7 +3756,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
     <col min="3" max="3" width="54" customWidth="1"/>
@@ -3719,7 +3766,7 @@
     <col min="8" max="8" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3745,7 +3792,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2025</v>
       </c>
@@ -3765,7 +3812,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5">
+    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -3788,7 +3835,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5">
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2025</v>
       </c>
@@ -3811,7 +3858,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.5">
+    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2025</v>
       </c>
@@ -3834,7 +3881,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="409.5">
+    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2025</v>
       </c>
@@ -3865,14 +3912,14 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.140625" customWidth="1"/>
     <col min="3" max="3" width="38.140625" customWidth="1"/>
     <col min="5" max="5" width="36.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3898,7 +3945,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2026</v>
       </c>
@@ -3932,12 +3979,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="48.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3963,7 +4010,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1983</v>
       </c>
@@ -3991,13 +4038,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10.140625" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4023,7 +4070,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1984</v>
       </c>
@@ -4054,9 +4101,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4082,7 +4129,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1985</v>
       </c>
@@ -4110,12 +4157,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="93.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4141,7 +4188,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1986</v>
       </c>
@@ -4169,9 +4216,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4197,7 +4244,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1988</v>
       </c>
@@ -4225,7 +4272,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" customWidth="1"/>
@@ -4234,7 +4281,7 @@
     <col min="6" max="6" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4260,7 +4307,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="90">
+    <row r="2" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1989</v>
       </c>
@@ -4278,7 +4325,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="409.5">
+    <row r="3" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1989</v>
       </c>
@@ -4306,7 +4353,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="30.7109375" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
@@ -4314,7 +4361,7 @@
     <col min="6" max="6" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4340,7 +4387,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5">
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1992</v>
       </c>
@@ -4360,7 +4407,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="60">
+    <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1992</v>
       </c>

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" firstSheet="11" activeTab="11"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="334">
   <si>
     <t>Year</t>
   </si>
@@ -1360,12 +1360,54 @@
   <si>
     <t xml:space="preserve">Professor (Department of Civil Engineering) at Nandha Engineering College Erode, Tamil Nadu </t>
   </si>
+  <si>
+    <t>Phd_Alumini/S2000/Fareed Md Abdul Karim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professor  at  University of Aden in  Civil (Transportation Engineering) </t>
+  </si>
+  <si>
+    <t>Prof and Dean at Lords Institute of Engineering and Technology, Hyderabad</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S1998/Syed Anisuddin</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S1998/N. Trivikrama Rao</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Vice Chancellor at MIT World Peace University. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Vice-Chancellor of Jawaharlal Nehru Technological University, Kakinada (JNTU-Kakinada) On Deputation from Professor (HAG) in the Department of Civil Engineering.</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S1992/S. Nagabhushana Rao</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Director (Retd.), ESCI, Hyderabad</t>
+  </si>
+  <si>
+    <t>Practice Lead for SRF Consulting Group, Florida, United States</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S1983/B.N. Nagaraj</t>
+  </si>
+  <si>
+    <t>Retd. Director, NIT Calicut</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S1985/L.R. Kadiyali</t>
+  </si>
+  <si>
+    <t>Retd. Chief Engineer (Roads Wing), Chief Executive of L.R. Kadiyali &amp; Associates (New Delhi)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1484,6 +1526,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1506,7 +1554,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1550,6 +1598,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1832,7 +1881,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
     <col min="3" max="5" width="42.28515625" customWidth="1"/>
@@ -1841,7 +1890,7 @@
     <col min="8" max="8" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1867,7 +1916,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1980</v>
       </c>
@@ -1895,14 +1944,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="21.42578125" customWidth="1"/>
     <col min="5" max="5" width="48" customWidth="1"/>
     <col min="7" max="7" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1928,7 +1977,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1996</v>
       </c>
@@ -1950,8 +1999,11 @@
       <c r="G2" s="3" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H2" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75">
       <c r="G3" s="2"/>
     </row>
   </sheetData>
@@ -1962,7 +2014,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="21.85546875" customWidth="1"/>
     <col min="5" max="5" width="44.140625" customWidth="1"/>
@@ -1970,7 +2022,7 @@
     <col min="7" max="7" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1996,7 +2048,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="60">
       <c r="A2" s="3">
         <v>1997</v>
       </c>
@@ -2017,7 +2069,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>1997</v>
       </c>
@@ -2039,8 +2091,14 @@
       <c r="G3" s="4" t="s">
         <v>177</v>
       </c>
+      <c r="H3" s="3" t="s">
+        <v>326</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2048,13 +2106,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="5" max="5" width="157.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2080,7 +2138,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1998</v>
       </c>
@@ -2106,7 +2164,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>1998</v>
       </c>
@@ -2125,8 +2183,14 @@
       <c r="F3" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="G3" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4" s="3">
         <v>1998</v>
       </c>
@@ -2145,8 +2209,14 @@
       <c r="F4" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G4" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
     </row>
@@ -2158,12 +2228,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2189,7 +2259,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1999</v>
       </c>
@@ -2217,9 +2287,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2245,7 +2315,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2000</v>
       </c>
@@ -2263,6 +2333,12 @@
       </c>
       <c r="F2" s="3" t="s">
         <v>39</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -2273,12 +2349,12 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2304,7 +2380,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2001</v>
       </c>
@@ -2328,7 +2404,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>2001</v>
       </c>
@@ -2357,13 +2433,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="60.28515625" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2389,7 +2465,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="315">
       <c r="A2" s="3">
         <v>2003</v>
       </c>
@@ -2410,7 +2486,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>2003</v>
       </c>
@@ -2439,12 +2515,12 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="46.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2470,7 +2546,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2004</v>
       </c>
@@ -2491,7 +2567,7 @@
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>2004</v>
       </c>
@@ -2520,7 +2596,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="24.7109375" customWidth="1"/>
     <col min="4" max="4" width="23.42578125" customWidth="1"/>
@@ -2528,7 +2604,7 @@
     <col min="6" max="6" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2554,7 +2630,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2005</v>
       </c>
@@ -2575,7 +2651,7 @@
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75">
       <c r="G3" s="2"/>
     </row>
   </sheetData>
@@ -2586,7 +2662,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="3" width="27.7109375" customWidth="1"/>
@@ -2594,7 +2670,7 @@
     <col min="5" max="5" width="48.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2620,7 +2696,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2006</v>
       </c>
@@ -2649,12 +2725,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="5" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2680,7 +2756,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1982</v>
       </c>
@@ -2714,13 +2790,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="45.5703125" customWidth="1"/>
     <col min="8" max="8" width="40.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2746,7 +2822,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2012</v>
       </c>
@@ -2780,14 +2856,14 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="4" max="4" width="30.42578125" customWidth="1"/>
     <col min="5" max="5" width="58.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2813,7 +2889,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2018</v>
       </c>
@@ -2844,14 +2920,14 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="138.5703125" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" customWidth="1"/>
     <col min="7" max="7" width="40.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2877,7 +2953,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2019</v>
       </c>
@@ -2900,7 +2976,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>2019</v>
       </c>
@@ -2923,7 +2999,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4" s="3">
         <v>2019</v>
       </c>
@@ -2946,7 +3022,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="409.5">
       <c r="A5" s="3">
         <v>2019</v>
       </c>
@@ -2969,7 +3045,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="409.5">
       <c r="A6" s="3">
         <v>2019</v>
       </c>
@@ -2992,7 +3068,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="409.5">
       <c r="A7" s="3">
         <v>2019</v>
       </c>
@@ -3023,7 +3099,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="34.140625" customWidth="1"/>
     <col min="3" max="3" width="56.140625" customWidth="1"/>
@@ -3031,7 +3107,7 @@
     <col min="5" max="5" width="46.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -3059,7 +3135,7 @@
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
     </row>
-    <row r="2" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="409.5">
       <c r="A2" s="12">
         <v>2020</v>
       </c>
@@ -3085,7 +3161,7 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="409.5">
       <c r="A3" s="12">
         <v>2020</v>
       </c>
@@ -3111,7 +3187,7 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="409.5">
       <c r="A4" s="12">
         <v>2020</v>
       </c>
@@ -3145,13 +3221,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="39.7109375" customWidth="1"/>
     <col min="5" max="5" width="118.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3177,7 +3253,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="8">
         <v>2021</v>
       </c>
@@ -3201,7 +3277,7 @@
       </c>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="8">
         <v>2021</v>
       </c>
@@ -3225,7 +3301,7 @@
       </c>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4" s="8">
         <v>2021</v>
       </c>
@@ -3257,7 +3333,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23.42578125" customWidth="1"/>
     <col min="3" max="4" width="41.5703125" customWidth="1"/>
@@ -3265,7 +3341,7 @@
     <col min="6" max="6" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3291,7 +3367,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="409.5">
       <c r="A2">
         <v>2022</v>
       </c>
@@ -3314,7 +3390,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>2022</v>
       </c>
@@ -3337,7 +3413,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4" s="3">
         <v>2022</v>
       </c>
@@ -3360,7 +3436,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="409.5">
       <c r="A5" s="3">
         <v>2022</v>
       </c>
@@ -3383,7 +3459,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="409.5">
       <c r="A6" s="3">
         <v>2022</v>
       </c>
@@ -3406,7 +3482,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="409.5">
       <c r="A7" s="3">
         <v>2022</v>
       </c>
@@ -3429,7 +3505,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="409.5">
       <c r="A8" s="3">
         <v>2022</v>
       </c>
@@ -3460,7 +3536,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
     <col min="4" max="4" width="52" customWidth="1"/>
@@ -3468,7 +3544,7 @@
     <col min="6" max="6" width="70.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3494,7 +3570,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2">
         <v>2023</v>
       </c>
@@ -3514,7 +3590,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3">
         <v>2023</v>
       </c>
@@ -3537,7 +3613,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4">
         <v>2023</v>
       </c>
@@ -3562,7 +3638,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="51.85546875" customWidth="1"/>
     <col min="4" max="4" width="45.5703125" customWidth="1"/>
@@ -3570,7 +3646,7 @@
     <col min="6" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3596,7 +3672,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -3619,7 +3695,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3">
         <v>2024</v>
       </c>
@@ -3639,7 +3715,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4">
         <v>2024</v>
       </c>
@@ -3662,7 +3738,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="409.5">
       <c r="A5">
         <v>2024</v>
       </c>
@@ -3682,7 +3758,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="409.5">
       <c r="A6">
         <v>2024</v>
       </c>
@@ -3705,7 +3781,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75">
       <c r="A7">
         <v>2024</v>
       </c>
@@ -3725,7 +3801,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="409.5">
       <c r="A8">
         <v>2024</v>
       </c>
@@ -3756,7 +3832,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
     <col min="3" max="3" width="54" customWidth="1"/>
@@ -3766,7 +3842,7 @@
     <col min="8" max="8" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3792,7 +3868,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2">
         <v>2025</v>
       </c>
@@ -3812,7 +3888,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -3835,7 +3911,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4">
         <v>2025</v>
       </c>
@@ -3858,7 +3934,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="409.5">
       <c r="A5">
         <v>2025</v>
       </c>
@@ -3881,7 +3957,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="409.5">
       <c r="A6">
         <v>2025</v>
       </c>
@@ -3912,14 +3988,14 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="36.140625" customWidth="1"/>
     <col min="3" max="3" width="38.140625" customWidth="1"/>
     <col min="5" max="5" width="36.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3945,7 +4021,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2">
         <v>2026</v>
       </c>
@@ -3979,12 +4055,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="48.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4010,7 +4086,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1983</v>
       </c>
@@ -4028,6 +4104,12 @@
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -4038,13 +4120,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="10.140625" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4070,7 +4152,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1984</v>
       </c>
@@ -4101,9 +4183,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4129,7 +4211,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1985</v>
       </c>
@@ -4147,6 +4229,12 @@
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -4157,12 +4245,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="93.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4188,7 +4276,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1986</v>
       </c>
@@ -4216,9 +4304,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4244,7 +4332,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1988</v>
       </c>
@@ -4272,7 +4360,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" customWidth="1"/>
@@ -4281,7 +4369,7 @@
     <col min="6" max="6" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4307,7 +4395,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="90">
       <c r="A2" s="3">
         <v>1989</v>
       </c>
@@ -4325,7 +4413,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="409.5">
       <c r="A3">
         <v>1989</v>
       </c>
@@ -4353,7 +4441,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="30.7109375" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
@@ -4361,7 +4449,7 @@
     <col min="6" max="6" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4387,7 +4475,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1992</v>
       </c>
@@ -4407,7 +4495,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="90">
       <c r="A3" s="3">
         <v>1992</v>
       </c>
@@ -4423,6 +4511,12 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" firstSheet="2" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" firstSheet="5" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -3098,16 +3098,19 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="34.140625" customWidth="1"/>
     <col min="3" max="3" width="56.140625" customWidth="1"/>
     <col min="4" max="4" width="53.28515625" customWidth="1"/>
     <col min="5" max="5" width="46.5703125" customWidth="1"/>
+    <col min="6" max="6" width="42.85546875" customWidth="1"/>
+    <col min="7" max="7" width="48.7109375" customWidth="1"/>
+    <col min="8" max="8" width="67" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75">
+    <row r="1" spans="1:8" ht="15.75">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -3132,10 +3135,8 @@
       <c r="H1" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-    </row>
-    <row r="2" spans="1:10" ht="409.5">
+    </row>
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="12">
         <v>2020</v>
       </c>
@@ -3157,11 +3158,8 @@
       <c r="G2" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="H2" s="15"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" spans="1:10" ht="409.5">
+    </row>
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="12">
         <v>2020</v>
       </c>
@@ -3183,11 +3181,8 @@
       <c r="G3" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" spans="1:10" ht="409.5">
+    </row>
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4" s="12">
         <v>2020</v>
       </c>
@@ -3209,9 +3204,6 @@
       <c r="G4" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
